--- a/research/traditional_assets/database/data/botswana/botswana_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bsm_chobe" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.244</v>
+        <v>0.0116</v>
+      </c>
+      <c r="E2">
+        <v>-0.0355</v>
       </c>
       <c r="G2">
-        <v>-0.9409660107334525</v>
+        <v>-0.06680672268907563</v>
       </c>
       <c r="H2">
-        <v>-0.9409660107334525</v>
+        <v>-0.06680672268907563</v>
       </c>
       <c r="I2">
-        <v>-1.261180679785331</v>
+        <v>0.2327731092436975</v>
       </c>
       <c r="J2">
-        <v>-1.261180679785331</v>
+        <v>0.1748600563821034</v>
       </c>
       <c r="K2">
-        <v>-4.96</v>
+        <v>4.69</v>
       </c>
       <c r="L2">
-        <v>-0.8872987477638641</v>
+        <v>0.1970588235294118</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.16</v>
+        <v>10.1</v>
       </c>
       <c r="V2">
-        <v>0.02086330935251798</v>
+        <v>0.1856617647058824</v>
       </c>
       <c r="W2">
-        <v>-0.168135593220339</v>
+        <v>0.183203125</v>
       </c>
       <c r="X2">
-        <v>0.06776339866051559</v>
+        <v>0.1032251926646767</v>
       </c>
       <c r="Y2">
-        <v>-0.2358989918808546</v>
+        <v>0.07997793233532327</v>
       </c>
       <c r="Z2">
-        <v>0.2103876552502823</v>
+        <v>0.975809758097581</v>
       </c>
       <c r="AA2">
-        <v>-0.2653368460669928</v>
+        <v>0.1706301493191497</v>
       </c>
       <c r="AB2">
-        <v>0.06491162149224596</v>
+        <v>0.0990925570278279</v>
       </c>
       <c r="AC2">
-        <v>-0.3302484675592388</v>
+        <v>0.07153759229132176</v>
       </c>
       <c r="AD2">
-        <v>4.84</v>
+        <v>5.38</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.84</v>
+        <v>5.38</v>
       </c>
       <c r="AG2">
-        <v>3.68</v>
+        <v>-4.72</v>
       </c>
       <c r="AH2">
-        <v>0.08007941760423561</v>
+        <v>0.08999665439946471</v>
       </c>
       <c r="AI2">
-        <v>0.1590013140604468</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AJ2">
-        <v>0.06207827260458839</v>
+        <v>-0.09500805152979065</v>
       </c>
       <c r="AK2">
-        <v>0.1256830601092896</v>
+        <v>-0.2128043282236249</v>
       </c>
       <c r="AL2">
-        <v>0.32</v>
+        <v>0.349</v>
       </c>
       <c r="AM2">
-        <v>0.317</v>
+        <v>0.337</v>
       </c>
       <c r="AN2">
-        <v>-1.241025641025641</v>
+        <v>0.6585067319461444</v>
       </c>
       <c r="AO2">
-        <v>-22.03125</v>
+        <v>15.87392550143267</v>
       </c>
       <c r="AP2">
-        <v>-0.9435897435897436</v>
+        <v>-0.5777233782129743</v>
       </c>
       <c r="AQ2">
-        <v>-22.2397476340694</v>
+        <v>16.43916913946588</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.244</v>
+        <v>0.0116</v>
+      </c>
+      <c r="E3">
+        <v>-0.0355</v>
       </c>
       <c r="G3">
-        <v>-0.9409660107334525</v>
+        <v>-0.06680672268907563</v>
       </c>
       <c r="H3">
-        <v>-0.9409660107334525</v>
+        <v>-0.06680672268907563</v>
       </c>
       <c r="I3">
-        <v>-1.261180679785331</v>
+        <v>0.2327731092436975</v>
       </c>
       <c r="J3">
-        <v>-1.261180679785331</v>
+        <v>0.1748600563821034</v>
       </c>
       <c r="K3">
-        <v>-4.96</v>
+        <v>4.69</v>
       </c>
       <c r="L3">
-        <v>-0.8872987477638641</v>
+        <v>0.1970588235294118</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.16</v>
+        <v>10.1</v>
       </c>
       <c r="V3">
-        <v>0.02086330935251798</v>
+        <v>0.1856617647058824</v>
       </c>
       <c r="W3">
-        <v>-0.168135593220339</v>
+        <v>0.183203125</v>
       </c>
       <c r="X3">
-        <v>0.06776339866051559</v>
+        <v>0.1032251926646767</v>
       </c>
       <c r="Y3">
-        <v>-0.2358989918808546</v>
+        <v>0.07997793233532327</v>
       </c>
       <c r="Z3">
-        <v>0.2103876552502823</v>
+        <v>0.975809758097581</v>
       </c>
       <c r="AA3">
-        <v>-0.2653368460669928</v>
+        <v>0.1706301493191497</v>
       </c>
       <c r="AB3">
-        <v>0.06491162149224596</v>
+        <v>0.0990925570278279</v>
       </c>
       <c r="AC3">
-        <v>-0.3302484675592388</v>
+        <v>0.07153759229132176</v>
       </c>
       <c r="AD3">
-        <v>4.84</v>
+        <v>5.38</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.84</v>
+        <v>5.38</v>
       </c>
       <c r="AG3">
-        <v>3.68</v>
+        <v>-4.72</v>
       </c>
       <c r="AH3">
-        <v>0.08007941760423561</v>
+        <v>0.08999665439946471</v>
       </c>
       <c r="AI3">
-        <v>0.1590013140604468</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AJ3">
-        <v>0.06207827260458839</v>
+        <v>-0.09500805152979065</v>
       </c>
       <c r="AK3">
-        <v>0.1256830601092896</v>
+        <v>-0.2128043282236249</v>
       </c>
       <c r="AL3">
+        <v>0.349</v>
+      </c>
+      <c r="AM3">
+        <v>0.337</v>
+      </c>
+      <c r="AN3">
+        <v>0.6585067319461444</v>
+      </c>
+      <c r="AO3">
+        <v>15.87392550143267</v>
+      </c>
+      <c r="AP3">
+        <v>-0.5777233782129743</v>
+      </c>
+      <c r="AQ3">
+        <v>16.43916913946588</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chobe Holdings Limited (BSM:CHOBE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BSM:CHOBE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.08999665439946471</v>
+      </c>
+      <c r="F2">
+        <v>0.34</v>
+      </c>
+      <c r="G2">
+        <v>54.4</v>
+      </c>
+      <c r="H2">
+        <v>41.2246564315015</v>
+      </c>
+      <c r="I2">
+        <v>49.68</v>
+      </c>
+      <c r="J2">
+        <v>51.4498564315015</v>
+      </c>
+      <c r="K2">
+        <v>5.38</v>
+      </c>
+      <c r="L2">
+        <v>20.3252</v>
+      </c>
+      <c r="M2">
+        <v>0.0990925570278279</v>
+      </c>
+      <c r="N2">
+        <v>0.09553147194337409</v>
+      </c>
+      <c r="O2">
+        <v>0.0573053119266055</v>
+      </c>
+      <c r="P2">
+        <v>0.0429</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.103225192664677</v>
+      </c>
+      <c r="T2">
+        <v>0.122644654459658</v>
+      </c>
+      <c r="U2">
+        <v>0.806990053140864</v>
+      </c>
+      <c r="V2">
+        <v>1.05023825865987</v>
+      </c>
+      <c r="W2">
+        <v>4.61585528399139</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>54.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.07346834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>8.17</v>
+      </c>
+      <c r="AH2">
+        <v>3.01</v>
+      </c>
+      <c r="AI2">
+        <v>1.869000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>5.38</v>
+      </c>
+      <c r="AK2">
+        <v>5.38</v>
+      </c>
+      <c r="AL2">
+        <v>0.349</v>
+      </c>
+      <c r="AM2">
+        <v>5.38</v>
+      </c>
+      <c r="AN2">
+        <v>10.1</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09861136180650029</v>
+      </c>
+      <c r="C2">
+        <v>60.01200526736006</v>
+      </c>
+      <c r="D2">
+        <v>49.91200526736006</v>
+      </c>
+      <c r="E2">
+        <v>-5.38</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>10.1</v>
+      </c>
+      <c r="H2">
+        <v>54.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>8.17</v>
+      </c>
+      <c r="K2">
+        <v>3.01</v>
+      </c>
+      <c r="L2">
+        <v>5.16</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.16</v>
+      </c>
+      <c r="O2">
+        <v>1.1352</v>
+      </c>
+      <c r="P2">
+        <v>4.0248</v>
+      </c>
+      <c r="Q2">
+        <v>7.0348</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09861136180650029</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.098448236810526</v>
+      </c>
+      <c r="C3">
+        <v>59.49334755001259</v>
+      </c>
+      <c r="D3">
+        <v>49.99114755001258</v>
+      </c>
+      <c r="E3">
+        <v>-4.7822</v>
+      </c>
+      <c r="F3">
+        <v>0.5978</v>
+      </c>
+      <c r="G3">
+        <v>10.1</v>
+      </c>
+      <c r="H3">
+        <v>54.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>8.17</v>
+      </c>
+      <c r="K3">
+        <v>3.01</v>
+      </c>
+      <c r="L3">
+        <v>5.16</v>
+      </c>
+      <c r="M3">
+        <v>0.02731946</v>
+      </c>
+      <c r="N3">
+        <v>5.13268054</v>
+      </c>
+      <c r="O3">
+        <v>1.1291897188</v>
+      </c>
+      <c r="P3">
+        <v>4.0034908212</v>
+      </c>
+      <c r="Q3">
+        <v>7.0134908212</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09908260283891515</v>
+      </c>
+      <c r="T3">
+        <v>0.7550999672076776</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.035646</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>188.8763540714201</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09828511181455171</v>
+      </c>
+      <c r="C4">
+        <v>58.97494121300043</v>
+      </c>
+      <c r="D4">
+        <v>50.07054121300043</v>
+      </c>
+      <c r="E4">
+        <v>-4.1844</v>
+      </c>
+      <c r="F4">
+        <v>1.1956</v>
+      </c>
+      <c r="G4">
+        <v>10.1</v>
+      </c>
+      <c r="H4">
+        <v>54.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>8.17</v>
+      </c>
+      <c r="K4">
+        <v>3.01</v>
+      </c>
+      <c r="L4">
+        <v>5.16</v>
+      </c>
+      <c r="M4">
+        <v>0.05463892000000001</v>
+      </c>
+      <c r="N4">
+        <v>5.10536108</v>
+      </c>
+      <c r="O4">
+        <v>1.1231794376</v>
+      </c>
+      <c r="P4">
+        <v>3.9821816424</v>
+      </c>
+      <c r="Q4">
+        <v>6.9921816424</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09956346103525684</v>
+      </c>
+      <c r="T4">
+        <v>0.7611231976454774</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.035646</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>94.43817703571005</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09812198681857738</v>
+      </c>
+      <c r="C5">
+        <v>58.45678745592115</v>
+      </c>
+      <c r="D5">
+        <v>50.15018745592115</v>
+      </c>
+      <c r="E5">
+        <v>-3.5866</v>
+      </c>
+      <c r="F5">
+        <v>1.7934</v>
+      </c>
+      <c r="G5">
+        <v>10.1</v>
+      </c>
+      <c r="H5">
+        <v>54.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>8.17</v>
+      </c>
+      <c r="K5">
+        <v>3.01</v>
+      </c>
+      <c r="L5">
+        <v>5.16</v>
+      </c>
+      <c r="M5">
+        <v>0.08195838</v>
+      </c>
+      <c r="N5">
+        <v>5.07804162</v>
+      </c>
+      <c r="O5">
+        <v>1.1171691564</v>
+      </c>
+      <c r="P5">
+        <v>3.9608724636</v>
+      </c>
+      <c r="Q5">
+        <v>6.9708724636</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1000542338335849</v>
+      </c>
+      <c r="T5">
+        <v>0.7672706184015824</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.035646</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>62.95878469047339</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09795886182260309</v>
+      </c>
+      <c r="C6">
+        <v>57.9388874860171</v>
+      </c>
+      <c r="D6">
+        <v>50.2300874860171</v>
+      </c>
+      <c r="E6">
+        <v>-2.9888</v>
+      </c>
+      <c r="F6">
+        <v>2.3912</v>
+      </c>
+      <c r="G6">
+        <v>10.1</v>
+      </c>
+      <c r="H6">
+        <v>54.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>8.17</v>
+      </c>
+      <c r="K6">
+        <v>3.01</v>
+      </c>
+      <c r="L6">
+        <v>5.16</v>
+      </c>
+      <c r="M6">
+        <v>0.10927784</v>
+      </c>
+      <c r="N6">
+        <v>5.05072216</v>
+      </c>
+      <c r="O6">
+        <v>1.1111588752</v>
+      </c>
+      <c r="P6">
+        <v>3.9395632848</v>
+      </c>
+      <c r="Q6">
+        <v>6.9495632848</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1005552310652116</v>
+      </c>
+      <c r="T6">
+        <v>0.7735461104234395</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.035646</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>47.21908851785503</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0977957368266288</v>
+      </c>
+      <c r="C7">
+        <v>57.42124251823657</v>
+      </c>
+      <c r="D7">
+        <v>50.31024251823656</v>
+      </c>
+      <c r="E7">
+        <v>-2.391</v>
+      </c>
+      <c r="F7">
+        <v>2.989</v>
+      </c>
+      <c r="G7">
+        <v>10.1</v>
+      </c>
+      <c r="H7">
+        <v>54.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>8.17</v>
+      </c>
+      <c r="K7">
+        <v>3.01</v>
+      </c>
+      <c r="L7">
+        <v>5.16</v>
+      </c>
+      <c r="M7">
+        <v>0.1365973</v>
+      </c>
+      <c r="N7">
+        <v>5.0234027</v>
+      </c>
+      <c r="O7">
+        <v>1.105148594</v>
+      </c>
+      <c r="P7">
+        <v>3.918254106</v>
+      </c>
+      <c r="Q7">
+        <v>6.928254106</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1010667756069777</v>
+      </c>
+      <c r="T7">
+        <v>0.7799537180668095</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.035646</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>37.77527081428402</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.0976326118306545</v>
+      </c>
+      <c r="C8">
+        <v>56.90385377529527</v>
+      </c>
+      <c r="D8">
+        <v>50.39065377529526</v>
+      </c>
+      <c r="E8">
+        <v>-1.7932</v>
+      </c>
+      <c r="F8">
+        <v>3.5868</v>
+      </c>
+      <c r="G8">
+        <v>10.1</v>
+      </c>
+      <c r="H8">
+        <v>54.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>8.17</v>
+      </c>
+      <c r="K8">
+        <v>3.01</v>
+      </c>
+      <c r="L8">
+        <v>5.16</v>
+      </c>
+      <c r="M8">
+        <v>0.16391676</v>
+      </c>
+      <c r="N8">
+        <v>4.99608324</v>
+      </c>
+      <c r="O8">
+        <v>1.0991383128</v>
+      </c>
+      <c r="P8">
+        <v>3.8969449272</v>
+      </c>
+      <c r="Q8">
+        <v>6.9069449272</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1015892040751644</v>
+      </c>
+      <c r="T8">
+        <v>0.7864976577876978</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.035646</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>31.47939234523669</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09746948683468019</v>
+      </c>
+      <c r="C9">
+        <v>56.38672248773852</v>
+      </c>
+      <c r="D9">
+        <v>50.47132248773852</v>
+      </c>
+      <c r="E9">
+        <v>-1.195399999999999</v>
+      </c>
+      <c r="F9">
+        <v>4.184600000000001</v>
+      </c>
+      <c r="G9">
+        <v>10.1</v>
+      </c>
+      <c r="H9">
+        <v>54.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>8.17</v>
+      </c>
+      <c r="K9">
+        <v>3.01</v>
+      </c>
+      <c r="L9">
+        <v>5.16</v>
+      </c>
+      <c r="M9">
+        <v>0.19123622</v>
+      </c>
+      <c r="N9">
+        <v>4.96876378</v>
+      </c>
+      <c r="O9">
+        <v>1.0931280316</v>
+      </c>
+      <c r="P9">
+        <v>3.8756357484</v>
+      </c>
+      <c r="Q9">
+        <v>6.885635748399999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1021228675641723</v>
+      </c>
+      <c r="T9">
+        <v>0.793182327395057</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.035646</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>26.98233629591716</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09730636183870589</v>
+      </c>
+      <c r="C10">
+        <v>55.86984989400406</v>
+      </c>
+      <c r="D10">
+        <v>50.55224989400406</v>
+      </c>
+      <c r="E10">
+        <v>-0.5975999999999999</v>
+      </c>
+      <c r="F10">
+        <v>4.7824</v>
+      </c>
+      <c r="G10">
+        <v>10.1</v>
+      </c>
+      <c r="H10">
+        <v>54.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>8.17</v>
+      </c>
+      <c r="K10">
+        <v>3.01</v>
+      </c>
+      <c r="L10">
+        <v>5.16</v>
+      </c>
+      <c r="M10">
+        <v>0.21855568</v>
+      </c>
+      <c r="N10">
+        <v>4.94144432</v>
+      </c>
+      <c r="O10">
+        <v>1.0871177504</v>
+      </c>
+      <c r="P10">
+        <v>3.8543265696</v>
+      </c>
+      <c r="Q10">
+        <v>6.8643265696</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.102668132433376</v>
+      </c>
+      <c r="T10">
+        <v>0.8000123159069238</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.035646</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>23.60954425892752</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0971432368427316</v>
+      </c>
+      <c r="C11">
+        <v>55.35323724048533</v>
+      </c>
+      <c r="D11">
+        <v>50.63343724048533</v>
+      </c>
+      <c r="E11">
+        <v>0.0002000000000004221</v>
+      </c>
+      <c r="F11">
+        <v>5.3802</v>
+      </c>
+      <c r="G11">
+        <v>10.1</v>
+      </c>
+      <c r="H11">
+        <v>54.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>8.17</v>
+      </c>
+      <c r="K11">
+        <v>3.01</v>
+      </c>
+      <c r="L11">
+        <v>5.16</v>
+      </c>
+      <c r="M11">
+        <v>0.24587514</v>
+      </c>
+      <c r="N11">
+        <v>4.91412486</v>
+      </c>
+      <c r="O11">
+        <v>1.0811074692</v>
+      </c>
+      <c r="P11">
+        <v>3.8330173908</v>
+      </c>
+      <c r="Q11">
+        <v>6.8430173908</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1032253811458589</v>
+      </c>
+      <c r="T11">
+        <v>0.8069924140564142</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.035646</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>20.98626156349113</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0969801118467573</v>
+      </c>
+      <c r="C12">
+        <v>54.83688578159563</v>
+      </c>
+      <c r="D12">
+        <v>50.71488578159563</v>
+      </c>
+      <c r="E12">
+        <v>0.5980000000000008</v>
+      </c>
+      <c r="F12">
+        <v>5.978000000000001</v>
+      </c>
+      <c r="G12">
+        <v>10.1</v>
+      </c>
+      <c r="H12">
+        <v>54.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>8.17</v>
+      </c>
+      <c r="K12">
+        <v>3.01</v>
+      </c>
+      <c r="L12">
+        <v>5.16</v>
+      </c>
+      <c r="M12">
+        <v>0.2731946000000001</v>
+      </c>
+      <c r="N12">
+        <v>4.8868054</v>
+      </c>
+      <c r="O12">
+        <v>1.075097188</v>
+      </c>
+      <c r="P12">
+        <v>3.811708212</v>
+      </c>
+      <c r="Q12">
+        <v>6.821708212</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1037950131630637</v>
+      </c>
+      <c r="T12">
+        <v>0.8141276254981155</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.035646</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>18.88763540714201</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09681698685078299</v>
+      </c>
+      <c r="C13">
+        <v>54.32079677983252</v>
+      </c>
+      <c r="D13">
+        <v>50.79659677983252</v>
+      </c>
+      <c r="E13">
+        <v>1.1958</v>
+      </c>
+      <c r="F13">
+        <v>6.5758</v>
+      </c>
+      <c r="G13">
+        <v>10.1</v>
+      </c>
+      <c r="H13">
+        <v>54.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>8.17</v>
+      </c>
+      <c r="K13">
+        <v>3.01</v>
+      </c>
+      <c r="L13">
+        <v>5.16</v>
+      </c>
+      <c r="M13">
+        <v>0.30051406</v>
+      </c>
+      <c r="N13">
+        <v>4.85948594</v>
+      </c>
+      <c r="O13">
+        <v>1.0690869068</v>
+      </c>
+      <c r="P13">
+        <v>3.7903990332</v>
+      </c>
+      <c r="Q13">
+        <v>6.8003990332</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1043774458997562</v>
+      </c>
+      <c r="T13">
+        <v>0.8214231787699674</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.035646</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>17.17057764285638</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.0966538618548087</v>
+      </c>
+      <c r="C14">
+        <v>53.8049715058432</v>
+      </c>
+      <c r="D14">
+        <v>50.8785715058432</v>
+      </c>
+      <c r="E14">
+        <v>1.7936</v>
+      </c>
+      <c r="F14">
+        <v>7.1736</v>
+      </c>
+      <c r="G14">
+        <v>10.1</v>
+      </c>
+      <c r="H14">
+        <v>54.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>8.17</v>
+      </c>
+      <c r="K14">
+        <v>3.01</v>
+      </c>
+      <c r="L14">
+        <v>5.16</v>
+      </c>
+      <c r="M14">
+        <v>0.32783352</v>
+      </c>
+      <c r="N14">
+        <v>4.83216648</v>
+      </c>
+      <c r="O14">
+        <v>1.0630766256</v>
+      </c>
+      <c r="P14">
+        <v>3.7690898544</v>
+      </c>
+      <c r="Q14">
+        <v>6.7790898544</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1049731157441008</v>
+      </c>
+      <c r="T14">
+        <v>0.828884540070725</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.035646</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>15.73969617261834</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09649073685883439</v>
+      </c>
+      <c r="C15">
+        <v>53.28941123849035</v>
+      </c>
+      <c r="D15">
+        <v>50.96081123849034</v>
+      </c>
+      <c r="E15">
+        <v>2.391400000000001</v>
+      </c>
+      <c r="F15">
+        <v>7.771400000000001</v>
+      </c>
+      <c r="G15">
+        <v>10.1</v>
+      </c>
+      <c r="H15">
+        <v>54.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>8.17</v>
+      </c>
+      <c r="K15">
+        <v>3.01</v>
+      </c>
+      <c r="L15">
+        <v>5.16</v>
+      </c>
+      <c r="M15">
+        <v>0.3551529800000001</v>
+      </c>
+      <c r="N15">
+        <v>4.80484702</v>
+      </c>
+      <c r="O15">
+        <v>1.0570663444</v>
+      </c>
+      <c r="P15">
+        <v>3.7477806756</v>
+      </c>
+      <c r="Q15">
+        <v>6.7577806756</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1055824791480855</v>
+      </c>
+      <c r="T15">
+        <v>0.8365174269186264</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.035646</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>14.52895031318617</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09632761186286008</v>
+      </c>
+      <c r="C16">
+        <v>52.77411726491853</v>
+      </c>
+      <c r="D16">
+        <v>51.04331726491853</v>
+      </c>
+      <c r="E16">
+        <v>2.989200000000001</v>
+      </c>
+      <c r="F16">
+        <v>8.369200000000001</v>
+      </c>
+      <c r="G16">
+        <v>10.1</v>
+      </c>
+      <c r="H16">
+        <v>54.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>8.17</v>
+      </c>
+      <c r="K16">
+        <v>3.01</v>
+      </c>
+      <c r="L16">
+        <v>5.16</v>
+      </c>
+      <c r="M16">
+        <v>0.3824724400000001</v>
+      </c>
+      <c r="N16">
+        <v>4.77752756</v>
+      </c>
+      <c r="O16">
+        <v>1.0510560632</v>
+      </c>
+      <c r="P16">
+        <v>3.7264714968</v>
+      </c>
+      <c r="Q16">
+        <v>6.7364714968</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1062060137940234</v>
+      </c>
+      <c r="T16">
+        <v>0.8443278227629907</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.035646</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>13.49116814795858</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09635168686688579</v>
+      </c>
+      <c r="C17">
+        <v>52.16412371038819</v>
+      </c>
+      <c r="D17">
+        <v>51.03112371038819</v>
+      </c>
+      <c r="E17">
+        <v>3.587000000000001</v>
+      </c>
+      <c r="F17">
+        <v>8.967000000000001</v>
+      </c>
+      <c r="G17">
+        <v>10.1</v>
+      </c>
+      <c r="H17">
+        <v>54.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>8.17</v>
+      </c>
+      <c r="K17">
+        <v>3.01</v>
+      </c>
+      <c r="L17">
+        <v>5.16</v>
+      </c>
+      <c r="M17">
+        <v>0.4241391</v>
+      </c>
+      <c r="N17">
+        <v>4.7358609</v>
+      </c>
+      <c r="O17">
+        <v>1.041889398</v>
+      </c>
+      <c r="P17">
+        <v>3.693971502000001</v>
+      </c>
+      <c r="Q17">
+        <v>6.703971502</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1068442198433951</v>
+      </c>
+      <c r="T17">
+        <v>0.8523219926272223</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.036894</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>12.1658201283494</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09620104187091148</v>
+      </c>
+      <c r="C18">
+        <v>51.64271864635354</v>
+      </c>
+      <c r="D18">
+        <v>51.10751864635354</v>
+      </c>
+      <c r="E18">
+        <v>4.1848</v>
+      </c>
+      <c r="F18">
+        <v>9.5648</v>
+      </c>
+      <c r="G18">
+        <v>10.1</v>
+      </c>
+      <c r="H18">
+        <v>54.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>8.17</v>
+      </c>
+      <c r="K18">
+        <v>3.01</v>
+      </c>
+      <c r="L18">
+        <v>5.16</v>
+      </c>
+      <c r="M18">
+        <v>0.45241504</v>
+      </c>
+      <c r="N18">
+        <v>4.70758496</v>
+      </c>
+      <c r="O18">
+        <v>1.0356686912</v>
+      </c>
+      <c r="P18">
+        <v>3.6719162688</v>
+      </c>
+      <c r="Q18">
+        <v>6.6819162688</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1074976212748946</v>
+      </c>
+      <c r="T18">
+        <v>0.8605064998691738</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.036894</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>11.40545637032757</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09605039687493719</v>
+      </c>
+      <c r="C19">
+        <v>51.12154265570939</v>
+      </c>
+      <c r="D19">
+        <v>51.18414265570939</v>
+      </c>
+      <c r="E19">
+        <v>4.782600000000001</v>
+      </c>
+      <c r="F19">
+        <v>10.1626</v>
+      </c>
+      <c r="G19">
+        <v>10.1</v>
+      </c>
+      <c r="H19">
+        <v>54.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>8.17</v>
+      </c>
+      <c r="K19">
+        <v>3.01</v>
+      </c>
+      <c r="L19">
+        <v>5.16</v>
+      </c>
+      <c r="M19">
+        <v>0.4806909800000001</v>
+      </c>
+      <c r="N19">
+        <v>4.67930902</v>
+      </c>
+      <c r="O19">
+        <v>1.0294479844</v>
+      </c>
+      <c r="P19">
+        <v>3.6498610356</v>
+      </c>
+      <c r="Q19">
+        <v>6.6598610356</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1081667673192014</v>
+      </c>
+      <c r="T19">
+        <v>0.8688882241531001</v>
+      </c>
+      <c r="U19">
+        <v>0.0473</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.036894</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>10.734547172073</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09643327187896289</v>
+      </c>
+      <c r="C20">
+        <v>50.32944566303703</v>
+      </c>
+      <c r="D20">
+        <v>50.98984566303703</v>
+      </c>
+      <c r="E20">
+        <v>5.380400000000001</v>
+      </c>
+      <c r="F20">
+        <v>10.7604</v>
+      </c>
+      <c r="G20">
+        <v>10.1</v>
+      </c>
+      <c r="H20">
+        <v>54.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>8.17</v>
+      </c>
+      <c r="K20">
+        <v>3.01</v>
+      </c>
+      <c r="L20">
+        <v>5.16</v>
+      </c>
+      <c r="M20">
+        <v>0.54985644</v>
+      </c>
+      <c r="N20">
+        <v>4.61014356</v>
+      </c>
+      <c r="O20">
+        <v>1.0142315832</v>
+      </c>
+      <c r="P20">
+        <v>3.5959119768</v>
+      </c>
+      <c r="Q20">
+        <v>6.6059119768</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1088522339987352</v>
+      </c>
+      <c r="T20">
+        <v>0.8774743807366341</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.039858</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>9.384267646296914</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09631226688298859</v>
+      </c>
+      <c r="C21">
+        <v>49.79289226113362</v>
+      </c>
+      <c r="D21">
+        <v>51.05109226113361</v>
+      </c>
+      <c r="E21">
+        <v>5.9782</v>
+      </c>
+      <c r="F21">
+        <v>11.3582</v>
+      </c>
+      <c r="G21">
+        <v>10.1</v>
+      </c>
+      <c r="H21">
+        <v>54.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>8.17</v>
+      </c>
+      <c r="K21">
+        <v>3.01</v>
+      </c>
+      <c r="L21">
+        <v>5.16</v>
+      </c>
+      <c r="M21">
+        <v>0.58040402</v>
+      </c>
+      <c r="N21">
+        <v>4.579595980000001</v>
+      </c>
+      <c r="O21">
+        <v>1.0075111156</v>
+      </c>
+      <c r="P21">
+        <v>3.572084864400001</v>
+      </c>
+      <c r="Q21">
+        <v>6.582084864400001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1095546257814674</v>
+      </c>
+      <c r="T21">
+        <v>0.8862725411864284</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.039858</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.890358822807602</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.0961912618870143</v>
+      </c>
+      <c r="C22">
+        <v>49.2564861692229</v>
+      </c>
+      <c r="D22">
+        <v>51.1124861692229</v>
+      </c>
+      <c r="E22">
+        <v>6.576000000000001</v>
+      </c>
+      <c r="F22">
+        <v>11.956</v>
+      </c>
+      <c r="G22">
+        <v>10.1</v>
+      </c>
+      <c r="H22">
+        <v>54.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>8.17</v>
+      </c>
+      <c r="K22">
+        <v>3.01</v>
+      </c>
+      <c r="L22">
+        <v>5.16</v>
+      </c>
+      <c r="M22">
+        <v>0.6109516</v>
+      </c>
+      <c r="N22">
+        <v>4.5490484</v>
+      </c>
+      <c r="O22">
+        <v>1.000790648</v>
+      </c>
+      <c r="P22">
+        <v>3.548257752</v>
+      </c>
+      <c r="Q22">
+        <v>6.558257752</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1102745773587679</v>
+      </c>
+      <c r="T22">
+        <v>0.8952906556474676</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.039858</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.445840881667223</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09607025689103998</v>
+      </c>
+      <c r="C23">
+        <v>48.72022791940861</v>
+      </c>
+      <c r="D23">
+        <v>51.17402791940862</v>
+      </c>
+      <c r="E23">
+        <v>7.173799999999999</v>
+      </c>
+      <c r="F23">
+        <v>12.5538</v>
+      </c>
+      <c r="G23">
+        <v>10.1</v>
+      </c>
+      <c r="H23">
+        <v>54.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>8.17</v>
+      </c>
+      <c r="K23">
+        <v>3.01</v>
+      </c>
+      <c r="L23">
+        <v>5.16</v>
+      </c>
+      <c r="M23">
+        <v>0.6414991799999999</v>
+      </c>
+      <c r="N23">
+        <v>4.51850082</v>
+      </c>
+      <c r="O23">
+        <v>0.9940701803999998</v>
+      </c>
+      <c r="P23">
+        <v>3.5244306396</v>
+      </c>
+      <c r="Q23">
+        <v>6.5344306396</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1110127555582785</v>
+      </c>
+      <c r="T23">
+        <v>0.9045370768037228</v>
+      </c>
+      <c r="U23">
+        <v>0.0511</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.039858</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.043657982540211</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.0962752918950657</v>
+      </c>
+      <c r="C24">
+        <v>48.01823648576698</v>
+      </c>
+      <c r="D24">
+        <v>51.06983648576698</v>
+      </c>
+      <c r="E24">
+        <v>7.7716</v>
+      </c>
+      <c r="F24">
+        <v>13.1516</v>
+      </c>
+      <c r="G24">
+        <v>10.1</v>
+      </c>
+      <c r="H24">
+        <v>54.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>8.17</v>
+      </c>
+      <c r="K24">
+        <v>3.01</v>
+      </c>
+      <c r="L24">
+        <v>5.16</v>
+      </c>
+      <c r="M24">
+        <v>0.6970348000000001</v>
+      </c>
+      <c r="N24">
+        <v>4.4629652</v>
+      </c>
+      <c r="O24">
+        <v>0.9818523439999999</v>
+      </c>
+      <c r="P24">
+        <v>3.481112856</v>
+      </c>
+      <c r="Q24">
+        <v>6.491112856</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1117698614039304</v>
+      </c>
+      <c r="T24">
+        <v>0.9140205856819333</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>7.402786776212608</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.0961691068990914</v>
+      </c>
+      <c r="C25">
+        <v>47.47434286941058</v>
+      </c>
+      <c r="D25">
+        <v>51.12374286941058</v>
+      </c>
+      <c r="E25">
+        <v>8.369400000000002</v>
+      </c>
+      <c r="F25">
+        <v>13.7494</v>
+      </c>
+      <c r="G25">
+        <v>10.1</v>
+      </c>
+      <c r="H25">
+        <v>54.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>8.17</v>
+      </c>
+      <c r="K25">
+        <v>3.01</v>
+      </c>
+      <c r="L25">
+        <v>5.16</v>
+      </c>
+      <c r="M25">
+        <v>0.7287182000000001</v>
+      </c>
+      <c r="N25">
+        <v>4.4312818</v>
+      </c>
+      <c r="O25">
+        <v>0.9748819959999998</v>
+      </c>
+      <c r="P25">
+        <v>3.456399804</v>
+      </c>
+      <c r="Q25">
+        <v>6.466399804</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1125466323364823</v>
+      </c>
+      <c r="T25">
+        <v>0.9237504194660715</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.080926481594668</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09606292190311709</v>
+      </c>
+      <c r="C26">
+        <v>46.93056317426241</v>
+      </c>
+      <c r="D26">
+        <v>51.17776317426241</v>
+      </c>
+      <c r="E26">
+        <v>8.967199999999998</v>
+      </c>
+      <c r="F26">
+        <v>14.3472</v>
+      </c>
+      <c r="G26">
+        <v>10.1</v>
+      </c>
+      <c r="H26">
+        <v>54.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>8.17</v>
+      </c>
+      <c r="K26">
+        <v>3.01</v>
+      </c>
+      <c r="L26">
+        <v>5.16</v>
+      </c>
+      <c r="M26">
+        <v>0.7604016</v>
+      </c>
+      <c r="N26">
+        <v>4.3995984</v>
+      </c>
+      <c r="O26">
+        <v>0.967911648</v>
+      </c>
+      <c r="P26">
+        <v>3.431686752000001</v>
+      </c>
+      <c r="Q26">
+        <v>6.441686752000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1133438446093646</v>
+      </c>
+      <c r="T26">
+        <v>0.9337363015076869</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.785887878194891</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09595673690714278</v>
+      </c>
+      <c r="C27">
+        <v>46.38689776183166</v>
+      </c>
+      <c r="D27">
+        <v>51.23189776183166</v>
+      </c>
+      <c r="E27">
+        <v>9.565000000000001</v>
+      </c>
+      <c r="F27">
+        <v>14.945</v>
+      </c>
+      <c r="G27">
+        <v>10.1</v>
+      </c>
+      <c r="H27">
+        <v>54.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>8.17</v>
+      </c>
+      <c r="K27">
+        <v>3.01</v>
+      </c>
+      <c r="L27">
+        <v>5.16</v>
+      </c>
+      <c r="M27">
+        <v>0.7920850000000002</v>
+      </c>
+      <c r="N27">
+        <v>4.367915</v>
+      </c>
+      <c r="O27">
+        <v>0.9609412999999999</v>
+      </c>
+      <c r="P27">
+        <v>3.4069737</v>
+      </c>
+      <c r="Q27">
+        <v>6.4169737</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1141623158761904</v>
+      </c>
+      <c r="T27">
+        <v>0.9439884737370787</v>
+      </c>
+      <c r="U27">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.514452363067094</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09585055191116849</v>
+      </c>
+      <c r="C28">
+        <v>45.84334699515873</v>
+      </c>
+      <c r="D28">
+        <v>51.28614699515873</v>
+      </c>
+      <c r="E28">
+        <v>10.1628</v>
+      </c>
+      <c r="F28">
+        <v>15.5428</v>
+      </c>
+      <c r="G28">
+        <v>10.1</v>
+      </c>
+      <c r="H28">
+        <v>54.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>8.17</v>
+      </c>
+      <c r="K28">
+        <v>3.01</v>
+      </c>
+      <c r="L28">
+        <v>5.16</v>
+      </c>
+      <c r="M28">
+        <v>0.8237684000000002</v>
+      </c>
+      <c r="N28">
+        <v>4.3362316</v>
+      </c>
+      <c r="O28">
+        <v>0.9539709519999998</v>
+      </c>
+      <c r="P28">
+        <v>3.382260648</v>
+      </c>
+      <c r="Q28">
+        <v>6.392260648</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1150029079880655</v>
+      </c>
+      <c r="T28">
+        <v>0.9545177317024001</v>
+      </c>
+      <c r="U28">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.263896502949128</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09616556691519418</v>
+      </c>
+      <c r="C29">
+        <v>45.08494195484215</v>
+      </c>
+      <c r="D29">
+        <v>51.12554195484215</v>
+      </c>
+      <c r="E29">
+        <v>10.7606</v>
+      </c>
+      <c r="F29">
+        <v>16.1406</v>
+      </c>
+      <c r="G29">
+        <v>10.1</v>
+      </c>
+      <c r="H29">
+        <v>54.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>8.17</v>
+      </c>
+      <c r="K29">
+        <v>3.01</v>
+      </c>
+      <c r="L29">
+        <v>5.16</v>
+      </c>
+      <c r="M29">
+        <v>0.8877330000000001</v>
+      </c>
+      <c r="N29">
+        <v>4.272267</v>
+      </c>
+      <c r="O29">
+        <v>0.93989874</v>
+      </c>
+      <c r="P29">
+        <v>3.33236826</v>
+      </c>
+      <c r="Q29">
+        <v>6.342368260000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1158665300208139</v>
+      </c>
+      <c r="T29">
+        <v>0.9653354624886891</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.0429</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.812558505766936</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.0960749819192199</v>
+      </c>
+      <c r="C30">
+        <v>44.53322204406211</v>
+      </c>
+      <c r="D30">
+        <v>51.17162204406211</v>
+      </c>
+      <c r="E30">
+        <v>11.3584</v>
+      </c>
+      <c r="F30">
+        <v>16.7384</v>
+      </c>
+      <c r="G30">
+        <v>10.1</v>
+      </c>
+      <c r="H30">
+        <v>54.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>8.17</v>
+      </c>
+      <c r="K30">
+        <v>3.01</v>
+      </c>
+      <c r="L30">
+        <v>5.16</v>
+      </c>
+      <c r="M30">
+        <v>0.9206120000000001</v>
+      </c>
+      <c r="N30">
+        <v>4.239388</v>
+      </c>
+      <c r="O30">
+        <v>0.9326653599999999</v>
+      </c>
+      <c r="P30">
+        <v>3.30672264</v>
+      </c>
+      <c r="Q30">
+        <v>6.31672264</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1167541415544721</v>
+      </c>
+      <c r="T30">
+        <v>0.9764536857968196</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.0429</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.604967130560974</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09598439692324558</v>
+      </c>
+      <c r="C31">
+        <v>43.98158527333664</v>
+      </c>
+      <c r="D31">
+        <v>51.21778527333664</v>
+      </c>
+      <c r="E31">
+        <v>11.9562</v>
+      </c>
+      <c r="F31">
+        <v>17.3362</v>
+      </c>
+      <c r="G31">
+        <v>10.1</v>
+      </c>
+      <c r="H31">
+        <v>54.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>8.17</v>
+      </c>
+      <c r="K31">
+        <v>3.01</v>
+      </c>
+      <c r="L31">
+        <v>5.16</v>
+      </c>
+      <c r="M31">
+        <v>0.9534909999999999</v>
+      </c>
+      <c r="N31">
+        <v>4.206509</v>
+      </c>
+      <c r="O31">
+        <v>0.92543198</v>
+      </c>
+      <c r="P31">
+        <v>3.281077020000001</v>
+      </c>
+      <c r="Q31">
+        <v>6.29107702</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1176667562299234</v>
+      </c>
+      <c r="T31">
+        <v>0.9878850984939114</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.0429</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.411692401920942</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09589381192727128</v>
+      </c>
+      <c r="C32">
+        <v>43.43003186787716</v>
+      </c>
+      <c r="D32">
+        <v>51.26403186787716</v>
+      </c>
+      <c r="E32">
+        <v>12.554</v>
+      </c>
+      <c r="F32">
+        <v>17.934</v>
+      </c>
+      <c r="G32">
+        <v>10.1</v>
+      </c>
+      <c r="H32">
+        <v>54.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>8.17</v>
+      </c>
+      <c r="K32">
+        <v>3.01</v>
+      </c>
+      <c r="L32">
+        <v>5.16</v>
+      </c>
+      <c r="M32">
+        <v>0.9863700000000001</v>
+      </c>
+      <c r="N32">
+        <v>4.17363</v>
+      </c>
+      <c r="O32">
+        <v>0.9181986</v>
+      </c>
+      <c r="P32">
+        <v>3.2554314</v>
+      </c>
+      <c r="Q32">
+        <v>6.2654314</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1186054456103875</v>
+      </c>
+      <c r="T32">
+        <v>0.9996431229823487</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.0429</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.231302655190243</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09580322693129699</v>
+      </c>
+      <c r="C33">
+        <v>42.87856205370932</v>
+      </c>
+      <c r="D33">
+        <v>51.31036205370931</v>
+      </c>
+      <c r="E33">
+        <v>13.1518</v>
+      </c>
+      <c r="F33">
+        <v>18.5318</v>
+      </c>
+      <c r="G33">
+        <v>10.1</v>
+      </c>
+      <c r="H33">
+        <v>54.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>8.17</v>
+      </c>
+      <c r="K33">
+        <v>3.01</v>
+      </c>
+      <c r="L33">
+        <v>5.16</v>
+      </c>
+      <c r="M33">
+        <v>1.019249</v>
+      </c>
+      <c r="N33">
+        <v>4.140751</v>
+      </c>
+      <c r="O33">
+        <v>0.9109652199999999</v>
+      </c>
+      <c r="P33">
+        <v>3.22978578</v>
+      </c>
+      <c r="Q33">
+        <v>6.23978578</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1195713433786913</v>
+      </c>
+      <c r="T33">
+        <v>1.011741959774799</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.0429</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.062550956635719</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
         <v>0.32</v>
       </c>
-      <c r="AM3">
-        <v>0.317</v>
-      </c>
-      <c r="AN3">
-        <v>-1.241025641025641</v>
-      </c>
-      <c r="AO3">
-        <v>-22.03125</v>
-      </c>
-      <c r="AP3">
-        <v>-0.9435897435897436</v>
-      </c>
-      <c r="AQ3">
-        <v>-22.2397476340694</v>
+      <c r="B34">
+        <v>0.09571264193532268</v>
+      </c>
+      <c r="C34">
+        <v>42.32717605767658</v>
+      </c>
+      <c r="D34">
+        <v>51.35677605767658</v>
+      </c>
+      <c r="E34">
+        <v>13.7496</v>
+      </c>
+      <c r="F34">
+        <v>19.1296</v>
+      </c>
+      <c r="G34">
+        <v>10.1</v>
+      </c>
+      <c r="H34">
+        <v>54.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>8.17</v>
+      </c>
+      <c r="K34">
+        <v>3.01</v>
+      </c>
+      <c r="L34">
+        <v>5.16</v>
+      </c>
+      <c r="M34">
+        <v>1.052128</v>
+      </c>
+      <c r="N34">
+        <v>4.107872</v>
+      </c>
+      <c r="O34">
+        <v>0.90373184</v>
+      </c>
+      <c r="P34">
+        <v>3.204140160000001</v>
+      </c>
+      <c r="Q34">
+        <v>6.21414016</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1205656499048863</v>
+      </c>
+      <c r="T34">
+        <v>1.024196644708203</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.0429</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.904346239240853</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09562205693934837</v>
+      </c>
+      <c r="C35">
+        <v>41.77587410744389</v>
+      </c>
+      <c r="D35">
+        <v>51.40327410744389</v>
+      </c>
+      <c r="E35">
+        <v>14.3474</v>
+      </c>
+      <c r="F35">
+        <v>19.7274</v>
+      </c>
+      <c r="G35">
+        <v>10.1</v>
+      </c>
+      <c r="H35">
+        <v>54.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>8.17</v>
+      </c>
+      <c r="K35">
+        <v>3.01</v>
+      </c>
+      <c r="L35">
+        <v>5.16</v>
+      </c>
+      <c r="M35">
+        <v>1.085007</v>
+      </c>
+      <c r="N35">
+        <v>4.074993</v>
+      </c>
+      <c r="O35">
+        <v>0.8964984599999999</v>
+      </c>
+      <c r="P35">
+        <v>3.17849454</v>
+      </c>
+      <c r="Q35">
+        <v>6.18849454</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.121589637222908</v>
+      </c>
+      <c r="T35">
+        <v>1.037023111281411</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.0429</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.755729686536584</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09553147194337408</v>
+      </c>
+      <c r="C36">
+        <v>41.22465643150151</v>
+      </c>
+      <c r="D36">
+        <v>51.44985643150151</v>
+      </c>
+      <c r="E36">
+        <v>14.9452</v>
+      </c>
+      <c r="F36">
+        <v>20.3252</v>
+      </c>
+      <c r="G36">
+        <v>10.1</v>
+      </c>
+      <c r="H36">
+        <v>54.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>8.17</v>
+      </c>
+      <c r="K36">
+        <v>3.01</v>
+      </c>
+      <c r="L36">
+        <v>5.16</v>
+      </c>
+      <c r="M36">
+        <v>1.117886</v>
+      </c>
+      <c r="N36">
+        <v>4.042114</v>
+      </c>
+      <c r="O36">
+        <v>0.8892650799999998</v>
+      </c>
+      <c r="P36">
+        <v>3.15284892</v>
+      </c>
+      <c r="Q36">
+        <v>6.16284892</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1226446544596577</v>
+      </c>
+      <c r="T36">
+        <v>1.050238258659867</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.0429</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.61585528399139</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09647828694739978</v>
+      </c>
+      <c r="C37">
+        <v>40.14409880282017</v>
+      </c>
+      <c r="D37">
+        <v>50.96709880282017</v>
+      </c>
+      <c r="E37">
+        <v>15.543</v>
+      </c>
+      <c r="F37">
+        <v>20.923</v>
+      </c>
+      <c r="G37">
+        <v>10.1</v>
+      </c>
+      <c r="H37">
+        <v>54.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>8.17</v>
+      </c>
+      <c r="K37">
+        <v>3.01</v>
+      </c>
+      <c r="L37">
+        <v>5.16</v>
+      </c>
+      <c r="M37">
+        <v>1.2302724</v>
+      </c>
+      <c r="N37">
+        <v>3.9297276</v>
+      </c>
+      <c r="O37">
+        <v>0.8645400719999998</v>
+      </c>
+      <c r="P37">
+        <v>3.065187528</v>
+      </c>
+      <c r="Q37">
+        <v>6.075187528</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1237321337652304</v>
+      </c>
+      <c r="T37">
+        <v>1.06386002595766</v>
+      </c>
+      <c r="U37">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.194193090895967</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09641734195142548</v>
+      </c>
+      <c r="C38">
+        <v>39.5771001841816</v>
+      </c>
+      <c r="D38">
+        <v>50.9979001841816</v>
+      </c>
+      <c r="E38">
+        <v>16.1408</v>
+      </c>
+      <c r="F38">
+        <v>21.5208</v>
+      </c>
+      <c r="G38">
+        <v>10.1</v>
+      </c>
+      <c r="H38">
+        <v>54.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>8.17</v>
+      </c>
+      <c r="K38">
+        <v>3.01</v>
+      </c>
+      <c r="L38">
+        <v>5.16</v>
+      </c>
+      <c r="M38">
+        <v>1.26542304</v>
+      </c>
+      <c r="N38">
+        <v>3.89457696</v>
+      </c>
+      <c r="O38">
+        <v>0.8568069312</v>
+      </c>
+      <c r="P38">
+        <v>3.0377700288</v>
+      </c>
+      <c r="Q38">
+        <v>6.0477700288</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1248535967991023</v>
+      </c>
+      <c r="T38">
+        <v>1.077907473483509</v>
+      </c>
+      <c r="U38">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.077687727259969</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09756851695545118</v>
+      </c>
+      <c r="C39">
+        <v>38.40371925348162</v>
+      </c>
+      <c r="D39">
+        <v>50.42231925348162</v>
+      </c>
+      <c r="E39">
+        <v>16.7386</v>
+      </c>
+      <c r="F39">
+        <v>22.1186</v>
+      </c>
+      <c r="G39">
+        <v>10.1</v>
+      </c>
+      <c r="H39">
+        <v>54.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>8.17</v>
+      </c>
+      <c r="K39">
+        <v>3.01</v>
+      </c>
+      <c r="L39">
+        <v>5.16</v>
+      </c>
+      <c r="M39">
+        <v>1.3934718</v>
+      </c>
+      <c r="N39">
+        <v>3.7665282</v>
+      </c>
+      <c r="O39">
+        <v>0.8286362039999998</v>
+      </c>
+      <c r="P39">
+        <v>2.937891996</v>
+      </c>
+      <c r="Q39">
+        <v>5.947891995999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1260106618340495</v>
+      </c>
+      <c r="T39">
+        <v>1.092400871724465</v>
+      </c>
+      <c r="U39">
+        <v>0.063</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.04914</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.702981287457701</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09754033195947688</v>
+      </c>
+      <c r="C40">
+        <v>37.81985639058752</v>
+      </c>
+      <c r="D40">
+        <v>50.43625639058752</v>
+      </c>
+      <c r="E40">
+        <v>17.3364</v>
+      </c>
+      <c r="F40">
+        <v>22.7164</v>
+      </c>
+      <c r="G40">
+        <v>10.1</v>
+      </c>
+      <c r="H40">
+        <v>54.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>8.17</v>
+      </c>
+      <c r="K40">
+        <v>3.01</v>
+      </c>
+      <c r="L40">
+        <v>5.16</v>
+      </c>
+      <c r="M40">
+        <v>1.4311332</v>
+      </c>
+      <c r="N40">
+        <v>3.7288668</v>
+      </c>
+      <c r="O40">
+        <v>0.8203506959999999</v>
+      </c>
+      <c r="P40">
+        <v>2.908516104</v>
+      </c>
+      <c r="Q40">
+        <v>5.918516104</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1272050515475434</v>
+      </c>
+      <c r="T40">
+        <v>1.107361798940936</v>
+      </c>
+      <c r="U40">
+        <v>0.063</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.04914</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.605534411471972</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09751214696350258</v>
+      </c>
+      <c r="C41">
+        <v>37.23600123449861</v>
+      </c>
+      <c r="D41">
+        <v>50.45020123449861</v>
+      </c>
+      <c r="E41">
+        <v>17.9342</v>
+      </c>
+      <c r="F41">
+        <v>23.3142</v>
+      </c>
+      <c r="G41">
+        <v>10.1</v>
+      </c>
+      <c r="H41">
+        <v>54.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>8.17</v>
+      </c>
+      <c r="K41">
+        <v>3.01</v>
+      </c>
+      <c r="L41">
+        <v>5.16</v>
+      </c>
+      <c r="M41">
+        <v>1.4687946</v>
+      </c>
+      <c r="N41">
+        <v>3.6912054</v>
+      </c>
+      <c r="O41">
+        <v>0.8120651879999999</v>
+      </c>
+      <c r="P41">
+        <v>2.879140212</v>
+      </c>
+      <c r="Q41">
+        <v>5.889140212</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1284386015795124</v>
+      </c>
+      <c r="T41">
+        <v>1.122813248361225</v>
+      </c>
+      <c r="U41">
+        <v>0.063</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.04914</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.513084811177819</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09969916196752826</v>
+      </c>
+      <c r="C42">
+        <v>35.57858460433496</v>
+      </c>
+      <c r="D42">
+        <v>49.39058460433496</v>
+      </c>
+      <c r="E42">
+        <v>18.532</v>
+      </c>
+      <c r="F42">
+        <v>23.912</v>
+      </c>
+      <c r="G42">
+        <v>10.1</v>
+      </c>
+      <c r="H42">
+        <v>54.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>8.17</v>
+      </c>
+      <c r="K42">
+        <v>3.01</v>
+      </c>
+      <c r="L42">
+        <v>5.16</v>
+      </c>
+      <c r="M42">
+        <v>1.6762312</v>
+      </c>
+      <c r="N42">
+        <v>3.4837688</v>
+      </c>
+      <c r="O42">
+        <v>0.766429136</v>
+      </c>
+      <c r="P42">
+        <v>2.717339664</v>
+      </c>
+      <c r="Q42">
+        <v>5.727339664</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1297132699458804</v>
+      </c>
+      <c r="T42">
+        <v>1.138779746095524</v>
+      </c>
+      <c r="U42">
+        <v>0.0701</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.054678</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.078334301377996</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09972635697155398</v>
+      </c>
+      <c r="C43">
+        <v>34.96788863521444</v>
+      </c>
+      <c r="D43">
+        <v>49.37768863521444</v>
+      </c>
+      <c r="E43">
+        <v>19.1298</v>
+      </c>
+      <c r="F43">
+        <v>24.5098</v>
+      </c>
+      <c r="G43">
+        <v>10.1</v>
+      </c>
+      <c r="H43">
+        <v>54.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>8.17</v>
+      </c>
+      <c r="K43">
+        <v>3.01</v>
+      </c>
+      <c r="L43">
+        <v>5.16</v>
+      </c>
+      <c r="M43">
+        <v>1.71813698</v>
+      </c>
+      <c r="N43">
+        <v>3.44186302</v>
+      </c>
+      <c r="O43">
+        <v>0.7572098644</v>
+      </c>
+      <c r="P43">
+        <v>2.6846531556</v>
+      </c>
+      <c r="Q43">
+        <v>5.6946531556</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1310311474094135</v>
+      </c>
+      <c r="T43">
+        <v>1.155287481041154</v>
+      </c>
+      <c r="U43">
+        <v>0.0701</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.054678</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.003252976954143</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1067314319755797</v>
+      </c>
+      <c r="C44">
+        <v>31.2584046998085</v>
+      </c>
+      <c r="D44">
+        <v>46.2660046998085</v>
+      </c>
+      <c r="E44">
+        <v>19.7276</v>
+      </c>
+      <c r="F44">
+        <v>25.1076</v>
+      </c>
+      <c r="G44">
+        <v>10.1</v>
+      </c>
+      <c r="H44">
+        <v>54.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>8.17</v>
+      </c>
+      <c r="K44">
+        <v>3.01</v>
+      </c>
+      <c r="L44">
+        <v>5.16</v>
+      </c>
+      <c r="M44">
+        <v>2.29483464</v>
+      </c>
+      <c r="N44">
+        <v>2.86516536</v>
+      </c>
+      <c r="O44">
+        <v>0.6303363792</v>
+      </c>
+      <c r="P44">
+        <v>2.2348289808</v>
+      </c>
+      <c r="Q44">
+        <v>5.244828980799999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1323944689234132</v>
+      </c>
+      <c r="T44">
+        <v>1.17236444822629</v>
+      </c>
+      <c r="U44">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.248528024659764</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1069247669796054</v>
+      </c>
+      <c r="C45">
+        <v>30.58027618647378</v>
+      </c>
+      <c r="D45">
+        <v>46.18567618647378</v>
+      </c>
+      <c r="E45">
+        <v>20.3254</v>
+      </c>
+      <c r="F45">
+        <v>25.7054</v>
+      </c>
+      <c r="G45">
+        <v>10.1</v>
+      </c>
+      <c r="H45">
+        <v>54.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>8.17</v>
+      </c>
+      <c r="K45">
+        <v>3.01</v>
+      </c>
+      <c r="L45">
+        <v>5.16</v>
+      </c>
+      <c r="M45">
+        <v>2.34947356</v>
+      </c>
+      <c r="N45">
+        <v>2.81052644</v>
+      </c>
+      <c r="O45">
+        <v>0.6183158167999999</v>
+      </c>
+      <c r="P45">
+        <v>2.1922106232</v>
+      </c>
+      <c r="Q45">
+        <v>5.202210623199999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1338056262800094</v>
+      </c>
+      <c r="T45">
+        <v>1.190040607242483</v>
+      </c>
+      <c r="U45">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.196236675249072</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1071181019836311</v>
+      </c>
+      <c r="C46">
+        <v>29.90242612753262</v>
+      </c>
+      <c r="D46">
+        <v>46.10562612753262</v>
+      </c>
+      <c r="E46">
+        <v>20.9232</v>
+      </c>
+      <c r="F46">
+        <v>26.3032</v>
+      </c>
+      <c r="G46">
+        <v>10.1</v>
+      </c>
+      <c r="H46">
+        <v>54.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>8.17</v>
+      </c>
+      <c r="K46">
+        <v>3.01</v>
+      </c>
+      <c r="L46">
+        <v>5.16</v>
+      </c>
+      <c r="M46">
+        <v>2.40411248</v>
+      </c>
+      <c r="N46">
+        <v>2.75588752</v>
+      </c>
+      <c r="O46">
+        <v>0.6062952543999999</v>
+      </c>
+      <c r="P46">
+        <v>2.1495922656</v>
+      </c>
+      <c r="Q46">
+        <v>5.1595922656</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1352671821136269</v>
+      </c>
+      <c r="T46">
+        <v>1.208348057652111</v>
+      </c>
+      <c r="U46">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.146322205357047</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1073114369876568</v>
+      </c>
+      <c r="C47">
+        <v>29.22485307761982</v>
+      </c>
+      <c r="D47">
+        <v>46.02585307761981</v>
+      </c>
+      <c r="E47">
+        <v>21.521</v>
+      </c>
+      <c r="F47">
+        <v>26.901</v>
+      </c>
+      <c r="G47">
+        <v>10.1</v>
+      </c>
+      <c r="H47">
+        <v>54.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>8.17</v>
+      </c>
+      <c r="K47">
+        <v>3.01</v>
+      </c>
+      <c r="L47">
+        <v>5.16</v>
+      </c>
+      <c r="M47">
+        <v>2.4587514</v>
+      </c>
+      <c r="N47">
+        <v>2.7012486</v>
+      </c>
+      <c r="O47">
+        <v>0.5942746919999999</v>
+      </c>
+      <c r="P47">
+        <v>2.106973908</v>
+      </c>
+      <c r="Q47">
+        <v>5.116973908</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1367818854321032</v>
+      </c>
+      <c r="T47">
+        <v>1.22732123353118</v>
+      </c>
+      <c r="U47">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.098626156349113</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1075047719916825</v>
+      </c>
+      <c r="C48">
+        <v>28.54755560135608</v>
+      </c>
+      <c r="D48">
+        <v>45.94635560135608</v>
+      </c>
+      <c r="E48">
+        <v>22.1188</v>
+      </c>
+      <c r="F48">
+        <v>27.4988</v>
+      </c>
+      <c r="G48">
+        <v>10.1</v>
+      </c>
+      <c r="H48">
+        <v>54.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>8.17</v>
+      </c>
+      <c r="K48">
+        <v>3.01</v>
+      </c>
+      <c r="L48">
+        <v>5.16</v>
+      </c>
+      <c r="M48">
+        <v>2.513390320000001</v>
+      </c>
+      <c r="N48">
+        <v>2.64660968</v>
+      </c>
+      <c r="O48">
+        <v>0.5822541295999999</v>
+      </c>
+      <c r="P48">
+        <v>2.0643555504</v>
+      </c>
+      <c r="Q48">
+        <v>5.0743555504</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1383526888734861</v>
+      </c>
+      <c r="T48">
+        <v>1.246997119627993</v>
+      </c>
+      <c r="U48">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.053003848602393</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1076981069957082</v>
+      </c>
+      <c r="C49">
+        <v>27.87053227326198</v>
+      </c>
+      <c r="D49">
+        <v>45.86713227326198</v>
+      </c>
+      <c r="E49">
+        <v>22.7166</v>
+      </c>
+      <c r="F49">
+        <v>28.0966</v>
+      </c>
+      <c r="G49">
+        <v>10.1</v>
+      </c>
+      <c r="H49">
+        <v>54.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>8.17</v>
+      </c>
+      <c r="K49">
+        <v>3.01</v>
+      </c>
+      <c r="L49">
+        <v>5.16</v>
+      </c>
+      <c r="M49">
+        <v>2.56802924</v>
+      </c>
+      <c r="N49">
+        <v>2.59197076</v>
+      </c>
+      <c r="O49">
+        <v>0.5702335671999998</v>
+      </c>
+      <c r="P49">
+        <v>2.0217371928</v>
+      </c>
+      <c r="Q49">
+        <v>5.0317371928</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1399827679164305</v>
+      </c>
+      <c r="T49">
+        <v>1.26741549199261</v>
+      </c>
+      <c r="U49">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.009322915653406</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1157912819997339</v>
+      </c>
+      <c r="C50">
+        <v>24.18496349533453</v>
+      </c>
+      <c r="D50">
+        <v>42.77936349533453</v>
+      </c>
+      <c r="E50">
+        <v>23.3144</v>
+      </c>
+      <c r="F50">
+        <v>28.6944</v>
+      </c>
+      <c r="G50">
+        <v>10.1</v>
+      </c>
+      <c r="H50">
+        <v>54.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>8.17</v>
+      </c>
+      <c r="K50">
+        <v>3.01</v>
+      </c>
+      <c r="L50">
+        <v>5.16</v>
+      </c>
+      <c r="M50">
+        <v>3.22812</v>
+      </c>
+      <c r="N50">
+        <v>1.93188</v>
+      </c>
+      <c r="O50">
+        <v>0.4250136</v>
+      </c>
+      <c r="P50">
+        <v>1.5068664</v>
+      </c>
+      <c r="Q50">
+        <v>4.516866400000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1416755423071805</v>
+      </c>
+      <c r="T50">
+        <v>1.28861918637125</v>
+      </c>
+      <c r="U50">
+        <v>0.1125</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.598453589085908</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1161491970037596</v>
+      </c>
+      <c r="C51">
+        <v>23.46017995645275</v>
+      </c>
+      <c r="D51">
+        <v>42.65237995645275</v>
+      </c>
+      <c r="E51">
+        <v>23.9122</v>
+      </c>
+      <c r="F51">
+        <v>29.2922</v>
+      </c>
+      <c r="G51">
+        <v>10.1</v>
+      </c>
+      <c r="H51">
+        <v>54.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>8.17</v>
+      </c>
+      <c r="K51">
+        <v>3.01</v>
+      </c>
+      <c r="L51">
+        <v>5.16</v>
+      </c>
+      <c r="M51">
+        <v>3.2953725</v>
+      </c>
+      <c r="N51">
+        <v>1.8646275</v>
+      </c>
+      <c r="O51">
+        <v>0.41021805</v>
+      </c>
+      <c r="P51">
+        <v>1.45440945</v>
+      </c>
+      <c r="Q51">
+        <v>4.46440945</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1434347000073717</v>
+      </c>
+      <c r="T51">
+        <v>1.310654398176504</v>
+      </c>
+      <c r="U51">
+        <v>0.1125</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.565832087267828</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1165071120077853</v>
+      </c>
+      <c r="C52">
+        <v>22.73614804618825</v>
+      </c>
+      <c r="D52">
+        <v>42.52614804618825</v>
+      </c>
+      <c r="E52">
+        <v>24.51</v>
+      </c>
+      <c r="F52">
+        <v>29.89</v>
+      </c>
+      <c r="G52">
+        <v>10.1</v>
+      </c>
+      <c r="H52">
+        <v>54.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>8.17</v>
+      </c>
+      <c r="K52">
+        <v>3.01</v>
+      </c>
+      <c r="L52">
+        <v>5.16</v>
+      </c>
+      <c r="M52">
+        <v>3.362625</v>
+      </c>
+      <c r="N52">
+        <v>1.797375</v>
+      </c>
+      <c r="O52">
+        <v>0.3954225</v>
+      </c>
+      <c r="P52">
+        <v>1.4019525</v>
+      </c>
+      <c r="Q52">
+        <v>4.4119525</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1452642240155705</v>
+      </c>
+      <c r="T52">
+        <v>1.333571018453968</v>
+      </c>
+      <c r="U52">
+        <v>0.1125</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.534515445522471</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.116865027011811</v>
+      </c>
+      <c r="C53">
+        <v>22.01286111078262</v>
+      </c>
+      <c r="D53">
+        <v>42.40066111078261</v>
+      </c>
+      <c r="E53">
+        <v>25.1078</v>
+      </c>
+      <c r="F53">
+        <v>30.4878</v>
+      </c>
+      <c r="G53">
+        <v>10.1</v>
+      </c>
+      <c r="H53">
+        <v>54.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>8.17</v>
+      </c>
+      <c r="K53">
+        <v>3.01</v>
+      </c>
+      <c r="L53">
+        <v>5.16</v>
+      </c>
+      <c r="M53">
+        <v>3.4298775</v>
+      </c>
+      <c r="N53">
+        <v>1.7301225</v>
+      </c>
+      <c r="O53">
+        <v>0.38062695</v>
+      </c>
+      <c r="P53">
+        <v>1.34949555</v>
+      </c>
+      <c r="Q53">
+        <v>4.35949555</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1471684224730836</v>
+      </c>
+      <c r="T53">
+        <v>1.357423010987655</v>
+      </c>
+      <c r="U53">
+        <v>0.1125</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.504426907374972</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1559005431932927</v>
+      </c>
+      <c r="C54">
+        <v>11.09171483514772</v>
+      </c>
+      <c r="D54">
+        <v>32.07731483514772</v>
+      </c>
+      <c r="E54">
+        <v>25.7056</v>
+      </c>
+      <c r="F54">
+        <v>31.0856</v>
+      </c>
+      <c r="G54">
+        <v>10.1</v>
+      </c>
+      <c r="H54">
+        <v>54.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>8.17</v>
+      </c>
+      <c r="K54">
+        <v>3.01</v>
+      </c>
+      <c r="L54">
+        <v>5.16</v>
+      </c>
+      <c r="M54">
+        <v>6.11142896</v>
+      </c>
+      <c r="N54">
+        <v>-0.9514289600000003</v>
+      </c>
+      <c r="O54">
+        <v>-0.2093143712</v>
+      </c>
+      <c r="P54">
+        <v>-0.7421145888000003</v>
+      </c>
+      <c r="Q54">
+        <v>2.2678854112</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1513711913159025</v>
+      </c>
+      <c r="T54">
+        <v>1.410066899372405</v>
+      </c>
+      <c r="U54">
+        <v>0.1966</v>
+      </c>
+      <c r="V54">
+        <v>0.1857503388209228</v>
+      </c>
+      <c r="W54">
+        <v>0.1600814833878066</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.8443197219132855</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1574785431932926</v>
+      </c>
+      <c r="C55">
+        <v>10.18127853406138</v>
+      </c>
+      <c r="D55">
+        <v>31.76467853406138</v>
+      </c>
+      <c r="E55">
+        <v>26.3034</v>
+      </c>
+      <c r="F55">
+        <v>31.6834</v>
+      </c>
+      <c r="G55">
+        <v>10.1</v>
+      </c>
+      <c r="H55">
+        <v>54.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>8.17</v>
+      </c>
+      <c r="K55">
+        <v>3.01</v>
+      </c>
+      <c r="L55">
+        <v>5.16</v>
+      </c>
+      <c r="M55">
+        <v>6.22895644</v>
+      </c>
+      <c r="N55">
+        <v>-1.06895644</v>
+      </c>
+      <c r="O55">
+        <v>-0.2351704168</v>
+      </c>
+      <c r="P55">
+        <v>-0.8337860232000001</v>
+      </c>
+      <c r="Q55">
+        <v>2.1762139768</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1537663230460281</v>
+      </c>
+      <c r="T55">
+        <v>1.440068322763307</v>
+      </c>
+      <c r="U55">
+        <v>0.1966</v>
+      </c>
+      <c r="V55">
+        <v>0.1822456154469431</v>
+      </c>
+      <c r="W55">
+        <v>0.160770512003131</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8283891611224689</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1590565431932927</v>
+      </c>
+      <c r="C56">
+        <v>9.276877528079098</v>
+      </c>
+      <c r="D56">
+        <v>31.45807752807911</v>
+      </c>
+      <c r="E56">
+        <v>26.90120000000001</v>
+      </c>
+      <c r="F56">
+        <v>32.28120000000001</v>
+      </c>
+      <c r="G56">
+        <v>10.1</v>
+      </c>
+      <c r="H56">
+        <v>54.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>8.17</v>
+      </c>
+      <c r="K56">
+        <v>3.01</v>
+      </c>
+      <c r="L56">
+        <v>5.16</v>
+      </c>
+      <c r="M56">
+        <v>6.346483920000001</v>
+      </c>
+      <c r="N56">
+        <v>-1.186483920000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.2610264624000001</v>
+      </c>
+      <c r="P56">
+        <v>-0.9254574576000005</v>
+      </c>
+      <c r="Q56">
+        <v>2.084542542399999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1562655909383331</v>
+      </c>
+      <c r="T56">
+        <v>1.471374155866857</v>
+      </c>
+      <c r="U56">
+        <v>0.1966</v>
+      </c>
+      <c r="V56">
+        <v>0.1788706966423701</v>
+      </c>
+      <c r="W56">
+        <v>0.16143402104011</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8130486211016823</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1705593124522623</v>
+      </c>
+      <c r="C57">
+        <v>6.611190000147744</v>
+      </c>
+      <c r="D57">
+        <v>29.39019000014775</v>
+      </c>
+      <c r="E57">
+        <v>27.49900000000001</v>
+      </c>
+      <c r="F57">
+        <v>32.879</v>
+      </c>
+      <c r="G57">
+        <v>10.1</v>
+      </c>
+      <c r="H57">
+        <v>54.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>8.17</v>
+      </c>
+      <c r="K57">
+        <v>3.01</v>
+      </c>
+      <c r="L57">
+        <v>5.16</v>
+      </c>
+      <c r="M57">
+        <v>7.029530200000001</v>
+      </c>
+      <c r="N57">
+        <v>-1.869530200000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.4112966440000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.458233556000001</v>
+      </c>
+      <c r="Q57">
+        <v>1.551766443999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1599087579791175</v>
+      </c>
+      <c r="T57">
+        <v>1.517008471299113</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1614901661564808</v>
+      </c>
+      <c r="W57">
+        <v>0.1792734024757444</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.7340462098021856</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1723093124522623</v>
+      </c>
+      <c r="C58">
+        <v>5.722377867805875</v>
+      </c>
+      <c r="D58">
+        <v>29.09917786780588</v>
+      </c>
+      <c r="E58">
+        <v>28.09680000000001</v>
+      </c>
+      <c r="F58">
+        <v>33.4768</v>
+      </c>
+      <c r="G58">
+        <v>10.1</v>
+      </c>
+      <c r="H58">
+        <v>54.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>8.17</v>
+      </c>
+      <c r="K58">
+        <v>3.01</v>
+      </c>
+      <c r="L58">
+        <v>5.16</v>
+      </c>
+      <c r="M58">
+        <v>7.157339840000001</v>
+      </c>
+      <c r="N58">
+        <v>-1.99733984</v>
+      </c>
+      <c r="O58">
+        <v>-0.4394147648</v>
+      </c>
+      <c r="P58">
+        <v>-1.5579250752</v>
+      </c>
+      <c r="Q58">
+        <v>1.452074924799999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1626612297513702</v>
+      </c>
+      <c r="T58">
+        <v>1.551485936555911</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1586064131894008</v>
+      </c>
+      <c r="W58">
+        <v>0.1798899488601061</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.7209382417700037</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1740593124522623</v>
+      </c>
+      <c r="C59">
+        <v>4.839272246998959</v>
+      </c>
+      <c r="D59">
+        <v>28.81387224699896</v>
+      </c>
+      <c r="E59">
+        <v>28.6946</v>
+      </c>
+      <c r="F59">
+        <v>34.0746</v>
+      </c>
+      <c r="G59">
+        <v>10.1</v>
+      </c>
+      <c r="H59">
+        <v>54.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>8.17</v>
+      </c>
+      <c r="K59">
+        <v>3.01</v>
+      </c>
+      <c r="L59">
+        <v>5.16</v>
+      </c>
+      <c r="M59">
+        <v>7.28514948</v>
+      </c>
+      <c r="N59">
+        <v>-2.12514948</v>
+      </c>
+      <c r="O59">
+        <v>-0.4675328855999999</v>
+      </c>
+      <c r="P59">
+        <v>-1.6576165944</v>
+      </c>
+      <c r="Q59">
+        <v>1.352383405599999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1655417234665184</v>
+      </c>
+      <c r="T59">
+        <v>1.587567004847908</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1558238445369552</v>
+      </c>
+      <c r="W59">
+        <v>0.180484862037999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.7082902024407054</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1758093124522623</v>
+      </c>
+      <c r="C60">
+        <v>3.961706917366165</v>
+      </c>
+      <c r="D60">
+        <v>28.53410691736616</v>
+      </c>
+      <c r="E60">
+        <v>29.2924</v>
+      </c>
+      <c r="F60">
+        <v>34.6724</v>
+      </c>
+      <c r="G60">
+        <v>10.1</v>
+      </c>
+      <c r="H60">
+        <v>54.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>8.17</v>
+      </c>
+      <c r="K60">
+        <v>3.01</v>
+      </c>
+      <c r="L60">
+        <v>5.16</v>
+      </c>
+      <c r="M60">
+        <v>7.412959119999999</v>
+      </c>
+      <c r="N60">
+        <v>-2.252959119999999</v>
+      </c>
+      <c r="O60">
+        <v>-0.4956510063999997</v>
+      </c>
+      <c r="P60">
+        <v>-1.757308113599999</v>
+      </c>
+      <c r="Q60">
+        <v>1.252691886400001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1685593835490545</v>
+      </c>
+      <c r="T60">
+        <v>1.625366219249049</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1531372265276974</v>
+      </c>
+      <c r="W60">
+        <v>0.1810592609683783</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6960783023986243</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1775593124522623</v>
+      </c>
+      <c r="C61">
+        <v>3.089522052067423</v>
+      </c>
+      <c r="D61">
+        <v>28.25972205206742</v>
+      </c>
+      <c r="E61">
+        <v>29.8902</v>
+      </c>
+      <c r="F61">
+        <v>35.2702</v>
+      </c>
+      <c r="G61">
+        <v>10.1</v>
+      </c>
+      <c r="H61">
+        <v>54.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>8.17</v>
+      </c>
+      <c r="K61">
+        <v>3.01</v>
+      </c>
+      <c r="L61">
+        <v>5.16</v>
+      </c>
+      <c r="M61">
+        <v>7.540768759999999</v>
+      </c>
+      <c r="N61">
+        <v>-2.380768759999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.5237691271999997</v>
+      </c>
+      <c r="P61">
+        <v>-1.856999632799999</v>
+      </c>
+      <c r="Q61">
+        <v>1.153000367200001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.171724246562446</v>
+      </c>
+      <c r="T61">
+        <v>1.665009297767318</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1505416803153635</v>
+      </c>
+      <c r="W61">
+        <v>0.1816141887485753</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.6842803650698341</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1793093124522623</v>
+      </c>
+      <c r="C62">
+        <v>2.222563913309791</v>
+      </c>
+      <c r="D62">
+        <v>27.9905639133098</v>
+      </c>
+      <c r="E62">
+        <v>30.488</v>
+      </c>
+      <c r="F62">
+        <v>35.868</v>
+      </c>
+      <c r="G62">
+        <v>10.1</v>
+      </c>
+      <c r="H62">
+        <v>54.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>8.17</v>
+      </c>
+      <c r="K62">
+        <v>3.01</v>
+      </c>
+      <c r="L62">
+        <v>5.16</v>
+      </c>
+      <c r="M62">
+        <v>7.6685784</v>
+      </c>
+      <c r="N62">
+        <v>-2.5085784</v>
+      </c>
+      <c r="O62">
+        <v>-0.551887248</v>
+      </c>
+      <c r="P62">
+        <v>-1.956691152</v>
+      </c>
+      <c r="Q62">
+        <v>1.053308847999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1750473527265072</v>
+      </c>
+      <c r="T62">
+        <v>1.706634530211501</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1480326523101074</v>
+      </c>
+      <c r="W62">
+        <v>0.182150618936099</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.6728756923186702</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1810593124522623</v>
+      </c>
+      <c r="C63">
+        <v>1.360684565109317</v>
+      </c>
+      <c r="D63">
+        <v>27.72648456510932</v>
+      </c>
+      <c r="E63">
+        <v>31.0858</v>
+      </c>
+      <c r="F63">
+        <v>36.4658</v>
+      </c>
+      <c r="G63">
+        <v>10.1</v>
+      </c>
+      <c r="H63">
+        <v>54.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>8.17</v>
+      </c>
+      <c r="K63">
+        <v>3.01</v>
+      </c>
+      <c r="L63">
+        <v>5.16</v>
+      </c>
+      <c r="M63">
+        <v>7.79638804</v>
+      </c>
+      <c r="N63">
+        <v>-2.63638804</v>
+      </c>
+      <c r="O63">
+        <v>-0.5800053687999999</v>
+      </c>
+      <c r="P63">
+        <v>-2.0563826712</v>
+      </c>
+      <c r="Q63">
+        <v>0.9536173287999996</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1785408745912894</v>
+      </c>
+      <c r="T63">
+        <v>1.750394389960514</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1456058875181385</v>
+      </c>
+      <c r="W63">
+        <v>0.182669461248622</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6618449432642657</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1828093124522623</v>
+      </c>
+      <c r="C64">
+        <v>0.503741602160666</v>
+      </c>
+      <c r="D64">
+        <v>27.46734160216067</v>
+      </c>
+      <c r="E64">
+        <v>31.6836</v>
+      </c>
+      <c r="F64">
+        <v>37.0636</v>
+      </c>
+      <c r="G64">
+        <v>10.1</v>
+      </c>
+      <c r="H64">
+        <v>54.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>8.17</v>
+      </c>
+      <c r="K64">
+        <v>3.01</v>
+      </c>
+      <c r="L64">
+        <v>5.16</v>
+      </c>
+      <c r="M64">
+        <v>7.92419768</v>
+      </c>
+      <c r="N64">
+        <v>-2.76419768</v>
+      </c>
+      <c r="O64">
+        <v>-0.6081234895999998</v>
+      </c>
+      <c r="P64">
+        <v>-2.1560741904</v>
+      </c>
+      <c r="Q64">
+        <v>0.8539258095999998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1822182660279023</v>
+      </c>
+      <c r="T64">
+        <v>1.796457400222633</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1432574054613943</v>
+      </c>
+      <c r="W64">
+        <v>0.1831715667123539</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.6511700248245196</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1845593124522623</v>
+      </c>
+      <c r="C65">
+        <v>-0.3484021062293081</v>
+      </c>
+      <c r="D65">
+        <v>27.21299789377069</v>
+      </c>
+      <c r="E65">
+        <v>32.2814</v>
+      </c>
+      <c r="F65">
+        <v>37.6614</v>
+      </c>
+      <c r="G65">
+        <v>10.1</v>
+      </c>
+      <c r="H65">
+        <v>54.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>8.17</v>
+      </c>
+      <c r="K65">
+        <v>3.01</v>
+      </c>
+      <c r="L65">
+        <v>5.16</v>
+      </c>
+      <c r="M65">
+        <v>8.05200732</v>
+      </c>
+      <c r="N65">
+        <v>-2.892007319999999</v>
+      </c>
+      <c r="O65">
+        <v>-0.6362416103999998</v>
+      </c>
+      <c r="P65">
+        <v>-2.255765709599999</v>
+      </c>
+      <c r="Q65">
+        <v>0.7542342904000003</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1860944353800078</v>
+      </c>
+      <c r="T65">
+        <v>1.845010302931353</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.1409834783905785</v>
+      </c>
+      <c r="W65">
+        <v>0.1836577323200943</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.6408339926844479</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1863093124522623</v>
+      </c>
+      <c r="C66">
+        <v>-1.195878658111809</v>
+      </c>
+      <c r="D66">
+        <v>26.96332134188819</v>
+      </c>
+      <c r="E66">
+        <v>32.8792</v>
+      </c>
+      <c r="F66">
+        <v>38.2592</v>
+      </c>
+      <c r="G66">
+        <v>10.1</v>
+      </c>
+      <c r="H66">
+        <v>54.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>8.17</v>
+      </c>
+      <c r="K66">
+        <v>3.01</v>
+      </c>
+      <c r="L66">
+        <v>5.16</v>
+      </c>
+      <c r="M66">
+        <v>8.17981696</v>
+      </c>
+      <c r="N66">
+        <v>-3.01981696</v>
+      </c>
+      <c r="O66">
+        <v>-0.6643597311999999</v>
+      </c>
+      <c r="P66">
+        <v>-2.3554572288</v>
+      </c>
+      <c r="Q66">
+        <v>0.6545427711999996</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1901859474738969</v>
+      </c>
+      <c r="T66">
+        <v>1.896260589123891</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.1387806115407257</v>
+      </c>
+      <c r="W66">
+        <v>0.1841287052525928</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.6308209615487532</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1880593124522623</v>
+      </c>
+      <c r="C67">
+        <v>-2.038815347667111</v>
+      </c>
+      <c r="D67">
+        <v>26.71818465233289</v>
+      </c>
+      <c r="E67">
+        <v>33.477</v>
+      </c>
+      <c r="F67">
+        <v>38.857</v>
+      </c>
+      <c r="G67">
+        <v>10.1</v>
+      </c>
+      <c r="H67">
+        <v>54.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>8.17</v>
+      </c>
+      <c r="K67">
+        <v>3.01</v>
+      </c>
+      <c r="L67">
+        <v>5.16</v>
+      </c>
+      <c r="M67">
+        <v>8.307626599999999</v>
+      </c>
+      <c r="N67">
+        <v>-3.147626599999999</v>
+      </c>
+      <c r="O67">
+        <v>-0.6924778519999997</v>
+      </c>
+      <c r="P67">
+        <v>-2.455148747999999</v>
+      </c>
+      <c r="Q67">
+        <v>0.5548512520000006</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1945112602588654</v>
+      </c>
+      <c r="T67">
+        <v>1.950439463098859</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.13664552520933</v>
+      </c>
+      <c r="W67">
+        <v>0.1845851867102453</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.6211160236787725</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1898093124522623</v>
+      </c>
+      <c r="C68">
+        <v>-2.877334881608768</v>
+      </c>
+      <c r="D68">
+        <v>26.47746511839124</v>
+      </c>
+      <c r="E68">
+        <v>34.0748</v>
+      </c>
+      <c r="F68">
+        <v>39.45480000000001</v>
+      </c>
+      <c r="G68">
+        <v>10.1</v>
+      </c>
+      <c r="H68">
+        <v>54.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>8.17</v>
+      </c>
+      <c r="K68">
+        <v>3.01</v>
+      </c>
+      <c r="L68">
+        <v>5.16</v>
+      </c>
+      <c r="M68">
+        <v>8.435436240000001</v>
+      </c>
+      <c r="N68">
+        <v>-3.275436240000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.7205959728000002</v>
+      </c>
+      <c r="P68">
+        <v>-2.554840267200001</v>
+      </c>
+      <c r="Q68">
+        <v>0.4551597327999986</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1990910032076555</v>
+      </c>
+      <c r="T68">
+        <v>2.00780532966059</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.134575138463734</v>
+      </c>
+      <c r="W68">
+        <v>0.1850278353964536</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.6117051748351546</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1915593124522623</v>
+      </c>
+      <c r="C69">
+        <v>-3.71155558399402</v>
+      </c>
+      <c r="D69">
+        <v>26.24104441600599</v>
+      </c>
+      <c r="E69">
+        <v>34.6726</v>
+      </c>
+      <c r="F69">
+        <v>40.05260000000001</v>
+      </c>
+      <c r="G69">
+        <v>10.1</v>
+      </c>
+      <c r="H69">
+        <v>54.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>8.17</v>
+      </c>
+      <c r="K69">
+        <v>3.01</v>
+      </c>
+      <c r="L69">
+        <v>5.16</v>
+      </c>
+      <c r="M69">
+        <v>8.56324588</v>
+      </c>
+      <c r="N69">
+        <v>-3.40324588</v>
+      </c>
+      <c r="O69">
+        <v>-0.7487140936</v>
+      </c>
+      <c r="P69">
+        <v>-2.6545317864</v>
+      </c>
+      <c r="Q69">
+        <v>0.3554682135999996</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2039483063351603</v>
+      </c>
+      <c r="T69">
+        <v>2.068647915407881</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.1325665543075589</v>
+      </c>
+      <c r="W69">
+        <v>0.1854572706890439</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.6025752468525405</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1933093124522623</v>
+      </c>
+      <c r="C70">
+        <v>-4.541591590158625</v>
+      </c>
+      <c r="D70">
+        <v>26.00880840984138</v>
+      </c>
+      <c r="E70">
+        <v>35.2704</v>
+      </c>
+      <c r="F70">
+        <v>40.6504</v>
+      </c>
+      <c r="G70">
+        <v>10.1</v>
+      </c>
+      <c r="H70">
+        <v>54.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>8.17</v>
+      </c>
+      <c r="K70">
+        <v>3.01</v>
+      </c>
+      <c r="L70">
+        <v>5.16</v>
+      </c>
+      <c r="M70">
+        <v>8.691055520000001</v>
+      </c>
+      <c r="N70">
+        <v>-3.531055520000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.7768322144000001</v>
+      </c>
+      <c r="P70">
+        <v>-2.754223305600001</v>
+      </c>
+      <c r="Q70">
+        <v>0.2557766943999993</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.209109190908134</v>
+      </c>
+      <c r="T70">
+        <v>2.133293162764377</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.1306170461559771</v>
+      </c>
+      <c r="W70">
+        <v>0.1858740755318521</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5937138461635325</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1950593124522623</v>
+      </c>
+      <c r="C71">
+        <v>-5.367553030444043</v>
+      </c>
+      <c r="D71">
+        <v>25.78064696955596</v>
+      </c>
+      <c r="E71">
+        <v>35.8682</v>
+      </c>
+      <c r="F71">
+        <v>41.2482</v>
+      </c>
+      <c r="G71">
+        <v>10.1</v>
+      </c>
+      <c r="H71">
+        <v>54.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>8.17</v>
+      </c>
+      <c r="K71">
+        <v>3.01</v>
+      </c>
+      <c r="L71">
+        <v>5.16</v>
+      </c>
+      <c r="M71">
+        <v>8.81886516</v>
+      </c>
+      <c r="N71">
+        <v>-3.65886516</v>
+      </c>
+      <c r="O71">
+        <v>-0.8049503351999998</v>
+      </c>
+      <c r="P71">
+        <v>-2.853914824799999</v>
+      </c>
+      <c r="Q71">
+        <v>0.1560851752000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2146030357761383</v>
+      </c>
+      <c r="T71">
+        <v>2.202109071240647</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1287240454870499</v>
+      </c>
+      <c r="W71">
+        <v>0.1862787990748687</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5851092976684089</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1968093124522623</v>
+      </c>
+      <c r="C72">
+        <v>-6.189546204338143</v>
+      </c>
+      <c r="D72">
+        <v>25.55645379566186</v>
+      </c>
+      <c r="E72">
+        <v>36.466</v>
+      </c>
+      <c r="F72">
+        <v>41.846</v>
+      </c>
+      <c r="G72">
+        <v>10.1</v>
+      </c>
+      <c r="H72">
+        <v>54.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>8.17</v>
+      </c>
+      <c r="K72">
+        <v>3.01</v>
+      </c>
+      <c r="L72">
+        <v>5.16</v>
+      </c>
+      <c r="M72">
+        <v>8.9466748</v>
+      </c>
+      <c r="N72">
+        <v>-3.7866748</v>
+      </c>
+      <c r="O72">
+        <v>-0.8330684559999999</v>
+      </c>
+      <c r="P72">
+        <v>-2.953606344</v>
+      </c>
+      <c r="Q72">
+        <v>0.05639365599999957</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2204631369686763</v>
+      </c>
+      <c r="T72">
+        <v>2.275512706948669</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.1268851305515206</v>
+      </c>
+      <c r="W72">
+        <v>0.1866719590880849</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.576750593416003</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1985593124522623</v>
+      </c>
+      <c r="C73">
+        <v>-7.007673745608187</v>
+      </c>
+      <c r="D73">
+        <v>25.33612625439181</v>
+      </c>
+      <c r="E73">
+        <v>37.06379999999999</v>
+      </c>
+      <c r="F73">
+        <v>42.4438</v>
+      </c>
+      <c r="G73">
+        <v>10.1</v>
+      </c>
+      <c r="H73">
+        <v>54.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>8.17</v>
+      </c>
+      <c r="K73">
+        <v>3.01</v>
+      </c>
+      <c r="L73">
+        <v>5.16</v>
+      </c>
+      <c r="M73">
+        <v>9.074484439999999</v>
+      </c>
+      <c r="N73">
+        <v>-3.914484439999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.8611865767999997</v>
+      </c>
+      <c r="P73">
+        <v>-3.053297863199999</v>
+      </c>
+      <c r="Q73">
+        <v>-0.0432978631999994</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2267273830710444</v>
+      </c>
+      <c r="T73">
+        <v>2.353978662360691</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.1250980160367105</v>
+      </c>
+      <c r="W73">
+        <v>0.1870540441713513</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5686273456214115</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2003093124522623</v>
+      </c>
+      <c r="C74">
+        <v>-7.822034778964991</v>
+      </c>
+      <c r="D74">
+        <v>25.11956522103501</v>
+      </c>
+      <c r="E74">
+        <v>37.6616</v>
+      </c>
+      <c r="F74">
+        <v>43.0416</v>
+      </c>
+      <c r="G74">
+        <v>10.1</v>
+      </c>
+      <c r="H74">
+        <v>54.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>8.17</v>
+      </c>
+      <c r="K74">
+        <v>3.01</v>
+      </c>
+      <c r="L74">
+        <v>5.16</v>
+      </c>
+      <c r="M74">
+        <v>9.20229408</v>
+      </c>
+      <c r="N74">
+        <v>-4.04229408</v>
+      </c>
+      <c r="O74">
+        <v>-0.8893046975999997</v>
+      </c>
+      <c r="P74">
+        <v>-3.1529893824</v>
+      </c>
+      <c r="Q74">
+        <v>-0.1429893824000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2334390753235817</v>
+      </c>
+      <c r="T74">
+        <v>2.438049328873574</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1233605435917562</v>
+      </c>
+      <c r="W74">
+        <v>0.1874255157800825</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5607297435988918</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2020593124522623</v>
+      </c>
+      <c r="C75">
+        <v>-8.632725068760408</v>
+      </c>
+      <c r="D75">
+        <v>24.9066749312396</v>
+      </c>
+      <c r="E75">
+        <v>38.2594</v>
+      </c>
+      <c r="F75">
+        <v>43.6394</v>
+      </c>
+      <c r="G75">
+        <v>10.1</v>
+      </c>
+      <c r="H75">
+        <v>54.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>8.17</v>
+      </c>
+      <c r="K75">
+        <v>3.01</v>
+      </c>
+      <c r="L75">
+        <v>5.16</v>
+      </c>
+      <c r="M75">
+        <v>9.33010372</v>
+      </c>
+      <c r="N75">
+        <v>-4.17010372</v>
+      </c>
+      <c r="O75">
+        <v>-0.9174228184</v>
+      </c>
+      <c r="P75">
+        <v>-3.2526809016</v>
+      </c>
+      <c r="Q75">
+        <v>-0.2426809016000004</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2406479299651959</v>
+      </c>
+      <c r="T75">
+        <v>2.528347452165187</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1216706731315951</v>
+      </c>
+      <c r="W75">
+        <v>0.187786810084465</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5530485142345234</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2038093124522623</v>
+      </c>
+      <c r="C76">
+        <v>-9.439837160187359</v>
+      </c>
+      <c r="D76">
+        <v>24.69736283981264</v>
+      </c>
+      <c r="E76">
+        <v>38.8572</v>
+      </c>
+      <c r="F76">
+        <v>44.2372</v>
+      </c>
+      <c r="G76">
+        <v>10.1</v>
+      </c>
+      <c r="H76">
+        <v>54.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>8.17</v>
+      </c>
+      <c r="K76">
+        <v>3.01</v>
+      </c>
+      <c r="L76">
+        <v>5.16</v>
+      </c>
+      <c r="M76">
+        <v>9.457913359999999</v>
+      </c>
+      <c r="N76">
+        <v>-4.297913359999999</v>
+      </c>
+      <c r="O76">
+        <v>-0.9455409391999997</v>
+      </c>
+      <c r="P76">
+        <v>-3.352372420799999</v>
+      </c>
+      <c r="Q76">
+        <v>-0.3423724207999994</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2484113118869342</v>
+      </c>
+      <c r="T76">
+        <v>2.625591584940771</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.120026474846033</v>
+      </c>
+      <c r="W76">
+        <v>0.1881383396779181</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5455748856637868</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2055593124522623</v>
+      </c>
+      <c r="C77">
+        <v>-10.24346051341914</v>
+      </c>
+      <c r="D77">
+        <v>24.49153948658086</v>
+      </c>
+      <c r="E77">
+        <v>39.455</v>
+      </c>
+      <c r="F77">
+        <v>44.835</v>
+      </c>
+      <c r="G77">
+        <v>10.1</v>
+      </c>
+      <c r="H77">
+        <v>54.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>8.17</v>
+      </c>
+      <c r="K77">
+        <v>3.01</v>
+      </c>
+      <c r="L77">
+        <v>5.16</v>
+      </c>
+      <c r="M77">
+        <v>9.585723</v>
+      </c>
+      <c r="N77">
+        <v>-4.425723</v>
+      </c>
+      <c r="O77">
+        <v>-0.9736590599999998</v>
+      </c>
+      <c r="P77">
+        <v>-3.45206394</v>
+      </c>
+      <c r="Q77">
+        <v>-0.4420639400000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2567957643624115</v>
+      </c>
+      <c r="T77">
+        <v>2.730615248338402</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.1184261218480859</v>
+      </c>
+      <c r="W77">
+        <v>0.1884804951488792</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5383005538549361</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2073093124522623</v>
+      </c>
+      <c r="C78">
+        <v>-11.04368163109704</v>
+      </c>
+      <c r="D78">
+        <v>24.28911836890295</v>
+      </c>
+      <c r="E78">
+        <v>40.0528</v>
+      </c>
+      <c r="F78">
+        <v>45.4328</v>
+      </c>
+      <c r="G78">
+        <v>10.1</v>
+      </c>
+      <c r="H78">
+        <v>54.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>8.17</v>
+      </c>
+      <c r="K78">
+        <v>3.01</v>
+      </c>
+      <c r="L78">
+        <v>5.16</v>
+      </c>
+      <c r="M78">
+        <v>9.71353264</v>
+      </c>
+      <c r="N78">
+        <v>-4.55353264</v>
+      </c>
+      <c r="O78">
+        <v>-1.0017771808</v>
+      </c>
+      <c r="P78">
+        <v>-3.5517554592</v>
+      </c>
+      <c r="Q78">
+        <v>-0.5417554592000005</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2658789212108454</v>
+      </c>
+      <c r="T78">
+        <v>2.844390883685836</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.1168678834027164</v>
+      </c>
+      <c r="W78">
+        <v>0.1888136465284992</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5312176518305292</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2090593124522623</v>
+      </c>
+      <c r="C79">
+        <v>-11.84058417954755</v>
+      </c>
+      <c r="D79">
+        <v>24.09001582045245</v>
+      </c>
+      <c r="E79">
+        <v>40.6506</v>
+      </c>
+      <c r="F79">
+        <v>46.0306</v>
+      </c>
+      <c r="G79">
+        <v>10.1</v>
+      </c>
+      <c r="H79">
+        <v>54.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>8.17</v>
+      </c>
+      <c r="K79">
+        <v>3.01</v>
+      </c>
+      <c r="L79">
+        <v>5.16</v>
+      </c>
+      <c r="M79">
+        <v>9.841342279999999</v>
+      </c>
+      <c r="N79">
+        <v>-4.681342279999999</v>
+      </c>
+      <c r="O79">
+        <v>-1.0298953016</v>
+      </c>
+      <c r="P79">
+        <v>-3.651446978399999</v>
+      </c>
+      <c r="Q79">
+        <v>-0.6414469783999994</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2757519177852299</v>
+      </c>
+      <c r="T79">
+        <v>2.968060052541742</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.1153501186832006</v>
+      </c>
+      <c r="W79">
+        <v>0.1891381446255317</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5243187212872755</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2108093124522623</v>
+      </c>
+      <c r="C80">
+        <v>-12.63424910408625</v>
+      </c>
+      <c r="D80">
+        <v>23.89415089591375</v>
+      </c>
+      <c r="E80">
+        <v>41.2484</v>
+      </c>
+      <c r="F80">
+        <v>46.6284</v>
+      </c>
+      <c r="G80">
+        <v>10.1</v>
+      </c>
+      <c r="H80">
+        <v>54.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>8.17</v>
+      </c>
+      <c r="K80">
+        <v>3.01</v>
+      </c>
+      <c r="L80">
+        <v>5.16</v>
+      </c>
+      <c r="M80">
+        <v>9.96915192</v>
+      </c>
+      <c r="N80">
+        <v>-4.80915192</v>
+      </c>
+      <c r="O80">
+        <v>-1.0580134224</v>
+      </c>
+      <c r="P80">
+        <v>-3.7511384976</v>
+      </c>
+      <c r="Q80">
+        <v>-0.7411384976000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2865224595027404</v>
+      </c>
+      <c r="T80">
+        <v>3.102971873111821</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.1138712710077749</v>
+      </c>
+      <c r="W80">
+        <v>0.1894543222585377</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5175966863989772</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2125593124522623</v>
+      </c>
+      <c r="C81">
+        <v>-13.42475473874232</v>
+      </c>
+      <c r="D81">
+        <v>23.70144526125769</v>
+      </c>
+      <c r="E81">
+        <v>41.8462</v>
+      </c>
+      <c r="F81">
+        <v>47.22620000000001</v>
+      </c>
+      <c r="G81">
+        <v>10.1</v>
+      </c>
+      <c r="H81">
+        <v>54.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>8.17</v>
+      </c>
+      <c r="K81">
+        <v>3.01</v>
+      </c>
+      <c r="L81">
+        <v>5.16</v>
+      </c>
+      <c r="M81">
+        <v>10.09696156</v>
+      </c>
+      <c r="N81">
+        <v>-4.93696156</v>
+      </c>
+      <c r="O81">
+        <v>-1.0861315432</v>
+      </c>
+      <c r="P81">
+        <v>-3.850830016800001</v>
+      </c>
+      <c r="Q81">
+        <v>-0.8408300168000009</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.298318767098109</v>
+      </c>
+      <c r="T81">
+        <v>3.250732438498099</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.1124298625140056</v>
+      </c>
+      <c r="W81">
+        <v>0.1897624953945056</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5110448296091166</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2143093124522623</v>
+      </c>
+      <c r="C82">
+        <v>-14.21217691071565</v>
+      </c>
+      <c r="D82">
+        <v>23.51182308928436</v>
+      </c>
+      <c r="E82">
+        <v>42.444</v>
+      </c>
+      <c r="F82">
+        <v>47.82400000000001</v>
+      </c>
+      <c r="G82">
+        <v>10.1</v>
+      </c>
+      <c r="H82">
+        <v>54.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>8.17</v>
+      </c>
+      <c r="K82">
+        <v>3.01</v>
+      </c>
+      <c r="L82">
+        <v>5.16</v>
+      </c>
+      <c r="M82">
+        <v>10.2247712</v>
+      </c>
+      <c r="N82">
+        <v>-5.064771200000001</v>
+      </c>
+      <c r="O82">
+        <v>-1.114249664</v>
+      </c>
+      <c r="P82">
+        <v>-3.950521536000001</v>
+      </c>
+      <c r="Q82">
+        <v>-0.9405215360000012</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3112947054530145</v>
+      </c>
+      <c r="T82">
+        <v>3.413269060423004</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.1110244892325806</v>
+      </c>
+      <c r="W82">
+        <v>0.1900629642020743</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5046567692390026</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2368654703999065</v>
+      </c>
+      <c r="C83">
+        <v>-17.00786237345213</v>
+      </c>
+      <c r="D83">
+        <v>21.31393762654787</v>
+      </c>
+      <c r="E83">
+        <v>43.0418</v>
+      </c>
+      <c r="F83">
+        <v>48.4218</v>
+      </c>
+      <c r="G83">
+        <v>10.1</v>
+      </c>
+      <c r="H83">
+        <v>54.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>8.17</v>
+      </c>
+      <c r="K83">
+        <v>3.01</v>
+      </c>
+      <c r="L83">
+        <v>5.16</v>
+      </c>
+      <c r="M83">
+        <v>11.56312584</v>
+      </c>
+      <c r="N83">
+        <v>-6.403125840000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.4086876848</v>
+      </c>
+      <c r="P83">
+        <v>-4.994438155200001</v>
+      </c>
+      <c r="Q83">
+        <v>-1.984438155200001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3285636791486689</v>
+      </c>
+      <c r="T83">
+        <v>3.629580249011582</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.09817414561666656</v>
+      </c>
+      <c r="W83">
+        <v>0.21535601402674</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4462461164393935</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2388654703999065</v>
+      </c>
+      <c r="C84">
+        <v>-17.78087380312572</v>
+      </c>
+      <c r="D84">
+        <v>21.13872619687428</v>
+      </c>
+      <c r="E84">
+        <v>43.6396</v>
+      </c>
+      <c r="F84">
+        <v>49.0196</v>
+      </c>
+      <c r="G84">
+        <v>10.1</v>
+      </c>
+      <c r="H84">
+        <v>54.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>8.17</v>
+      </c>
+      <c r="K84">
+        <v>3.01</v>
+      </c>
+      <c r="L84">
+        <v>5.16</v>
+      </c>
+      <c r="M84">
+        <v>11.70588048</v>
+      </c>
+      <c r="N84">
+        <v>-6.545880480000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.4400937056</v>
+      </c>
+      <c r="P84">
+        <v>-5.105786774400001</v>
+      </c>
+      <c r="Q84">
+        <v>-2.095786774400001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.344661661323595</v>
+      </c>
+      <c r="T84">
+        <v>3.831223596178892</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.09697689993841453</v>
+      </c>
+      <c r="W84">
+        <v>0.2156419162947066</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4408040906291569</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2408654703999065</v>
+      </c>
+      <c r="C85">
+        <v>-18.55102806567668</v>
+      </c>
+      <c r="D85">
+        <v>20.96637193432332</v>
+      </c>
+      <c r="E85">
+        <v>44.2374</v>
+      </c>
+      <c r="F85">
+        <v>49.6174</v>
+      </c>
+      <c r="G85">
+        <v>10.1</v>
+      </c>
+      <c r="H85">
+        <v>54.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>8.17</v>
+      </c>
+      <c r="K85">
+        <v>3.01</v>
+      </c>
+      <c r="L85">
+        <v>5.16</v>
+      </c>
+      <c r="M85">
+        <v>11.84863512</v>
+      </c>
+      <c r="N85">
+        <v>-6.688635120000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.4714997264</v>
+      </c>
+      <c r="P85">
+        <v>-5.2171353936</v>
+      </c>
+      <c r="Q85">
+        <v>-2.207135393600001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3626535237543947</v>
+      </c>
+      <c r="T85">
+        <v>4.056589690071768</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.09580850355361435</v>
+      </c>
+      <c r="W85">
+        <v>0.2159209293513969</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4354931979709744</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2428654703999065</v>
+      </c>
+      <c r="C86">
+        <v>-19.31839448348405</v>
+      </c>
+      <c r="D86">
+        <v>20.79680551651595</v>
+      </c>
+      <c r="E86">
+        <v>44.83519999999999</v>
+      </c>
+      <c r="F86">
+        <v>50.2152</v>
+      </c>
+      <c r="G86">
+        <v>10.1</v>
+      </c>
+      <c r="H86">
+        <v>54.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>8.17</v>
+      </c>
+      <c r="K86">
+        <v>3.01</v>
+      </c>
+      <c r="L86">
+        <v>5.16</v>
+      </c>
+      <c r="M86">
+        <v>11.99138976</v>
+      </c>
+      <c r="N86">
+        <v>-6.831389759999999</v>
+      </c>
+      <c r="O86">
+        <v>-1.5029057472</v>
+      </c>
+      <c r="P86">
+        <v>-5.328484012799999</v>
+      </c>
+      <c r="Q86">
+        <v>-2.318484012799999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3828943689890442</v>
+      </c>
+      <c r="T86">
+        <v>4.310126545701252</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.09466792613035706</v>
+      </c>
+      <c r="W86">
+        <v>0.2161932992400707</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4303087551379866</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2448654703999065</v>
+      </c>
+      <c r="C87">
+        <v>-20.08304015432775</v>
+      </c>
+      <c r="D87">
+        <v>20.62995984567225</v>
+      </c>
+      <c r="E87">
+        <v>45.433</v>
+      </c>
+      <c r="F87">
+        <v>50.813</v>
+      </c>
+      <c r="G87">
+        <v>10.1</v>
+      </c>
+      <c r="H87">
+        <v>54.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>8.17</v>
+      </c>
+      <c r="K87">
+        <v>3.01</v>
+      </c>
+      <c r="L87">
+        <v>5.16</v>
+      </c>
+      <c r="M87">
+        <v>12.1341444</v>
+      </c>
+      <c r="N87">
+        <v>-6.974144400000002</v>
+      </c>
+      <c r="O87">
+        <v>-1.534311768</v>
+      </c>
+      <c r="P87">
+        <v>-5.439832632000002</v>
+      </c>
+      <c r="Q87">
+        <v>-2.429832632000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4058339935883138</v>
+      </c>
+      <c r="T87">
+        <v>4.597468315414669</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.09355418582294106</v>
+      </c>
+      <c r="W87">
+        <v>0.2164592604254817</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4252462991951867</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2468654703999065</v>
+      </c>
+      <c r="C88">
+        <v>-20.84503003991434</v>
+      </c>
+      <c r="D88">
+        <v>20.46576996008566</v>
+      </c>
+      <c r="E88">
+        <v>46.0308</v>
+      </c>
+      <c r="F88">
+        <v>51.4108</v>
+      </c>
+      <c r="G88">
+        <v>10.1</v>
+      </c>
+      <c r="H88">
+        <v>54.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>8.17</v>
+      </c>
+      <c r="K88">
+        <v>3.01</v>
+      </c>
+      <c r="L88">
+        <v>5.16</v>
+      </c>
+      <c r="M88">
+        <v>12.27689904</v>
+      </c>
+      <c r="N88">
+        <v>-7.116899040000002</v>
+      </c>
+      <c r="O88">
+        <v>-1.5657177888</v>
+      </c>
+      <c r="P88">
+        <v>-5.551181251200001</v>
+      </c>
+      <c r="Q88">
+        <v>-2.541181251200001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4320507074160506</v>
+      </c>
+      <c r="T88">
+        <v>4.92585890937286</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.09246634645290687</v>
+      </c>
+      <c r="W88">
+        <v>0.2167190364670459</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4203015747859403</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2488654703999065</v>
+      </c>
+      <c r="C89">
+        <v>-21.60442705020886</v>
+      </c>
+      <c r="D89">
+        <v>20.30417294979114</v>
+      </c>
+      <c r="E89">
+        <v>46.6286</v>
+      </c>
+      <c r="F89">
+        <v>52.0086</v>
+      </c>
+      <c r="G89">
+        <v>10.1</v>
+      </c>
+      <c r="H89">
+        <v>54.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>8.17</v>
+      </c>
+      <c r="K89">
+        <v>3.01</v>
+      </c>
+      <c r="L89">
+        <v>5.16</v>
+      </c>
+      <c r="M89">
+        <v>12.41965368</v>
+      </c>
+      <c r="N89">
+        <v>-7.259653680000001</v>
+      </c>
+      <c r="O89">
+        <v>-1.5971238096</v>
+      </c>
+      <c r="P89">
+        <v>-5.662529870400001</v>
+      </c>
+      <c r="Q89">
+        <v>-2.652529870400001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4623007618326698</v>
+      </c>
+      <c r="T89">
+        <v>5.304771133170772</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.09140351488448266</v>
+      </c>
+      <c r="W89">
+        <v>0.2169728406455856</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4154705222021939</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2508654703999065</v>
+      </c>
+      <c r="C90">
+        <v>-22.36129212380261</v>
+      </c>
+      <c r="D90">
+        <v>20.14510787619739</v>
+      </c>
+      <c r="E90">
+        <v>47.2264</v>
+      </c>
+      <c r="F90">
+        <v>52.6064</v>
+      </c>
+      <c r="G90">
+        <v>10.1</v>
+      </c>
+      <c r="H90">
+        <v>54.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>8.17</v>
+      </c>
+      <c r="K90">
+        <v>3.01</v>
+      </c>
+      <c r="L90">
+        <v>5.16</v>
+      </c>
+      <c r="M90">
+        <v>12.56240832</v>
+      </c>
+      <c r="N90">
+        <v>-7.402408320000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.6285298304</v>
+      </c>
+      <c r="P90">
+        <v>-5.773878489600001</v>
+      </c>
+      <c r="Q90">
+        <v>-2.763878489600001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4975924919853924</v>
+      </c>
+      <c r="T90">
+        <v>5.746835394268337</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.09036483857897717</v>
+      </c>
+      <c r="W90">
+        <v>0.2172208765473403</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4107492662680781</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2528654703999065</v>
+      </c>
+      <c r="C91">
+        <v>-23.11568430453274</v>
+      </c>
+      <c r="D91">
+        <v>19.98851569546726</v>
+      </c>
+      <c r="E91">
+        <v>47.8242</v>
+      </c>
+      <c r="F91">
+        <v>53.2042</v>
+      </c>
+      <c r="G91">
+        <v>10.1</v>
+      </c>
+      <c r="H91">
+        <v>54.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>8.17</v>
+      </c>
+      <c r="K91">
+        <v>3.01</v>
+      </c>
+      <c r="L91">
+        <v>5.16</v>
+      </c>
+      <c r="M91">
+        <v>12.70516296</v>
+      </c>
+      <c r="N91">
+        <v>-7.545162960000001</v>
+      </c>
+      <c r="O91">
+        <v>-1.6599358512</v>
+      </c>
+      <c r="P91">
+        <v>-5.885227108800001</v>
+      </c>
+      <c r="Q91">
+        <v>-2.875227108800001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5393009003477007</v>
+      </c>
+      <c r="T91">
+        <v>6.269274975565458</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.08934950331404484</v>
+      </c>
+      <c r="W91">
+        <v>0.2174633386086061</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4061341059729312</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2548654703999065</v>
+      </c>
+      <c r="C92">
+        <v>-23.86766081455578</v>
+      </c>
+      <c r="D92">
+        <v>19.83433918544421</v>
+      </c>
+      <c r="E92">
+        <v>48.422</v>
+      </c>
+      <c r="F92">
+        <v>53.802</v>
+      </c>
+      <c r="G92">
+        <v>10.1</v>
+      </c>
+      <c r="H92">
+        <v>54.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>8.17</v>
+      </c>
+      <c r="K92">
+        <v>3.01</v>
+      </c>
+      <c r="L92">
+        <v>5.16</v>
+      </c>
+      <c r="M92">
+        <v>12.8479176</v>
+      </c>
+      <c r="N92">
+        <v>-7.6879176</v>
+      </c>
+      <c r="O92">
+        <v>-1.691341872</v>
+      </c>
+      <c r="P92">
+        <v>-5.996575728000001</v>
+      </c>
+      <c r="Q92">
+        <v>-2.986575728000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.589350990382471</v>
+      </c>
+      <c r="T92">
+        <v>6.896202473122005</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0883567310549999</v>
+      </c>
+      <c r="W92">
+        <v>0.217700412624066</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4016215047954541</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2568654703999065</v>
+      </c>
+      <c r="C93">
+        <v>-24.61727712406537</v>
+      </c>
+      <c r="D93">
+        <v>19.68252287593463</v>
+      </c>
+      <c r="E93">
+        <v>49.0198</v>
+      </c>
+      <c r="F93">
+        <v>54.39980000000001</v>
+      </c>
+      <c r="G93">
+        <v>10.1</v>
+      </c>
+      <c r="H93">
+        <v>54.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>8.17</v>
+      </c>
+      <c r="K93">
+        <v>3.01</v>
+      </c>
+      <c r="L93">
+        <v>5.16</v>
+      </c>
+      <c r="M93">
+        <v>12.99067224</v>
+      </c>
+      <c r="N93">
+        <v>-7.830672240000002</v>
+      </c>
+      <c r="O93">
+        <v>-1.7227478928</v>
+      </c>
+      <c r="P93">
+        <v>-6.107924347200002</v>
+      </c>
+      <c r="Q93">
+        <v>-3.097924347200002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.65052332264719</v>
+      </c>
+      <c r="T93">
+        <v>7.662447192357784</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.08738577796648341</v>
+      </c>
+      <c r="W93">
+        <v>0.2179322762216038</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3972080816658338</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2588654703999065</v>
+      </c>
+      <c r="C94">
+        <v>-25.36458701783243</v>
+      </c>
+      <c r="D94">
+        <v>19.53301298216758</v>
+      </c>
+      <c r="E94">
+        <v>49.6176</v>
+      </c>
+      <c r="F94">
+        <v>54.99760000000001</v>
+      </c>
+      <c r="G94">
+        <v>10.1</v>
+      </c>
+      <c r="H94">
+        <v>54.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>8.17</v>
+      </c>
+      <c r="K94">
+        <v>3.01</v>
+      </c>
+      <c r="L94">
+        <v>5.16</v>
+      </c>
+      <c r="M94">
+        <v>13.13342688</v>
+      </c>
+      <c r="N94">
+        <v>-7.973426880000002</v>
+      </c>
+      <c r="O94">
+        <v>-1.7541539136</v>
+      </c>
+      <c r="P94">
+        <v>-6.219272966400002</v>
+      </c>
+      <c r="Q94">
+        <v>-3.209272966400002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7269887379780891</v>
+      </c>
+      <c r="T94">
+        <v>8.62025309140251</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.08643593255380425</v>
+      </c>
+      <c r="W94">
+        <v>0.2181590993061516</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3928906025172921</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2608654703999065</v>
+      </c>
+      <c r="C95">
+        <v>-26.10964265873557</v>
+      </c>
+      <c r="D95">
+        <v>19.38575734126444</v>
+      </c>
+      <c r="E95">
+        <v>50.2154</v>
+      </c>
+      <c r="F95">
+        <v>55.59540000000001</v>
+      </c>
+      <c r="G95">
+        <v>10.1</v>
+      </c>
+      <c r="H95">
+        <v>54.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>8.17</v>
+      </c>
+      <c r="K95">
+        <v>3.01</v>
+      </c>
+      <c r="L95">
+        <v>5.16</v>
+      </c>
+      <c r="M95">
+        <v>13.27618152</v>
+      </c>
+      <c r="N95">
+        <v>-8.116181520000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.7855599344</v>
+      </c>
+      <c r="P95">
+        <v>-6.330621585600001</v>
+      </c>
+      <c r="Q95">
+        <v>-3.320621585600001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8253014148321016</v>
+      </c>
+      <c r="T95">
+        <v>9.851717818745726</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.08550651392419345</v>
+      </c>
+      <c r="W95">
+        <v>0.2183810444749026</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3886659723826975</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2628654703999065</v>
+      </c>
+      <c r="C96">
+        <v>-26.8524946484393</v>
+      </c>
+      <c r="D96">
+        <v>19.2407053515607</v>
+      </c>
+      <c r="E96">
+        <v>50.8132</v>
+      </c>
+      <c r="F96">
+        <v>56.1932</v>
+      </c>
+      <c r="G96">
+        <v>10.1</v>
+      </c>
+      <c r="H96">
+        <v>54.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>8.17</v>
+      </c>
+      <c r="K96">
+        <v>3.01</v>
+      </c>
+      <c r="L96">
+        <v>5.16</v>
+      </c>
+      <c r="M96">
+        <v>13.41893616</v>
+      </c>
+      <c r="N96">
+        <v>-8.258936160000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.8169659552</v>
+      </c>
+      <c r="P96">
+        <v>-6.441970204800001</v>
+      </c>
+      <c r="Q96">
+        <v>-3.431970204800002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9563849839707854</v>
+      </c>
+      <c r="T96">
+        <v>11.49367078853668</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.08459687015904246</v>
+      </c>
+      <c r="W96">
+        <v>0.2185982674060207</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3845312279956475</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2648654703999065</v>
+      </c>
+      <c r="C97">
+        <v>-27.59319208536846</v>
+      </c>
+      <c r="D97">
+        <v>19.09780791463155</v>
+      </c>
+      <c r="E97">
+        <v>51.411</v>
+      </c>
+      <c r="F97">
+        <v>56.791</v>
+      </c>
+      <c r="G97">
+        <v>10.1</v>
+      </c>
+      <c r="H97">
+        <v>54.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>8.17</v>
+      </c>
+      <c r="K97">
+        <v>3.01</v>
+      </c>
+      <c r="L97">
+        <v>5.16</v>
+      </c>
+      <c r="M97">
+        <v>13.5616908</v>
+      </c>
+      <c r="N97">
+        <v>-8.401690800000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.848371976</v>
+      </c>
+      <c r="P97">
+        <v>-6.553318824000001</v>
+      </c>
+      <c r="Q97">
+        <v>-3.543318824000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.139901980764943</v>
+      </c>
+      <c r="T97">
+        <v>13.79240494624403</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.08370637678894727</v>
+      </c>
+      <c r="W97">
+        <v>0.2188109172227994</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3804835308588513</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2668654703999065</v>
+      </c>
+      <c r="C98">
+        <v>-28.33178262011809</v>
+      </c>
+      <c r="D98">
+        <v>18.95701737988191</v>
+      </c>
+      <c r="E98">
+        <v>52.00879999999999</v>
+      </c>
+      <c r="F98">
+        <v>57.3888</v>
+      </c>
+      <c r="G98">
+        <v>10.1</v>
+      </c>
+      <c r="H98">
+        <v>54.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>8.17</v>
+      </c>
+      <c r="K98">
+        <v>3.01</v>
+      </c>
+      <c r="L98">
+        <v>5.16</v>
+      </c>
+      <c r="M98">
+        <v>13.70444544</v>
+      </c>
+      <c r="N98">
+        <v>-8.544445440000001</v>
+      </c>
+      <c r="O98">
+        <v>-1.8797779968</v>
+      </c>
+      <c r="P98">
+        <v>-6.664667443200001</v>
+      </c>
+      <c r="Q98">
+        <v>-3.654667443200001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.415177475956176</v>
+      </c>
+      <c r="T98">
+        <v>17.240506182805</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.08283443536406242</v>
+      </c>
+      <c r="W98">
+        <v>0.2190191368350619</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3765201607457382</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2688654703999065</v>
+      </c>
+      <c r="C99">
+        <v>-29.0683125084306</v>
+      </c>
+      <c r="D99">
+        <v>18.8182874915694</v>
+      </c>
+      <c r="E99">
+        <v>52.6066</v>
+      </c>
+      <c r="F99">
+        <v>57.9866</v>
+      </c>
+      <c r="G99">
+        <v>10.1</v>
+      </c>
+      <c r="H99">
+        <v>54.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>8.17</v>
+      </c>
+      <c r="K99">
+        <v>3.01</v>
+      </c>
+      <c r="L99">
+        <v>5.16</v>
+      </c>
+      <c r="M99">
+        <v>13.84720008</v>
+      </c>
+      <c r="N99">
+        <v>-8.687200080000002</v>
+      </c>
+      <c r="O99">
+        <v>-1.9111840176</v>
+      </c>
+      <c r="P99">
+        <v>-6.776016062400002</v>
+      </c>
+      <c r="Q99">
+        <v>-3.766016062400002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.873969967941568</v>
+      </c>
+      <c r="T99">
+        <v>22.98734157707333</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0819804721128865</v>
+      </c>
+      <c r="W99">
+        <v>0.2192230632594427</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3726385096040296</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2708654703999065</v>
+      </c>
+      <c r="C100">
+        <v>-29.80282666186341</v>
+      </c>
+      <c r="D100">
+        <v>18.68157333813659</v>
+      </c>
+      <c r="E100">
+        <v>53.2044</v>
+      </c>
+      <c r="F100">
+        <v>58.5844</v>
+      </c>
+      <c r="G100">
+        <v>10.1</v>
+      </c>
+      <c r="H100">
+        <v>54.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>8.17</v>
+      </c>
+      <c r="K100">
+        <v>3.01</v>
+      </c>
+      <c r="L100">
+        <v>5.16</v>
+      </c>
+      <c r="M100">
+        <v>13.98995472</v>
+      </c>
+      <c r="N100">
+        <v>-8.829954720000002</v>
+      </c>
+      <c r="O100">
+        <v>-1.9425900384</v>
+      </c>
+      <c r="P100">
+        <v>-6.887364681600001</v>
+      </c>
+      <c r="Q100">
+        <v>-3.877364681600001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.791554951912352</v>
+      </c>
+      <c r="T100">
+        <v>34.48101236560999</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.08114393668316316</v>
+      </c>
+      <c r="W100">
+        <v>0.2194228279200606</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.36883607583256</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2728654703999065</v>
+      </c>
+      <c r="C101">
+        <v>-30.53536869626411</v>
+      </c>
+      <c r="D101">
+        <v>18.54683130373589</v>
+      </c>
+      <c r="E101">
+        <v>53.8022</v>
+      </c>
+      <c r="F101">
+        <v>59.1822</v>
+      </c>
+      <c r="G101">
+        <v>10.1</v>
+      </c>
+      <c r="H101">
+        <v>54.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>8.17</v>
+      </c>
+      <c r="K101">
+        <v>3.01</v>
+      </c>
+      <c r="L101">
+        <v>5.16</v>
+      </c>
+      <c r="M101">
+        <v>14.13270936</v>
+      </c>
+      <c r="N101">
+        <v>-8.972709360000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.9739960592</v>
+      </c>
+      <c r="P101">
+        <v>-6.998713300800001</v>
+      </c>
+      <c r="Q101">
+        <v>-3.988713300800002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.544309903824704</v>
+      </c>
+      <c r="T101">
+        <v>68.96202473121998</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.08032430095909082</v>
+      </c>
+      <c r="W101">
+        <v>0.2196185569309691</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3651104589049583</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/botswana/botswana_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/botswana/botswana_hotel_gaming.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09016442288214344</v>
+        <v>0.09000116115180272</v>
       </c>
       <c r="C2">
-        <v>114.0673626591454</v>
+        <v>113.3166391975221</v>
       </c>
       <c r="D2">
-        <v>106.6373626591454</v>
+        <v>107.0312391975221</v>
       </c>
       <c r="E2">
-        <v>-3.16</v>
+        <v>-2.0154</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.1446</v>
       </c>
       <c r="G2">
         <v>7.43</v>
@@ -1451,28 +1451,28 @@
         <v>14.36</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05757338</v>
       </c>
       <c r="N2">
-        <v>14.36</v>
+        <v>14.30242662</v>
       </c>
       <c r="O2">
-        <v>3.1592</v>
+        <v>3.1465338564</v>
       </c>
       <c r="P2">
-        <v>11.2008</v>
+        <v>11.1558927636</v>
       </c>
       <c r="Q2">
-        <v>14.5408</v>
+        <v>14.4958927636</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09016442288214344</v>
+        <v>0.09051396075939669</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7539416154456742</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>249.4208260831655</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09000116115180272</v>
+        <v>0.089837899421462</v>
       </c>
       <c r="C3">
-        <v>113.3166391975221</v>
+        <v>112.568836173342</v>
       </c>
       <c r="D3">
-        <v>107.0312391975221</v>
+        <v>107.428036173342</v>
       </c>
       <c r="E3">
-        <v>-2.0154</v>
+        <v>-0.8708</v>
       </c>
       <c r="F3">
-        <v>1.1446</v>
+        <v>2.2892</v>
       </c>
       <c r="G3">
         <v>7.43</v>
@@ -1533,28 +1533,28 @@
         <v>14.36</v>
       </c>
       <c r="M3">
-        <v>0.05757338</v>
+        <v>0.11514676</v>
       </c>
       <c r="N3">
-        <v>14.30242662</v>
+        <v>14.24485324</v>
       </c>
       <c r="O3">
-        <v>3.1465338564</v>
+        <v>3.1338677128</v>
       </c>
       <c r="P3">
-        <v>11.1558927636</v>
+        <v>11.1109855272</v>
       </c>
       <c r="Q3">
-        <v>14.4958927636</v>
+        <v>14.4509855272</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09051396075939669</v>
+        <v>0.09087063206271634</v>
       </c>
       <c r="T3">
-        <v>0.7539416154456742</v>
+        <v>0.759955606021345</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>249.4208260831655</v>
+        <v>124.7104130415828</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.089837899421462</v>
+        <v>0.0896746376911213</v>
       </c>
       <c r="C4">
-        <v>112.568836173342</v>
+        <v>111.8239861882877</v>
       </c>
       <c r="D4">
-        <v>107.428036173342</v>
+        <v>107.8277861882877</v>
       </c>
       <c r="E4">
-        <v>-0.8708</v>
+        <v>0.2737999999999996</v>
       </c>
       <c r="F4">
-        <v>2.2892</v>
+        <v>3.4338</v>
       </c>
       <c r="G4">
         <v>7.43</v>
@@ -1615,28 +1615,28 @@
         <v>14.36</v>
       </c>
       <c r="M4">
-        <v>0.11514676</v>
+        <v>0.17272014</v>
       </c>
       <c r="N4">
-        <v>14.24485324</v>
+        <v>14.18727986</v>
       </c>
       <c r="O4">
-        <v>3.1338677128</v>
+        <v>3.1212015692</v>
       </c>
       <c r="P4">
-        <v>11.1109855272</v>
+        <v>11.0660782908</v>
       </c>
       <c r="Q4">
-        <v>14.4509855272</v>
+        <v>14.4060782908</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09087063206271634</v>
+        <v>0.09123465741352711</v>
       </c>
       <c r="T4">
-        <v>0.759955606021345</v>
+        <v>0.7660935964026998</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>124.7104130415828</v>
+        <v>83.14027536105519</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0896746376911213</v>
+        <v>0.0895113759607806</v>
       </c>
       <c r="C5">
-        <v>111.8239861882877</v>
+        <v>111.0821223311102</v>
       </c>
       <c r="D5">
-        <v>107.8277861882877</v>
+        <v>108.2305223311102</v>
       </c>
       <c r="E5">
-        <v>0.2737999999999996</v>
+        <v>1.4184</v>
       </c>
       <c r="F5">
-        <v>3.4338</v>
+        <v>4.5784</v>
       </c>
       <c r="G5">
         <v>7.43</v>
@@ -1697,28 +1697,28 @@
         <v>14.36</v>
       </c>
       <c r="M5">
-        <v>0.17272014</v>
+        <v>0.23029352</v>
       </c>
       <c r="N5">
-        <v>14.18727986</v>
+        <v>14.12970648</v>
       </c>
       <c r="O5">
-        <v>3.1212015692</v>
+        <v>3.1085354256</v>
       </c>
       <c r="P5">
-        <v>11.0660782908</v>
+        <v>11.0211710544</v>
       </c>
       <c r="Q5">
-        <v>14.4060782908</v>
+        <v>14.3611710544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09123465741352711</v>
+        <v>0.09160626662581312</v>
       </c>
       <c r="T5">
-        <v>0.7660935964026998</v>
+        <v>0.7723594615836661</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>83.14027536105519</v>
+        <v>62.35520652079138</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0895113759607806</v>
+        <v>0.08934811423043987</v>
       </c>
       <c r="C6">
-        <v>111.0821223311102</v>
+        <v>110.3432781867589</v>
       </c>
       <c r="D6">
-        <v>108.2305223311102</v>
+        <v>108.6362781867589</v>
       </c>
       <c r="E6">
-        <v>1.4184</v>
+        <v>2.563</v>
       </c>
       <c r="F6">
-        <v>4.5784</v>
+        <v>5.723</v>
       </c>
       <c r="G6">
         <v>7.43</v>
@@ -1779,28 +1779,28 @@
         <v>14.36</v>
       </c>
       <c r="M6">
-        <v>0.23029352</v>
+        <v>0.2878669</v>
       </c>
       <c r="N6">
-        <v>14.12970648</v>
+        <v>14.0721331</v>
       </c>
       <c r="O6">
-        <v>3.1085354256</v>
+        <v>3.095869282</v>
       </c>
       <c r="P6">
-        <v>11.0211710544</v>
+        <v>10.976263818</v>
       </c>
       <c r="Q6">
-        <v>14.3611710544</v>
+        <v>14.316263818</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09160626662581312</v>
+        <v>0.09198569918993671</v>
       </c>
       <c r="T6">
-        <v>0.7723594615836661</v>
+        <v>0.7787572397158108</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>62.35520652079138</v>
+        <v>49.88416521663311</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08934811423043987</v>
+        <v>0.08918485250009914</v>
       </c>
       <c r="C7">
-        <v>110.3432781867589</v>
+        <v>109.6074878457177</v>
       </c>
       <c r="D7">
-        <v>108.6362781867589</v>
+        <v>109.0450878457177</v>
       </c>
       <c r="E7">
-        <v>2.563</v>
+        <v>3.7076</v>
       </c>
       <c r="F7">
-        <v>5.723</v>
+        <v>6.8676</v>
       </c>
       <c r="G7">
         <v>7.43</v>
@@ -1861,28 +1861,28 @@
         <v>14.36</v>
       </c>
       <c r="M7">
-        <v>0.2878669</v>
+        <v>0.34544028</v>
       </c>
       <c r="N7">
-        <v>14.0721331</v>
+        <v>14.01455972</v>
       </c>
       <c r="O7">
-        <v>3.095869282</v>
+        <v>3.0832031384</v>
       </c>
       <c r="P7">
-        <v>10.976263818</v>
+        <v>10.9313565816</v>
       </c>
       <c r="Q7">
-        <v>14.316263818</v>
+        <v>14.2713565816</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09198569918993671</v>
+        <v>0.09237320478733951</v>
       </c>
       <c r="T7">
-        <v>0.7787572397158108</v>
+        <v>0.785291140786937</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.88416521663311</v>
+        <v>41.57013768052759</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08918485250009914</v>
+        <v>0.08902159076975844</v>
       </c>
       <c r="C8">
-        <v>109.6074878457177</v>
+        <v>108.8747859135534</v>
       </c>
       <c r="D8">
-        <v>109.0450878457177</v>
+        <v>109.4569859135534</v>
       </c>
       <c r="E8">
-        <v>3.707599999999999</v>
+        <v>4.852199999999998</v>
       </c>
       <c r="F8">
-        <v>6.867599999999999</v>
+        <v>8.012199999999998</v>
       </c>
       <c r="G8">
         <v>7.43</v>
@@ -1943,28 +1943,28 @@
         <v>14.36</v>
       </c>
       <c r="M8">
-        <v>0.3454402799999999</v>
+        <v>0.4030136599999999</v>
       </c>
       <c r="N8">
-        <v>14.01455972</v>
+        <v>13.95698634</v>
       </c>
       <c r="O8">
-        <v>3.0832031384</v>
+        <v>3.0705369948</v>
       </c>
       <c r="P8">
-        <v>10.9313565816</v>
+        <v>10.8864493452</v>
       </c>
       <c r="Q8">
-        <v>14.2713565816</v>
+        <v>14.2264493452</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09237320478733951</v>
+        <v>0.09276904383844993</v>
       </c>
       <c r="T8">
-        <v>0.785291140786937</v>
+        <v>0.7919655558595929</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.57013768052759</v>
+        <v>35.63154658330937</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08902159076975845</v>
+        <v>0.08885832903941773</v>
       </c>
       <c r="C9">
-        <v>108.8747859135533</v>
+        <v>108.1452075206799</v>
       </c>
       <c r="D9">
-        <v>109.4569859135533</v>
+        <v>109.8720075206799</v>
       </c>
       <c r="E9">
-        <v>4.8522</v>
+        <v>5.9968</v>
       </c>
       <c r="F9">
-        <v>8.0122</v>
+        <v>9.1568</v>
       </c>
       <c r="G9">
         <v>7.43</v>
@@ -2025,28 +2025,28 @@
         <v>14.36</v>
       </c>
       <c r="M9">
-        <v>0.40301366</v>
+        <v>0.46058704</v>
       </c>
       <c r="N9">
-        <v>13.95698634</v>
+        <v>13.89941296</v>
       </c>
       <c r="O9">
-        <v>3.0705369948</v>
+        <v>3.0578708512</v>
       </c>
       <c r="P9">
-        <v>10.8864493452</v>
+        <v>10.8415421088</v>
       </c>
       <c r="Q9">
-        <v>14.2264493452</v>
+        <v>14.1815421088</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09276904383844994</v>
+        <v>0.09317348808632361</v>
       </c>
       <c r="T9">
-        <v>0.7919655558595931</v>
+        <v>0.7987850669120893</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.63154658330936</v>
+        <v>31.17760326039569</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08885832903941773</v>
+        <v>0.088695067309077</v>
       </c>
       <c r="C10">
-        <v>108.1452075206799</v>
+        <v>107.4187883323473</v>
       </c>
       <c r="D10">
-        <v>109.8720075206799</v>
+        <v>110.2901883323473</v>
       </c>
       <c r="E10">
-        <v>5.9968</v>
+        <v>7.141399999999999</v>
       </c>
       <c r="F10">
-        <v>9.1568</v>
+        <v>10.3014</v>
       </c>
       <c r="G10">
         <v>7.43</v>
@@ -2107,28 +2107,28 @@
         <v>14.36</v>
       </c>
       <c r="M10">
-        <v>0.46058704</v>
+        <v>0.51816042</v>
       </c>
       <c r="N10">
-        <v>13.89941296</v>
+        <v>13.84183958</v>
       </c>
       <c r="O10">
-        <v>3.0578708512</v>
+        <v>3.0452047076</v>
       </c>
       <c r="P10">
-        <v>10.8415421088</v>
+        <v>10.7966348724</v>
       </c>
       <c r="Q10">
-        <v>14.1815421088</v>
+        <v>14.1366348724</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09317348808632361</v>
+        <v>0.09358682121876594</v>
       </c>
       <c r="T10">
-        <v>0.7987850669120893</v>
+        <v>0.8057544573283767</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.17760326039569</v>
+        <v>27.71342512035173</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.088695067309077</v>
+        <v>0.0885318055787363</v>
       </c>
       <c r="C11">
-        <v>107.4187883323473</v>
+        <v>106.6955645588577</v>
       </c>
       <c r="D11">
-        <v>110.2901883323473</v>
+        <v>110.7115645588577</v>
       </c>
       <c r="E11">
-        <v>7.141399999999999</v>
+        <v>8.285999999999998</v>
       </c>
       <c r="F11">
-        <v>10.3014</v>
+        <v>11.446</v>
       </c>
       <c r="G11">
         <v>7.43</v>
@@ -2189,28 +2189,28 @@
         <v>14.36</v>
       </c>
       <c r="M11">
-        <v>0.51816042</v>
+        <v>0.5757337999999999</v>
       </c>
       <c r="N11">
-        <v>13.84183958</v>
+        <v>13.7842662</v>
       </c>
       <c r="O11">
-        <v>3.0452047076</v>
+        <v>3.032538564</v>
       </c>
       <c r="P11">
-        <v>10.7966348724</v>
+        <v>10.751727636</v>
       </c>
       <c r="Q11">
-        <v>14.1366348724</v>
+        <v>14.091727636</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09358682121876594</v>
+        <v>0.09400933953192922</v>
       </c>
       <c r="T11">
-        <v>0.8057544573283767</v>
+        <v>0.8128787230872483</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.71342512035173</v>
+        <v>24.94208260831656</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0885318055787363</v>
+        <v>0.08836854384839558</v>
       </c>
       <c r="C12">
-        <v>106.6955645588577</v>
+        <v>105.9755729660181</v>
       </c>
       <c r="D12">
-        <v>110.7115645588577</v>
+        <v>111.1361729660181</v>
       </c>
       <c r="E12">
-        <v>8.286</v>
+        <v>9.4306</v>
       </c>
       <c r="F12">
-        <v>11.446</v>
+        <v>12.5906</v>
       </c>
       <c r="G12">
         <v>7.43</v>
@@ -2271,28 +2271,28 @@
         <v>14.36</v>
       </c>
       <c r="M12">
-        <v>0.5757338</v>
+        <v>0.63330718</v>
       </c>
       <c r="N12">
-        <v>13.7842662</v>
+        <v>13.72669282</v>
       </c>
       <c r="O12">
-        <v>3.032538564</v>
+        <v>3.0198724204</v>
       </c>
       <c r="P12">
-        <v>10.751727636</v>
+        <v>10.7068203996</v>
       </c>
       <c r="Q12">
-        <v>14.091727636</v>
+        <v>14.0468203996</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09400933953192922</v>
+        <v>0.09444135263864673</v>
       </c>
       <c r="T12">
-        <v>0.8128787230872483</v>
+        <v>0.8201630847058698</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.94208260831655</v>
+        <v>22.67462055301505</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08836854384839558</v>
+        <v>0.08820528211805487</v>
       </c>
       <c r="C13">
-        <v>105.9755729660181</v>
+        <v>105.258850885834</v>
       </c>
       <c r="D13">
-        <v>111.1361729660181</v>
+        <v>111.564050885834</v>
       </c>
       <c r="E13">
-        <v>9.4306</v>
+        <v>10.5752</v>
       </c>
       <c r="F13">
-        <v>12.5906</v>
+        <v>13.7352</v>
       </c>
       <c r="G13">
         <v>7.43</v>
@@ -2353,28 +2353,28 @@
         <v>14.36</v>
       </c>
       <c r="M13">
-        <v>0.63330718</v>
+        <v>0.6908805599999999</v>
       </c>
       <c r="N13">
-        <v>13.72669282</v>
+        <v>13.66911944</v>
       </c>
       <c r="O13">
-        <v>3.0198724204</v>
+        <v>3.0072062768</v>
       </c>
       <c r="P13">
-        <v>10.7068203996</v>
+        <v>10.6619131632</v>
       </c>
       <c r="Q13">
-        <v>14.0468203996</v>
+        <v>14.0019131632</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09444135263864673</v>
+        <v>0.09488318422506234</v>
       </c>
       <c r="T13">
-        <v>0.8201630847058698</v>
+        <v>0.8276129999976418</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.67462055301505</v>
+        <v>20.7850688402638</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08820528211805487</v>
+        <v>0.08804202038771414</v>
       </c>
       <c r="C14">
-        <v>105.258850885834</v>
+        <v>104.5454362274503</v>
       </c>
       <c r="D14">
-        <v>111.564050885834</v>
+        <v>111.9952362274503</v>
       </c>
       <c r="E14">
-        <v>10.5752</v>
+        <v>11.7198</v>
       </c>
       <c r="F14">
-        <v>13.7352</v>
+        <v>14.8798</v>
       </c>
       <c r="G14">
         <v>7.43</v>
@@ -2435,28 +2435,28 @@
         <v>14.36</v>
       </c>
       <c r="M14">
-        <v>0.6908805599999999</v>
+        <v>0.74845394</v>
       </c>
       <c r="N14">
-        <v>13.66911944</v>
+        <v>13.61154606</v>
       </c>
       <c r="O14">
-        <v>3.0072062768</v>
+        <v>2.9945401332</v>
       </c>
       <c r="P14">
-        <v>10.6619131632</v>
+        <v>10.6170059268</v>
       </c>
       <c r="Q14">
-        <v>14.0019131632</v>
+        <v>13.9570059268</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09488318422506234</v>
+        <v>0.09533517285944154</v>
       </c>
       <c r="T14">
-        <v>0.8276129999976418</v>
+        <v>0.8352341777099143</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.7850688402638</v>
+        <v>19.18621739101273</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08804202038771414</v>
+        <v>0.08787875865737342</v>
       </c>
       <c r="C15">
-        <v>104.5454362274503</v>
+        <v>103.8353674883483</v>
       </c>
       <c r="D15">
-        <v>111.9952362274503</v>
+        <v>112.4297674883483</v>
       </c>
       <c r="E15">
-        <v>11.7198</v>
+        <v>12.8644</v>
       </c>
       <c r="F15">
-        <v>14.8798</v>
+        <v>16.0244</v>
       </c>
       <c r="G15">
         <v>7.43</v>
@@ -2517,28 +2517,28 @@
         <v>14.36</v>
       </c>
       <c r="M15">
-        <v>0.74845394</v>
+        <v>0.80602732</v>
       </c>
       <c r="N15">
-        <v>13.61154606</v>
+        <v>13.55397268</v>
       </c>
       <c r="O15">
-        <v>2.9945401332</v>
+        <v>2.9818739896</v>
       </c>
       <c r="P15">
-        <v>10.6170059268</v>
+        <v>10.5720986904</v>
       </c>
       <c r="Q15">
-        <v>13.9570059268</v>
+        <v>13.9120986904</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09533517285944154</v>
+        <v>0.09579767285741096</v>
       </c>
       <c r="T15">
-        <v>0.8352341777099143</v>
+        <v>0.8430325921131699</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.18621739101273</v>
+        <v>17.81577329165468</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08787875865737342</v>
+        <v>0.08771549692703272</v>
       </c>
       <c r="C16">
-        <v>103.8353674883483</v>
+        <v>103.128683765803</v>
       </c>
       <c r="D16">
-        <v>112.4297674883483</v>
+        <v>112.867683765803</v>
       </c>
       <c r="E16">
-        <v>12.8644</v>
+        <v>14.009</v>
       </c>
       <c r="F16">
-        <v>16.0244</v>
+        <v>17.169</v>
       </c>
       <c r="G16">
         <v>7.43</v>
@@ -2599,28 +2599,28 @@
         <v>14.36</v>
       </c>
       <c r="M16">
-        <v>0.80602732</v>
+        <v>0.8636007</v>
       </c>
       <c r="N16">
-        <v>13.55397268</v>
+        <v>13.4963993</v>
       </c>
       <c r="O16">
-        <v>2.9818739896</v>
+        <v>2.969207846</v>
       </c>
       <c r="P16">
-        <v>10.5720986904</v>
+        <v>10.527191454</v>
       </c>
       <c r="Q16">
-        <v>13.9120986904</v>
+        <v>13.867191454</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09579767285741096</v>
+        <v>0.09627105520827378</v>
       </c>
       <c r="T16">
-        <v>0.8430325921131699</v>
+        <v>0.8510144986200315</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.81577329165468</v>
+        <v>16.62805507221103</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08771549692703272</v>
+        <v>0.08755223519669199</v>
       </c>
       <c r="C17">
-        <v>103.128683765803</v>
+        <v>102.4254247686104</v>
       </c>
       <c r="D17">
-        <v>112.867683765803</v>
+        <v>113.3090247686104</v>
       </c>
       <c r="E17">
-        <v>14.009</v>
+        <v>15.1536</v>
       </c>
       <c r="F17">
-        <v>17.169</v>
+        <v>18.3136</v>
       </c>
       <c r="G17">
         <v>7.43</v>
@@ -2681,28 +2681,28 @@
         <v>14.36</v>
       </c>
       <c r="M17">
-        <v>0.8636006999999998</v>
+        <v>0.92117408</v>
       </c>
       <c r="N17">
-        <v>13.4963993</v>
+        <v>13.43882592</v>
       </c>
       <c r="O17">
-        <v>2.969207846</v>
+        <v>2.9565417024</v>
       </c>
       <c r="P17">
-        <v>10.527191454</v>
+        <v>10.4822842176</v>
       </c>
       <c r="Q17">
-        <v>13.867191454</v>
+        <v>13.8222842176</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09627105520827378</v>
+        <v>0.09675570856749047</v>
       </c>
       <c r="T17">
-        <v>0.8510144986200315</v>
+        <v>0.8591864505199136</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.62805507221104</v>
+        <v>15.58880163019784</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08755223519669199</v>
+        <v>0.08738897346635129</v>
       </c>
       <c r="C18">
-        <v>102.4254247686104</v>
+        <v>101.7256308290895</v>
       </c>
       <c r="D18">
-        <v>113.3090247686104</v>
+        <v>113.7538308290895</v>
       </c>
       <c r="E18">
-        <v>15.1536</v>
+        <v>16.2982</v>
       </c>
       <c r="F18">
-        <v>18.3136</v>
+        <v>19.4582</v>
       </c>
       <c r="G18">
         <v>7.43</v>
@@ -2763,28 +2763,28 @@
         <v>14.36</v>
       </c>
       <c r="M18">
-        <v>0.92117408</v>
+        <v>0.97874746</v>
       </c>
       <c r="N18">
-        <v>13.43882592</v>
+        <v>13.38125254</v>
       </c>
       <c r="O18">
-        <v>2.9565417024</v>
+        <v>2.9438755588</v>
       </c>
       <c r="P18">
-        <v>10.4822842176</v>
+        <v>10.4373769812</v>
       </c>
       <c r="Q18">
-        <v>13.8222842176</v>
+        <v>13.7773769812</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09675570856749047</v>
+        <v>0.09725204032090518</v>
       </c>
       <c r="T18">
-        <v>0.8591864505199136</v>
+        <v>0.8675553169234075</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.58880163019784</v>
+        <v>14.67181329900974</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08738897346635129</v>
+        <v>0.08722571173601057</v>
       </c>
       <c r="C19">
-        <v>101.7256308290895</v>
+        <v>101.0293429153704</v>
       </c>
       <c r="D19">
-        <v>113.7538308290895</v>
+        <v>114.2021429153704</v>
       </c>
       <c r="E19">
-        <v>16.2982</v>
+        <v>17.4428</v>
       </c>
       <c r="F19">
-        <v>19.4582</v>
+        <v>20.6028</v>
       </c>
       <c r="G19">
         <v>7.43</v>
@@ -2845,28 +2845,28 @@
         <v>14.36</v>
       </c>
       <c r="M19">
-        <v>0.97874746</v>
+        <v>1.03632084</v>
       </c>
       <c r="N19">
-        <v>13.38125254</v>
+        <v>13.32367916</v>
       </c>
       <c r="O19">
-        <v>2.9438755588</v>
+        <v>2.9312094152</v>
       </c>
       <c r="P19">
-        <v>10.4373769812</v>
+        <v>10.3924697448</v>
       </c>
       <c r="Q19">
-        <v>13.7773769812</v>
+        <v>13.7324697448</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09725204032090518</v>
+        <v>0.09776047772684215</v>
       </c>
       <c r="T19">
-        <v>0.8675553169234075</v>
+        <v>0.8761283020196693</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.67181329900974</v>
+        <v>13.85671256017586</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08722571173601058</v>
+        <v>0.08706245000566985</v>
       </c>
       <c r="C20">
-        <v>101.0293429153704</v>
+        <v>100.3366026439716</v>
       </c>
       <c r="D20">
-        <v>114.2021429153704</v>
+        <v>114.6540026439716</v>
       </c>
       <c r="E20">
-        <v>17.4428</v>
+        <v>18.5874</v>
       </c>
       <c r="F20">
-        <v>20.6028</v>
+        <v>21.7474</v>
       </c>
       <c r="G20">
         <v>7.43</v>
@@ -2927,28 +2927,28 @@
         <v>14.36</v>
       </c>
       <c r="M20">
-        <v>1.03632084</v>
+        <v>1.09389422</v>
       </c>
       <c r="N20">
-        <v>13.32367916</v>
+        <v>13.26610578</v>
       </c>
       <c r="O20">
-        <v>2.9312094152</v>
+        <v>2.9185432716</v>
       </c>
       <c r="P20">
-        <v>10.3924697448</v>
+        <v>10.3475625084</v>
       </c>
       <c r="Q20">
-        <v>13.7324697448</v>
+        <v>13.6875625084</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09776047772684215</v>
+        <v>0.09828146914280228</v>
       </c>
       <c r="T20">
-        <v>0.8761283020196692</v>
+        <v>0.8849129657602832</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.85671256017586</v>
+        <v>13.12741189911398</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08706245000566985</v>
+        <v>0.08713318827532915</v>
       </c>
       <c r="C21">
-        <v>100.3366026439716</v>
+        <v>98.99578197736051</v>
       </c>
       <c r="D21">
-        <v>114.6540026439716</v>
+        <v>114.4577819773605</v>
       </c>
       <c r="E21">
-        <v>18.5874</v>
+        <v>19.732</v>
       </c>
       <c r="F21">
-        <v>21.7474</v>
+        <v>22.892</v>
       </c>
       <c r="G21">
         <v>7.43</v>
@@ -3009,45 +3009,45 @@
         <v>14.36</v>
       </c>
       <c r="M21">
-        <v>1.09389422</v>
+        <v>1.1858056</v>
       </c>
       <c r="N21">
-        <v>13.26610578</v>
+        <v>13.1741944</v>
       </c>
       <c r="O21">
-        <v>2.9185432716</v>
+        <v>2.898322768</v>
       </c>
       <c r="P21">
-        <v>10.3475625084</v>
+        <v>10.275871632</v>
       </c>
       <c r="Q21">
-        <v>13.6875625084</v>
+        <v>13.615871632</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09828146914280228</v>
+        <v>0.09881548534416143</v>
       </c>
       <c r="T21">
-        <v>0.8849129657602832</v>
+        <v>0.8939172460944127</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.12741189911398</v>
+        <v>12.10991076446257</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08713318827532915</v>
+        <v>0.08698162654498844</v>
       </c>
       <c r="C22">
-        <v>98.99578197736051</v>
+        <v>98.27242370438404</v>
       </c>
       <c r="D22">
-        <v>114.4577819773605</v>
+        <v>114.879023704384</v>
       </c>
       <c r="E22">
-        <v>19.732</v>
+        <v>20.8766</v>
       </c>
       <c r="F22">
-        <v>22.892</v>
+        <v>24.0366</v>
       </c>
       <c r="G22">
         <v>7.43</v>
@@ -3091,28 +3091,28 @@
         <v>14.36</v>
       </c>
       <c r="M22">
-        <v>1.1858056</v>
+        <v>1.24509588</v>
       </c>
       <c r="N22">
-        <v>13.1741944</v>
+        <v>13.11490412</v>
       </c>
       <c r="O22">
-        <v>2.898322768</v>
+        <v>2.8852789064</v>
       </c>
       <c r="P22">
-        <v>10.275871632</v>
+        <v>10.2296252136</v>
       </c>
       <c r="Q22">
-        <v>13.615871632</v>
+        <v>13.5696252136</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09881548534416143</v>
+        <v>0.09936302094302332</v>
       </c>
       <c r="T22">
-        <v>0.8939172460944127</v>
+        <v>0.9031494828926973</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.10991076446257</v>
+        <v>11.53324834710721</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08698162654498842</v>
+        <v>0.08683006481464771</v>
       </c>
       <c r="C23">
-        <v>98.2724237043841</v>
+        <v>97.55217749692967</v>
       </c>
       <c r="D23">
-        <v>114.8790237043841</v>
+        <v>115.3033774969297</v>
       </c>
       <c r="E23">
-        <v>20.8766</v>
+        <v>22.0212</v>
       </c>
       <c r="F23">
-        <v>24.0366</v>
+        <v>25.1812</v>
       </c>
       <c r="G23">
         <v>7.43</v>
@@ -3173,28 +3173,28 @@
         <v>14.36</v>
       </c>
       <c r="M23">
-        <v>1.24509588</v>
+        <v>1.30438616</v>
       </c>
       <c r="N23">
-        <v>13.11490412</v>
+        <v>13.05561384</v>
       </c>
       <c r="O23">
-        <v>2.8852789064</v>
+        <v>2.8722350448</v>
       </c>
       <c r="P23">
-        <v>10.2296252136</v>
+        <v>10.1833787952</v>
       </c>
       <c r="Q23">
-        <v>13.5696252136</v>
+        <v>13.5233787952</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09936302094302331</v>
+        <v>0.099924595916215</v>
       </c>
       <c r="T23">
-        <v>0.903149482892697</v>
+        <v>0.9126184437114505</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.53324834710721</v>
+        <v>11.00900978587507</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08683006481464771</v>
+        <v>0.08667850308430698</v>
       </c>
       <c r="C24">
-        <v>97.55217749692967</v>
+        <v>96.83507797001509</v>
       </c>
       <c r="D24">
-        <v>115.3033774969297</v>
+        <v>115.7308779700151</v>
       </c>
       <c r="E24">
-        <v>22.0212</v>
+        <v>23.1658</v>
       </c>
       <c r="F24">
-        <v>25.1812</v>
+        <v>26.3258</v>
       </c>
       <c r="G24">
         <v>7.43</v>
@@ -3255,28 +3255,28 @@
         <v>14.36</v>
       </c>
       <c r="M24">
-        <v>1.30438616</v>
+        <v>1.36367644</v>
       </c>
       <c r="N24">
-        <v>13.05561384</v>
+        <v>12.99632356</v>
       </c>
       <c r="O24">
-        <v>2.8722350448</v>
+        <v>2.8591911832</v>
       </c>
       <c r="P24">
-        <v>10.1833787952</v>
+        <v>10.1371323768</v>
       </c>
       <c r="Q24">
-        <v>13.5233787952</v>
+        <v>13.4771323768</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.099924595916215</v>
+        <v>0.1005007572523467</v>
       </c>
       <c r="T24">
-        <v>0.9126184437114505</v>
+        <v>0.9223333515644573</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.00900978587507</v>
+        <v>10.53035718648919</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08667850308430698</v>
+        <v>0.08652694135396628</v>
       </c>
       <c r="C25">
-        <v>96.83507797001509</v>
+        <v>96.12116025392483</v>
       </c>
       <c r="D25">
-        <v>115.7308779700151</v>
+        <v>116.1615602539248</v>
       </c>
       <c r="E25">
-        <v>23.1658</v>
+        <v>24.3104</v>
       </c>
       <c r="F25">
-        <v>26.3258</v>
+        <v>27.4704</v>
       </c>
       <c r="G25">
         <v>7.43</v>
@@ -3337,28 +3337,28 @@
         <v>14.36</v>
       </c>
       <c r="M25">
-        <v>1.36367644</v>
+        <v>1.42296672</v>
       </c>
       <c r="N25">
-        <v>12.99632356</v>
+        <v>12.93703328</v>
       </c>
       <c r="O25">
-        <v>2.8591911832</v>
+        <v>2.8461473216</v>
       </c>
       <c r="P25">
-        <v>10.1371323768</v>
+        <v>10.0908859584</v>
       </c>
       <c r="Q25">
-        <v>13.4771323768</v>
+        <v>13.4308859584</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1005007572523467</v>
+        <v>0.101092080728903</v>
       </c>
       <c r="T25">
-        <v>0.9223333515644573</v>
+        <v>0.9323039148872799</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.53035718648919</v>
+        <v>10.09159230371881</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08652694135396628</v>
+        <v>0.08670687962362554</v>
       </c>
       <c r="C26">
-        <v>96.12116025392483</v>
+        <v>94.46559705298345</v>
       </c>
       <c r="D26">
-        <v>116.1615602539248</v>
+        <v>115.6505970529835</v>
       </c>
       <c r="E26">
-        <v>24.3104</v>
+        <v>25.455</v>
       </c>
       <c r="F26">
-        <v>27.4704</v>
+        <v>28.615</v>
       </c>
       <c r="G26">
         <v>7.43</v>
@@ -3419,45 +3419,45 @@
         <v>14.36</v>
       </c>
       <c r="M26">
-        <v>1.42296672</v>
+        <v>1.5309025</v>
       </c>
       <c r="N26">
-        <v>12.93703328</v>
+        <v>12.8290975</v>
       </c>
       <c r="O26">
-        <v>2.8461473216</v>
+        <v>2.82240145</v>
       </c>
       <c r="P26">
-        <v>10.0908859584</v>
+        <v>10.00669605</v>
       </c>
       <c r="Q26">
-        <v>13.4308859584</v>
+        <v>13.34669605</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.101092080728903</v>
+        <v>0.1016991728315007</v>
       </c>
       <c r="T26">
-        <v>0.9323039148872799</v>
+        <v>0.9425403598987112</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.09159230371881</v>
+        <v>9.380087889333254</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08670687962362554</v>
+        <v>0.08656857789328484</v>
       </c>
       <c r="C27">
-        <v>94.46559705298345</v>
+        <v>93.71332561860646</v>
       </c>
       <c r="D27">
-        <v>115.6505970529835</v>
+        <v>116.0429256186065</v>
       </c>
       <c r="E27">
-        <v>25.455</v>
+        <v>26.5996</v>
       </c>
       <c r="F27">
-        <v>28.615</v>
+        <v>29.7596</v>
       </c>
       <c r="G27">
         <v>7.43</v>
@@ -3501,28 +3501,28 @@
         <v>14.36</v>
       </c>
       <c r="M27">
-        <v>1.5309025</v>
+        <v>1.5921386</v>
       </c>
       <c r="N27">
-        <v>12.8290975</v>
+        <v>12.7678614</v>
       </c>
       <c r="O27">
-        <v>2.82240145</v>
+        <v>2.808929508</v>
       </c>
       <c r="P27">
-        <v>10.00669605</v>
+        <v>9.958931891999999</v>
       </c>
       <c r="Q27">
-        <v>13.34669605</v>
+        <v>13.298931892</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1016991728315007</v>
+        <v>0.1023226728287633</v>
       </c>
       <c r="T27">
-        <v>0.9425403598987112</v>
+        <v>0.9530534655861271</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.380087889333254</v>
+        <v>9.019315278205051</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08656857789328484</v>
+        <v>0.08643027616294413</v>
       </c>
       <c r="C28">
-        <v>93.71332561860646</v>
+        <v>92.96372508507548</v>
       </c>
       <c r="D28">
-        <v>116.0429256186065</v>
+        <v>116.4379250850755</v>
       </c>
       <c r="E28">
-        <v>26.5996</v>
+        <v>27.7442</v>
       </c>
       <c r="F28">
-        <v>29.7596</v>
+        <v>30.9042</v>
       </c>
       <c r="G28">
         <v>7.43</v>
@@ -3583,28 +3583,28 @@
         <v>14.36</v>
       </c>
       <c r="M28">
-        <v>1.5921386</v>
+        <v>1.6533747</v>
       </c>
       <c r="N28">
-        <v>12.7678614</v>
+        <v>12.7066253</v>
       </c>
       <c r="O28">
-        <v>2.808929508</v>
+        <v>2.795457566</v>
       </c>
       <c r="P28">
-        <v>9.958931891999999</v>
+        <v>9.911167733999999</v>
       </c>
       <c r="Q28">
-        <v>13.298931892</v>
+        <v>13.251167734</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1023226728287633</v>
+        <v>0.1029632550177317</v>
       </c>
       <c r="T28">
-        <v>0.9530534655861271</v>
+        <v>0.9638546015663489</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.019315278205051</v>
+        <v>8.685266564197455</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08643027616294413</v>
+        <v>0.0862919744326034</v>
       </c>
       <c r="C29">
-        <v>92.96372508507548</v>
+        <v>92.21682282005142</v>
       </c>
       <c r="D29">
-        <v>116.4379250850755</v>
+        <v>116.8356228200514</v>
       </c>
       <c r="E29">
-        <v>27.7442</v>
+        <v>28.8888</v>
       </c>
       <c r="F29">
-        <v>30.9042</v>
+        <v>32.0488</v>
       </c>
       <c r="G29">
         <v>7.43</v>
@@ -3665,28 +3665,28 @@
         <v>14.36</v>
       </c>
       <c r="M29">
-        <v>1.6533747</v>
+        <v>1.7146108</v>
       </c>
       <c r="N29">
-        <v>12.7066253</v>
+        <v>12.6453892</v>
       </c>
       <c r="O29">
-        <v>2.795457566</v>
+        <v>2.781985624</v>
       </c>
       <c r="P29">
-        <v>9.911167733999999</v>
+        <v>9.863403576</v>
       </c>
       <c r="Q29">
-        <v>13.251167734</v>
+        <v>13.203403576</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1029632550177317</v>
+        <v>0.1036216311563936</v>
       </c>
       <c r="T29">
-        <v>0.9638546015663489</v>
+        <v>0.974955769101577</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.685266564197455</v>
+        <v>8.375078472618977</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0862919744326034</v>
+        <v>0.08615367270226269</v>
       </c>
       <c r="C30">
-        <v>92.21682282005142</v>
+        <v>91.47264656637731</v>
       </c>
       <c r="D30">
-        <v>116.8356228200514</v>
+        <v>117.2360465663773</v>
       </c>
       <c r="E30">
-        <v>28.8888</v>
+        <v>30.0334</v>
       </c>
       <c r="F30">
-        <v>32.0488</v>
+        <v>33.1934</v>
       </c>
       <c r="G30">
         <v>7.43</v>
@@ -3747,28 +3747,28 @@
         <v>14.36</v>
       </c>
       <c r="M30">
-        <v>1.7146108</v>
+        <v>1.7758469</v>
       </c>
       <c r="N30">
-        <v>12.6453892</v>
+        <v>12.5841531</v>
       </c>
       <c r="O30">
-        <v>2.781985624</v>
+        <v>2.768513682</v>
       </c>
       <c r="P30">
-        <v>9.863403576</v>
+        <v>9.815639418</v>
       </c>
       <c r="Q30">
-        <v>13.203403576</v>
+        <v>13.155639418</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1036216311563936</v>
+        <v>0.1042985531017784</v>
       </c>
       <c r="T30">
-        <v>0.974955769101577</v>
+        <v>0.9863696455814592</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.375078472618977</v>
+        <v>8.08628266321832</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08615367270226268</v>
+        <v>0.08601537097192198</v>
       </c>
       <c r="C31">
-        <v>91.47264656637734</v>
+        <v>90.73122444852973</v>
       </c>
       <c r="D31">
-        <v>117.2360465663773</v>
+        <v>117.6392244485297</v>
       </c>
       <c r="E31">
-        <v>30.0334</v>
+        <v>31.17799999999999</v>
       </c>
       <c r="F31">
-        <v>33.1934</v>
+        <v>34.33799999999999</v>
       </c>
       <c r="G31">
         <v>7.43</v>
@@ -3829,28 +3829,28 @@
         <v>14.36</v>
       </c>
       <c r="M31">
-        <v>1.7758469</v>
+        <v>1.837083</v>
       </c>
       <c r="N31">
-        <v>12.5841531</v>
+        <v>12.522917</v>
       </c>
       <c r="O31">
-        <v>2.768513682</v>
+        <v>2.75504174</v>
       </c>
       <c r="P31">
-        <v>9.815639418</v>
+        <v>9.76787526</v>
       </c>
       <c r="Q31">
-        <v>13.155639418</v>
+        <v>13.10787526</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1042985531017784</v>
+        <v>0.1049948156741743</v>
       </c>
       <c r="T31">
-        <v>0.9863696455814592</v>
+        <v>0.9981096328179097</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.086282663218322</v>
+        <v>7.816739907777712</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08601537097192198</v>
+        <v>0.08607050924158126</v>
       </c>
       <c r="C32">
-        <v>90.73122444852973</v>
+        <v>89.42555314840686</v>
       </c>
       <c r="D32">
-        <v>117.6392244485297</v>
+        <v>117.4781531484069</v>
       </c>
       <c r="E32">
-        <v>31.17799999999999</v>
+        <v>32.32259999999999</v>
       </c>
       <c r="F32">
-        <v>34.33799999999999</v>
+        <v>35.4826</v>
       </c>
       <c r="G32">
         <v>7.43</v>
@@ -3911,45 +3911,45 @@
         <v>14.36</v>
       </c>
       <c r="M32">
-        <v>1.837083</v>
+        <v>1.92670518</v>
       </c>
       <c r="N32">
-        <v>12.522917</v>
+        <v>12.43329482</v>
       </c>
       <c r="O32">
-        <v>2.75504174</v>
+        <v>2.7353248604</v>
       </c>
       <c r="P32">
-        <v>9.76787526</v>
+        <v>9.6979699596</v>
       </c>
       <c r="Q32">
-        <v>13.10787526</v>
+        <v>13.0379699596</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1049948156741743</v>
+        <v>0.1057112597704076</v>
       </c>
       <c r="T32">
-        <v>0.9981096328179097</v>
+        <v>1.010189909539475</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.816739907777712</v>
+        <v>7.453138211835815</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08607050924158126</v>
+        <v>0.08593844751124055</v>
       </c>
       <c r="C33">
-        <v>89.42555314840686</v>
+        <v>88.66747452987447</v>
       </c>
       <c r="D33">
-        <v>117.4781531484069</v>
+        <v>117.8646745298745</v>
       </c>
       <c r="E33">
-        <v>32.32259999999999</v>
+        <v>33.46720000000001</v>
       </c>
       <c r="F33">
-        <v>35.4826</v>
+        <v>36.6272</v>
       </c>
       <c r="G33">
         <v>7.43</v>
@@ -3993,28 +3993,28 @@
         <v>14.36</v>
       </c>
       <c r="M33">
-        <v>1.92670518</v>
+        <v>1.98885696</v>
       </c>
       <c r="N33">
-        <v>12.43329482</v>
+        <v>12.37114304</v>
       </c>
       <c r="O33">
-        <v>2.7353248604</v>
+        <v>2.7216514688</v>
       </c>
       <c r="P33">
-        <v>9.6979699596</v>
+        <v>9.6494915712</v>
       </c>
       <c r="Q33">
-        <v>13.0379699596</v>
+        <v>12.9894915712</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1057112597704076</v>
+        <v>0.1064487757518243</v>
       </c>
       <c r="T33">
-        <v>1.010189909539475</v>
+        <v>1.022625488517556</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.453138211835815</v>
+        <v>7.220227642715944</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08593844751124055</v>
+        <v>0.08580638578089983</v>
       </c>
       <c r="C34">
-        <v>88.66747452987447</v>
+        <v>87.91194773807943</v>
       </c>
       <c r="D34">
-        <v>117.8646745298745</v>
+        <v>118.2537477380794</v>
       </c>
       <c r="E34">
-        <v>33.46720000000001</v>
+        <v>34.6118</v>
       </c>
       <c r="F34">
-        <v>36.6272</v>
+        <v>37.7718</v>
       </c>
       <c r="G34">
         <v>7.43</v>
@@ -4075,28 +4075,28 @@
         <v>14.36</v>
       </c>
       <c r="M34">
-        <v>1.98885696</v>
+        <v>2.05100874</v>
       </c>
       <c r="N34">
-        <v>12.37114304</v>
+        <v>12.30899126</v>
       </c>
       <c r="O34">
-        <v>2.7216514688</v>
+        <v>2.7079780772</v>
       </c>
       <c r="P34">
-        <v>9.6494915712</v>
+        <v>9.601013182799999</v>
       </c>
       <c r="Q34">
-        <v>12.9894915712</v>
+        <v>12.9410131828</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064487757518243</v>
+        <v>0.1072083071356714</v>
       </c>
       <c r="T34">
-        <v>1.022625488517556</v>
+        <v>1.035432278808416</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.220227642715944</v>
+        <v>7.001432865663946</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08580638578089983</v>
+        <v>0.08567432405055911</v>
       </c>
       <c r="C35">
-        <v>87.91194773807943</v>
+        <v>87.15899812758232</v>
       </c>
       <c r="D35">
-        <v>118.2537477380794</v>
+        <v>118.6453981275823</v>
       </c>
       <c r="E35">
-        <v>34.6118</v>
+        <v>35.7564</v>
       </c>
       <c r="F35">
-        <v>37.7718</v>
+        <v>38.9164</v>
       </c>
       <c r="G35">
         <v>7.43</v>
@@ -4157,28 +4157,28 @@
         <v>14.36</v>
       </c>
       <c r="M35">
-        <v>2.05100874</v>
+        <v>2.11316052</v>
       </c>
       <c r="N35">
-        <v>12.30899126</v>
+        <v>12.24683948</v>
       </c>
       <c r="O35">
-        <v>2.7079780772</v>
+        <v>2.6943046856</v>
       </c>
       <c r="P35">
-        <v>9.601013182799999</v>
+        <v>9.5525347944</v>
       </c>
       <c r="Q35">
-        <v>12.9410131828</v>
+        <v>12.8925347944</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1072083071356714</v>
+        <v>0.1079908546220593</v>
       </c>
       <c r="T35">
-        <v>1.035432278808416</v>
+        <v>1.048627153653545</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.001432865663946</v>
+        <v>6.795508369615006</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08567432405055911</v>
+        <v>0.0855422623202184</v>
       </c>
       <c r="C36">
-        <v>87.15899812758232</v>
+        <v>86.40865138995184</v>
       </c>
       <c r="D36">
-        <v>118.6453981275823</v>
+        <v>119.0396513899518</v>
       </c>
       <c r="E36">
-        <v>35.7564</v>
+        <v>36.901</v>
       </c>
       <c r="F36">
-        <v>38.9164</v>
+        <v>40.061</v>
       </c>
       <c r="G36">
         <v>7.43</v>
@@ -4239,28 +4239,28 @@
         <v>14.36</v>
       </c>
       <c r="M36">
-        <v>2.11316052</v>
+        <v>2.1753123</v>
       </c>
       <c r="N36">
-        <v>12.24683948</v>
+        <v>12.1846877</v>
       </c>
       <c r="O36">
-        <v>2.6943046856</v>
+        <v>2.680631294</v>
       </c>
       <c r="P36">
-        <v>9.5525347944</v>
+        <v>9.504056406</v>
       </c>
       <c r="Q36">
-        <v>12.8925347944</v>
+        <v>12.844056406</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1079908546220593</v>
+        <v>0.1087974804926437</v>
       </c>
       <c r="T36">
-        <v>1.048627153653545</v>
+        <v>1.062228024647754</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.795508369615006</v>
+        <v>6.601350987626007</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0855422623202184</v>
+        <v>0.08541020058987768</v>
       </c>
       <c r="C37">
-        <v>86.40865138995184</v>
+        <v>85.66093355938298</v>
       </c>
       <c r="D37">
-        <v>119.0396513899518</v>
+        <v>119.436533559383</v>
       </c>
       <c r="E37">
-        <v>36.901</v>
+        <v>38.04560000000001</v>
       </c>
       <c r="F37">
-        <v>40.061</v>
+        <v>41.2056</v>
       </c>
       <c r="G37">
         <v>7.43</v>
@@ -4321,28 +4321,28 @@
         <v>14.36</v>
       </c>
       <c r="M37">
-        <v>2.1753123</v>
+        <v>2.23746408</v>
       </c>
       <c r="N37">
-        <v>12.1846877</v>
+        <v>12.12253592</v>
       </c>
       <c r="O37">
-        <v>2.680631294</v>
+        <v>2.6669579024</v>
       </c>
       <c r="P37">
-        <v>9.504056406</v>
+        <v>9.455578017599999</v>
       </c>
       <c r="Q37">
-        <v>12.844056406</v>
+        <v>12.7955780176</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1087974804926437</v>
+        <v>0.1096293134216839</v>
       </c>
       <c r="T37">
-        <v>1.062228024647754</v>
+        <v>1.076253922860533</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.601350987626007</v>
+        <v>6.417980126858617</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08541020058987769</v>
+        <v>0.08527813885953697</v>
       </c>
       <c r="C38">
-        <v>85.66093355938295</v>
+        <v>84.91587101842754</v>
       </c>
       <c r="D38">
-        <v>119.436533559383</v>
+        <v>119.8360710184275</v>
       </c>
       <c r="E38">
-        <v>38.04559999999999</v>
+        <v>39.19019999999999</v>
       </c>
       <c r="F38">
-        <v>41.2056</v>
+        <v>42.35019999999999</v>
       </c>
       <c r="G38">
         <v>7.43</v>
@@ -4403,28 +4403,28 @@
         <v>14.36</v>
       </c>
       <c r="M38">
-        <v>2.23746408</v>
+        <v>2.29961586</v>
       </c>
       <c r="N38">
-        <v>12.12253592</v>
+        <v>12.06038414</v>
       </c>
       <c r="O38">
-        <v>2.6669579024</v>
+        <v>2.6532845108</v>
       </c>
       <c r="P38">
-        <v>9.455578017599999</v>
+        <v>9.407099629200001</v>
       </c>
       <c r="Q38">
-        <v>12.7955780176</v>
+        <v>12.7470996292</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1096293134216839</v>
+        <v>0.1104875537452968</v>
       </c>
       <c r="T38">
-        <v>1.076253922860532</v>
+        <v>1.09072508768324</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.417980126858617</v>
+        <v>6.244521204511088</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08527813885953697</v>
+        <v>0.08544247712919625</v>
       </c>
       <c r="C39">
-        <v>84.91587101842754</v>
+        <v>83.27448943513363</v>
       </c>
       <c r="D39">
-        <v>119.8360710184275</v>
+        <v>119.3392894351336</v>
       </c>
       <c r="E39">
-        <v>39.19019999999999</v>
+        <v>40.3348</v>
       </c>
       <c r="F39">
-        <v>42.35019999999999</v>
+        <v>43.4948</v>
       </c>
       <c r="G39">
         <v>7.43</v>
@@ -4485,45 +4485,45 @@
         <v>14.36</v>
       </c>
       <c r="M39">
-        <v>2.29961586</v>
+        <v>2.40526244</v>
       </c>
       <c r="N39">
-        <v>12.06038414</v>
+        <v>11.95473756</v>
       </c>
       <c r="O39">
-        <v>2.6532845108</v>
+        <v>2.6300422632</v>
       </c>
       <c r="P39">
-        <v>9.407099629200001</v>
+        <v>9.3246952968</v>
       </c>
       <c r="Q39">
-        <v>12.7470996292</v>
+        <v>12.6646952968</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1104875537452968</v>
+        <v>0.1113734792406391</v>
       </c>
       <c r="T39">
-        <v>1.09072508768324</v>
+        <v>1.105663064274423</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.244521204511088</v>
+        <v>5.970242482146771</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08544247712919625</v>
+        <v>0.08531821539885553</v>
       </c>
       <c r="C40">
-        <v>83.27448943513363</v>
+        <v>82.50514187133732</v>
       </c>
       <c r="D40">
-        <v>119.3392894351336</v>
+        <v>119.7145418713373</v>
       </c>
       <c r="E40">
-        <v>40.3348</v>
+        <v>41.4794</v>
       </c>
       <c r="F40">
-        <v>43.4948</v>
+        <v>44.6394</v>
       </c>
       <c r="G40">
         <v>7.43</v>
@@ -4567,28 +4567,28 @@
         <v>14.36</v>
       </c>
       <c r="M40">
-        <v>2.40526244</v>
+        <v>2.46855882</v>
       </c>
       <c r="N40">
-        <v>11.95473756</v>
+        <v>11.89144118</v>
       </c>
       <c r="O40">
-        <v>2.6300422632</v>
+        <v>2.6161170596</v>
       </c>
       <c r="P40">
-        <v>9.3246952968</v>
+        <v>9.275324120399999</v>
       </c>
       <c r="Q40">
-        <v>12.6646952968</v>
+        <v>12.6153241204</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1113734792406391</v>
+        <v>0.1122884514735337</v>
       </c>
       <c r="T40">
-        <v>1.105663064274423</v>
+        <v>1.121090810589906</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.970242482146771</v>
+        <v>5.817159341578905</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08531821539885553</v>
+        <v>0.08519395366851483</v>
       </c>
       <c r="C41">
-        <v>82.50514187133732</v>
+        <v>81.73816165139422</v>
       </c>
       <c r="D41">
-        <v>119.7145418713373</v>
+        <v>120.0921616513942</v>
       </c>
       <c r="E41">
-        <v>41.4794</v>
+        <v>42.624</v>
       </c>
       <c r="F41">
-        <v>44.6394</v>
+        <v>45.784</v>
       </c>
       <c r="G41">
         <v>7.43</v>
@@ -4649,28 +4649,28 @@
         <v>14.36</v>
       </c>
       <c r="M41">
-        <v>2.46855882</v>
+        <v>2.5318552</v>
       </c>
       <c r="N41">
-        <v>11.89144118</v>
+        <v>11.8281448</v>
       </c>
       <c r="O41">
-        <v>2.6161170596</v>
+        <v>2.602191856</v>
       </c>
       <c r="P41">
-        <v>9.275324120399999</v>
+        <v>9.225952943999999</v>
       </c>
       <c r="Q41">
-        <v>12.6153241204</v>
+        <v>12.565952944</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1122884514735337</v>
+        <v>0.113233922780858</v>
       </c>
       <c r="T41">
-        <v>1.121090810589906</v>
+        <v>1.137032815115905</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.817159341578905</v>
+        <v>5.671730358039433</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08519395366851483</v>
+        <v>0.08506969193817412</v>
       </c>
       <c r="C42">
-        <v>81.73816165139422</v>
+        <v>80.9735712483794</v>
       </c>
       <c r="D42">
-        <v>120.0921616513942</v>
+        <v>120.4721712483794</v>
       </c>
       <c r="E42">
-        <v>42.624</v>
+        <v>43.76860000000001</v>
       </c>
       <c r="F42">
-        <v>45.784</v>
+        <v>46.9286</v>
       </c>
       <c r="G42">
         <v>7.43</v>
@@ -4731,28 +4731,28 @@
         <v>14.36</v>
       </c>
       <c r="M42">
-        <v>2.5318552</v>
+        <v>2.59515158</v>
       </c>
       <c r="N42">
-        <v>11.8281448</v>
+        <v>11.76484842</v>
       </c>
       <c r="O42">
-        <v>2.602191856</v>
+        <v>2.5882666524</v>
       </c>
       <c r="P42">
-        <v>9.225952943999999</v>
+        <v>9.1765817676</v>
       </c>
       <c r="Q42">
-        <v>12.565952944</v>
+        <v>12.5165817676</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.113233922780858</v>
+        <v>0.114211443963007</v>
       </c>
       <c r="T42">
-        <v>1.137032815115905</v>
+        <v>1.15351522657499</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.671730358039433</v>
+        <v>5.533395471257982</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08506969193817412</v>
+        <v>0.08494543020783341</v>
       </c>
       <c r="C43">
-        <v>80.9735712483794</v>
+        <v>80.21139342071847</v>
       </c>
       <c r="D43">
-        <v>120.4721712483794</v>
+        <v>120.8545934207185</v>
       </c>
       <c r="E43">
-        <v>43.76860000000001</v>
+        <v>44.9132</v>
       </c>
       <c r="F43">
-        <v>46.9286</v>
+        <v>48.0732</v>
       </c>
       <c r="G43">
         <v>7.43</v>
@@ -4813,28 +4813,28 @@
         <v>14.36</v>
       </c>
       <c r="M43">
-        <v>2.59515158</v>
+        <v>2.65844796</v>
       </c>
       <c r="N43">
-        <v>11.76484842</v>
+        <v>11.70155204</v>
       </c>
       <c r="O43">
-        <v>2.5882666524</v>
+        <v>2.5743414488</v>
       </c>
       <c r="P43">
-        <v>9.1765817676</v>
+        <v>9.127210591199999</v>
       </c>
       <c r="Q43">
-        <v>12.5165817676</v>
+        <v>12.4672105912</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.114211443963007</v>
+        <v>0.1152226727721266</v>
       </c>
       <c r="T43">
-        <v>1.15351522657499</v>
+        <v>1.170565997049905</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.533395471257982</v>
+        <v>5.401647960037555</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08494543020783341</v>
+        <v>0.08482116847749269</v>
       </c>
       <c r="C44">
-        <v>80.21139342071848</v>
+        <v>79.45165121673104</v>
       </c>
       <c r="D44">
-        <v>120.8545934207185</v>
+        <v>121.239451216731</v>
       </c>
       <c r="E44">
-        <v>44.91319999999999</v>
+        <v>46.0578</v>
       </c>
       <c r="F44">
-        <v>48.07319999999999</v>
+        <v>49.2178</v>
       </c>
       <c r="G44">
         <v>7.43</v>
@@ -4895,28 +4895,28 @@
         <v>14.36</v>
       </c>
       <c r="M44">
-        <v>2.65844796</v>
+        <v>2.72174434</v>
       </c>
       <c r="N44">
-        <v>11.70155204</v>
+        <v>11.63825566</v>
       </c>
       <c r="O44">
-        <v>2.5743414488</v>
+        <v>2.5604162452</v>
       </c>
       <c r="P44">
-        <v>9.127210591199999</v>
+        <v>9.0778394148</v>
       </c>
       <c r="Q44">
-        <v>12.4672105912</v>
+        <v>12.4178394148</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1152226727721266</v>
+        <v>0.1162693832938468</v>
       </c>
       <c r="T44">
-        <v>1.170565997049905</v>
+        <v>1.188215040173062</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.401647960037556</v>
+        <v>5.276028240036681</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08482116847749269</v>
+        <v>0.08469690674715197</v>
       </c>
       <c r="C45">
-        <v>79.45165121673104</v>
+        <v>78.69436797926133</v>
       </c>
       <c r="D45">
-        <v>121.239451216731</v>
+        <v>121.6267679792613</v>
       </c>
       <c r="E45">
-        <v>46.0578</v>
+        <v>47.2024</v>
       </c>
       <c r="F45">
-        <v>49.2178</v>
+        <v>50.3624</v>
       </c>
       <c r="G45">
         <v>7.43</v>
@@ -4977,28 +4977,28 @@
         <v>14.36</v>
       </c>
       <c r="M45">
-        <v>2.72174434</v>
+        <v>2.78504072</v>
       </c>
       <c r="N45">
-        <v>11.63825566</v>
+        <v>11.57495928</v>
       </c>
       <c r="O45">
-        <v>2.5604162452</v>
+        <v>2.5464910416</v>
       </c>
       <c r="P45">
-        <v>9.0778394148</v>
+        <v>9.0284682384</v>
       </c>
       <c r="Q45">
-        <v>12.4178394148</v>
+        <v>12.3684682384</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1162693832938468</v>
+        <v>0.1173534763341999</v>
       </c>
       <c r="T45">
-        <v>1.188215040173062</v>
+        <v>1.206494406264904</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.276028240036681</v>
+        <v>5.156118507308575</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08469690674715197</v>
+        <v>0.08457264501681125</v>
       </c>
       <c r="C46">
-        <v>78.69436797926133</v>
+        <v>77.93956735039785</v>
       </c>
       <c r="D46">
-        <v>121.6267679792613</v>
+        <v>122.0165673503978</v>
       </c>
       <c r="E46">
-        <v>47.2024</v>
+        <v>48.34699999999999</v>
       </c>
       <c r="F46">
-        <v>50.3624</v>
+        <v>51.507</v>
       </c>
       <c r="G46">
         <v>7.43</v>
@@ -5059,28 +5059,28 @@
         <v>14.36</v>
       </c>
       <c r="M46">
-        <v>2.78504072</v>
+        <v>2.8483371</v>
       </c>
       <c r="N46">
-        <v>11.57495928</v>
+        <v>11.5116629</v>
       </c>
       <c r="O46">
-        <v>2.5464910416</v>
+        <v>2.532565838</v>
       </c>
       <c r="P46">
-        <v>9.0284682384</v>
+        <v>8.979097061999999</v>
       </c>
       <c r="Q46">
-        <v>12.3684682384</v>
+        <v>12.319097062</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1173534763341999</v>
+        <v>0.1184769909396568</v>
       </c>
       <c r="T46">
-        <v>1.206494406264904</v>
+        <v>1.225438476578267</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.156118507308575</v>
+        <v>5.041538096035051</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08457264501681125</v>
+        <v>0.08444838328647053</v>
       </c>
       <c r="C47">
-        <v>77.93956735039785</v>
+        <v>77.18727327628383</v>
       </c>
       <c r="D47">
-        <v>122.0165673503978</v>
+        <v>122.4088732762838</v>
       </c>
       <c r="E47">
-        <v>48.34699999999999</v>
+        <v>49.49160000000001</v>
       </c>
       <c r="F47">
-        <v>51.507</v>
+        <v>52.6516</v>
       </c>
       <c r="G47">
         <v>7.43</v>
@@ -5141,28 +5141,28 @@
         <v>14.36</v>
       </c>
       <c r="M47">
-        <v>2.8483371</v>
+        <v>2.91163348</v>
       </c>
       <c r="N47">
-        <v>11.5116629</v>
+        <v>11.44836652</v>
       </c>
       <c r="O47">
-        <v>2.532565838</v>
+        <v>2.5186406344</v>
       </c>
       <c r="P47">
-        <v>8.979097061999999</v>
+        <v>8.9297258856</v>
       </c>
       <c r="Q47">
-        <v>12.319097062</v>
+        <v>12.2697258856</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1184769909396568</v>
+        <v>0.1196421171971676</v>
       </c>
       <c r="T47">
-        <v>1.225438476578267</v>
+        <v>1.245084179125458</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.041538096035051</v>
+        <v>4.931939441773419</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08444838328647053</v>
+        <v>0.08432412155612981</v>
       </c>
       <c r="C48">
-        <v>77.18727327628383</v>
+        <v>76.43751001202114</v>
       </c>
       <c r="D48">
-        <v>122.4088732762838</v>
+        <v>122.8037100120211</v>
       </c>
       <c r="E48">
-        <v>49.49160000000001</v>
+        <v>50.6362</v>
       </c>
       <c r="F48">
-        <v>52.6516</v>
+        <v>53.7962</v>
       </c>
       <c r="G48">
         <v>7.43</v>
@@ -5223,28 +5223,28 @@
         <v>14.36</v>
       </c>
       <c r="M48">
-        <v>2.91163348</v>
+        <v>2.97492986</v>
       </c>
       <c r="N48">
-        <v>11.44836652</v>
+        <v>11.38507014</v>
       </c>
       <c r="O48">
-        <v>2.5186406344</v>
+        <v>2.5047154308</v>
       </c>
       <c r="P48">
-        <v>8.9297258856</v>
+        <v>8.880354709199999</v>
       </c>
       <c r="Q48">
-        <v>12.2697258856</v>
+        <v>12.2203547092</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1196421171971676</v>
+        <v>0.1208512104832638</v>
       </c>
       <c r="T48">
-        <v>1.245084179125458</v>
+        <v>1.265471228938581</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.931939441773419</v>
+        <v>4.82700456003356</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08432412155612981</v>
+        <v>0.08419985982578912</v>
       </c>
       <c r="C49">
-        <v>76.43751001202114</v>
+        <v>75.69030212666894</v>
       </c>
       <c r="D49">
-        <v>122.8037100120211</v>
+        <v>123.2011021266689</v>
       </c>
       <c r="E49">
-        <v>50.6362</v>
+        <v>51.7808</v>
       </c>
       <c r="F49">
-        <v>53.7962</v>
+        <v>54.9408</v>
       </c>
       <c r="G49">
         <v>7.43</v>
@@ -5305,28 +5305,28 @@
         <v>14.36</v>
       </c>
       <c r="M49">
-        <v>2.97492986</v>
+        <v>3.03822624</v>
       </c>
       <c r="N49">
-        <v>11.38507014</v>
+        <v>11.32177376</v>
       </c>
       <c r="O49">
-        <v>2.5047154308</v>
+        <v>2.4907902272</v>
       </c>
       <c r="P49">
-        <v>8.880354709199999</v>
+        <v>8.830983532799999</v>
       </c>
       <c r="Q49">
-        <v>12.2203547092</v>
+        <v>12.1709835328</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1208512104832638</v>
+        <v>0.1221068073572867</v>
       </c>
       <c r="T49">
-        <v>1.265471228938581</v>
+        <v>1.286642396052209</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.82700456003356</v>
+        <v>4.72644196503286</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08419985982578909</v>
+        <v>0.08407559809544839</v>
       </c>
       <c r="C50">
-        <v>75.69030212666902</v>
+        <v>74.94567450834066</v>
       </c>
       <c r="D50">
-        <v>123.201102126669</v>
+        <v>123.6010745083406</v>
       </c>
       <c r="E50">
-        <v>51.7808</v>
+        <v>52.9254</v>
       </c>
       <c r="F50">
-        <v>54.9408</v>
+        <v>56.08539999999999</v>
       </c>
       <c r="G50">
         <v>7.43</v>
@@ -5387,28 +5387,28 @@
         <v>14.36</v>
       </c>
       <c r="M50">
-        <v>3.03822624</v>
+        <v>3.10152262</v>
       </c>
       <c r="N50">
-        <v>11.32177376</v>
+        <v>11.25847738</v>
       </c>
       <c r="O50">
-        <v>2.4907902272</v>
+        <v>2.4768650236</v>
       </c>
       <c r="P50">
-        <v>8.830983532799999</v>
+        <v>8.781612356399998</v>
       </c>
       <c r="Q50">
-        <v>12.1709835328</v>
+        <v>12.1216123564</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1221068073572867</v>
+        <v>0.1234116433244086</v>
       </c>
       <c r="T50">
-        <v>1.286642396052209</v>
+        <v>1.30864380501343</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.72644196503286</v>
+        <v>4.629983965746476</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08407559809544839</v>
+        <v>0.08395133636510767</v>
       </c>
       <c r="C51">
-        <v>74.94567450834066</v>
+        <v>74.2036523693989</v>
       </c>
       <c r="D51">
-        <v>123.6010745083406</v>
+        <v>124.0036523693989</v>
       </c>
       <c r="E51">
-        <v>52.9254</v>
+        <v>54.06999999999999</v>
       </c>
       <c r="F51">
-        <v>56.08539999999999</v>
+        <v>57.23</v>
       </c>
       <c r="G51">
         <v>7.43</v>
@@ -5469,28 +5469,28 @@
         <v>14.36</v>
       </c>
       <c r="M51">
-        <v>3.10152262</v>
+        <v>3.164819</v>
       </c>
       <c r="N51">
-        <v>11.25847738</v>
+        <v>11.195181</v>
       </c>
       <c r="O51">
-        <v>2.4768650236</v>
+        <v>2.46293982</v>
       </c>
       <c r="P51">
-        <v>8.781612356399998</v>
+        <v>8.732241179999999</v>
       </c>
       <c r="Q51">
-        <v>12.1216123564</v>
+        <v>12.07224118</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1234116433244086</v>
+        <v>0.1247686727302153</v>
       </c>
       <c r="T51">
-        <v>1.30864380501343</v>
+        <v>1.3315252703331</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.629983965746476</v>
+        <v>4.537384286431546</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08395133636510767</v>
+        <v>0.08482157463476696</v>
       </c>
       <c r="C52">
-        <v>74.2036523693989</v>
+        <v>70.29358929212903</v>
       </c>
       <c r="D52">
-        <v>124.0036523693989</v>
+        <v>121.238189292129</v>
       </c>
       <c r="E52">
-        <v>54.06999999999999</v>
+        <v>55.2146</v>
       </c>
       <c r="F52">
-        <v>57.23</v>
+        <v>58.3746</v>
       </c>
       <c r="G52">
         <v>7.43</v>
@@ -5551,45 +5551,45 @@
         <v>14.36</v>
       </c>
       <c r="M52">
-        <v>3.164819</v>
+        <v>3.37405188</v>
       </c>
       <c r="N52">
-        <v>11.195181</v>
+        <v>10.98594812</v>
       </c>
       <c r="O52">
-        <v>2.46293982</v>
+        <v>2.4169085864</v>
       </c>
       <c r="P52">
-        <v>8.732241179999999</v>
+        <v>8.5690395336</v>
       </c>
       <c r="Q52">
-        <v>12.07224118</v>
+        <v>11.9090395336</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1247686727302153</v>
+        <v>0.1261810910913611</v>
       </c>
       <c r="T52">
-        <v>1.3315252703331</v>
+        <v>1.355340673012757</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.537384286431546</v>
+        <v>4.256010432181025</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08482157463476696</v>
+        <v>0.08471681290442624</v>
       </c>
       <c r="C53">
-        <v>70.29358929212903</v>
+        <v>69.47535523902222</v>
       </c>
       <c r="D53">
-        <v>121.238189292129</v>
+        <v>121.5645552390222</v>
       </c>
       <c r="E53">
-        <v>55.2146</v>
+        <v>56.3592</v>
       </c>
       <c r="F53">
-        <v>58.3746</v>
+        <v>59.5192</v>
       </c>
       <c r="G53">
         <v>7.43</v>
@@ -5633,28 +5633,28 @@
         <v>14.36</v>
       </c>
       <c r="M53">
-        <v>3.37405188</v>
+        <v>3.44020976</v>
       </c>
       <c r="N53">
-        <v>10.98594812</v>
+        <v>10.91979024</v>
       </c>
       <c r="O53">
-        <v>2.4169085864</v>
+        <v>2.4023538528</v>
       </c>
       <c r="P53">
-        <v>8.5690395336</v>
+        <v>8.5174363872</v>
       </c>
       <c r="Q53">
-        <v>11.9090395336</v>
+        <v>11.8574363872</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1261810910913611</v>
+        <v>0.1276523602175547</v>
       </c>
       <c r="T53">
-        <v>1.355340673012757</v>
+        <v>1.380148384137399</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.256010432181025</v>
+        <v>4.174164077716005</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08471681290442624</v>
+        <v>0.08461205117408552</v>
       </c>
       <c r="C54">
-        <v>69.47535523902222</v>
+        <v>68.6588830439099</v>
       </c>
       <c r="D54">
-        <v>121.5645552390222</v>
+        <v>121.8926830439099</v>
       </c>
       <c r="E54">
-        <v>56.3592</v>
+        <v>57.5038</v>
       </c>
       <c r="F54">
-        <v>59.5192</v>
+        <v>60.6638</v>
       </c>
       <c r="G54">
         <v>7.43</v>
@@ -5715,28 +5715,28 @@
         <v>14.36</v>
       </c>
       <c r="M54">
-        <v>3.44020976</v>
+        <v>3.506367640000001</v>
       </c>
       <c r="N54">
-        <v>10.91979024</v>
+        <v>10.85363236</v>
       </c>
       <c r="O54">
-        <v>2.4023538528</v>
+        <v>2.3877991192</v>
       </c>
       <c r="P54">
-        <v>8.5174363872</v>
+        <v>8.465833240799999</v>
       </c>
       <c r="Q54">
-        <v>11.8574363872</v>
+        <v>11.8058332408</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1276523602175547</v>
+        <v>0.1291862365406075</v>
       </c>
       <c r="T54">
-        <v>1.380148384137399</v>
+        <v>1.40601174254394</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.174164077716005</v>
+        <v>4.09540626492891</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08461205117408552</v>
+        <v>0.0845072894437448</v>
       </c>
       <c r="C55">
-        <v>68.6588830439099</v>
+        <v>67.8441870122596</v>
       </c>
       <c r="D55">
-        <v>121.8926830439099</v>
+        <v>122.2225870122596</v>
       </c>
       <c r="E55">
-        <v>57.5038</v>
+        <v>58.6484</v>
       </c>
       <c r="F55">
-        <v>60.6638</v>
+        <v>61.8084</v>
       </c>
       <c r="G55">
         <v>7.43</v>
@@ -5797,28 +5797,28 @@
         <v>14.36</v>
       </c>
       <c r="M55">
-        <v>3.506367640000001</v>
+        <v>3.57252552</v>
       </c>
       <c r="N55">
-        <v>10.85363236</v>
+        <v>10.78747448</v>
       </c>
       <c r="O55">
-        <v>2.3877991192</v>
+        <v>2.3732443856</v>
       </c>
       <c r="P55">
-        <v>8.465833240799999</v>
+        <v>8.414230094400001</v>
       </c>
       <c r="Q55">
-        <v>11.8058332408</v>
+        <v>11.7542300944</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1291862365406075</v>
+        <v>0.1307868031385757</v>
       </c>
       <c r="T55">
-        <v>1.40601174254394</v>
+        <v>1.432999594794245</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.09540626492891</v>
+        <v>4.019565408170968</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0845072894437448</v>
+        <v>0.08590402771340409</v>
       </c>
       <c r="C56">
-        <v>67.8441870122596</v>
+        <v>62.4428334034512</v>
       </c>
       <c r="D56">
-        <v>122.2225870122596</v>
+        <v>117.9658334034512</v>
       </c>
       <c r="E56">
-        <v>58.6484</v>
+        <v>59.79300000000001</v>
       </c>
       <c r="F56">
-        <v>61.8084</v>
+        <v>62.953</v>
       </c>
       <c r="G56">
         <v>7.43</v>
@@ -5879,45 +5879,45 @@
         <v>14.36</v>
       </c>
       <c r="M56">
-        <v>3.57252552</v>
+        <v>3.8590189</v>
       </c>
       <c r="N56">
-        <v>10.78747448</v>
+        <v>10.5009811</v>
       </c>
       <c r="O56">
-        <v>2.3732443856</v>
+        <v>2.310215842</v>
       </c>
       <c r="P56">
-        <v>8.414230094400001</v>
+        <v>8.190765257999999</v>
       </c>
       <c r="Q56">
-        <v>11.7542300944</v>
+        <v>11.530765258</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1307868031385757</v>
+        <v>0.1324585060297869</v>
       </c>
       <c r="T56">
-        <v>1.432999594794245</v>
+        <v>1.461186907144563</v>
       </c>
       <c r="U56">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.019565408170968</v>
+        <v>3.72115306302335</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08590402771340409</v>
+        <v>0.08582656598306337</v>
       </c>
       <c r="C57">
-        <v>62.4428334034512</v>
+        <v>61.52652772128957</v>
       </c>
       <c r="D57">
-        <v>117.9658334034512</v>
+        <v>118.1941277212896</v>
       </c>
       <c r="E57">
-        <v>59.79300000000001</v>
+        <v>60.9376</v>
       </c>
       <c r="F57">
-        <v>62.953</v>
+        <v>64.0976</v>
       </c>
       <c r="G57">
         <v>7.43</v>
@@ -5961,28 +5961,28 @@
         <v>14.36</v>
       </c>
       <c r="M57">
-        <v>3.8590189</v>
+        <v>3.92918288</v>
       </c>
       <c r="N57">
-        <v>10.5009811</v>
+        <v>10.43081712</v>
       </c>
       <c r="O57">
-        <v>2.310215842</v>
+        <v>2.2947797664</v>
       </c>
       <c r="P57">
-        <v>8.190765257999999</v>
+        <v>8.136037353600001</v>
       </c>
       <c r="Q57">
-        <v>11.530765258</v>
+        <v>11.4760373536</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1324585060297869</v>
+        <v>0.1342061954160531</v>
       </c>
       <c r="T57">
-        <v>1.461186907144563</v>
+        <v>1.49065546096535</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.72115306302335</v>
+        <v>3.654703901183648</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08582656598306337</v>
+        <v>0.08574910425272267</v>
       </c>
       <c r="C58">
-        <v>61.52652772128957</v>
+        <v>60.61110736926074</v>
       </c>
       <c r="D58">
-        <v>118.1941277212896</v>
+        <v>118.4233073692607</v>
       </c>
       <c r="E58">
-        <v>60.9376</v>
+        <v>62.0822</v>
       </c>
       <c r="F58">
-        <v>64.0976</v>
+        <v>65.2422</v>
       </c>
       <c r="G58">
         <v>7.43</v>
@@ -6043,28 +6043,28 @@
         <v>14.36</v>
       </c>
       <c r="M58">
-        <v>3.92918288</v>
+        <v>3.99934686</v>
       </c>
       <c r="N58">
-        <v>10.43081712</v>
+        <v>10.36065314</v>
       </c>
       <c r="O58">
-        <v>2.2947797664</v>
+        <v>2.2793436908</v>
       </c>
       <c r="P58">
-        <v>8.136037353600001</v>
+        <v>8.081309449199999</v>
       </c>
       <c r="Q58">
-        <v>11.4760373536</v>
+        <v>11.4213094492</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1342061954160531</v>
+        <v>0.1360351726807504</v>
       </c>
       <c r="T58">
-        <v>1.49065546096535</v>
+        <v>1.521494645196406</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.654703901183648</v>
+        <v>3.59058628888218</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08574910425272267</v>
+        <v>0.08567164252238194</v>
       </c>
       <c r="C59">
-        <v>60.61110736926074</v>
+        <v>59.69657750736316</v>
       </c>
       <c r="D59">
-        <v>118.4233073692607</v>
+        <v>118.6533775073632</v>
       </c>
       <c r="E59">
-        <v>62.0822</v>
+        <v>63.22680000000001</v>
       </c>
       <c r="F59">
-        <v>65.2422</v>
+        <v>66.38680000000001</v>
       </c>
       <c r="G59">
         <v>7.43</v>
@@ -6125,28 +6125,28 @@
         <v>14.36</v>
       </c>
       <c r="M59">
-        <v>3.99934686</v>
+        <v>4.06951084</v>
       </c>
       <c r="N59">
-        <v>10.36065314</v>
+        <v>10.29048916</v>
       </c>
       <c r="O59">
-        <v>2.2793436908</v>
+        <v>2.2639076152</v>
       </c>
       <c r="P59">
-        <v>8.081309449199999</v>
+        <v>8.026581544799999</v>
       </c>
       <c r="Q59">
-        <v>11.4213094492</v>
+        <v>11.3665815448</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1360351726807504</v>
+        <v>0.1379512441009094</v>
       </c>
       <c r="T59">
-        <v>1.521494645196406</v>
+        <v>1.553802362009894</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.59058628888218</v>
+        <v>3.528679628729039</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08567164252238194</v>
+        <v>0.08688274079204122</v>
       </c>
       <c r="C60">
-        <v>59.69657750736317</v>
+        <v>55.05413638435229</v>
       </c>
       <c r="D60">
-        <v>118.6533775073632</v>
+        <v>115.1555363843523</v>
       </c>
       <c r="E60">
-        <v>63.2268</v>
+        <v>64.37139999999999</v>
       </c>
       <c r="F60">
-        <v>66.38679999999999</v>
+        <v>67.53139999999999</v>
       </c>
       <c r="G60">
         <v>7.43</v>
@@ -6207,45 +6207,45 @@
         <v>14.36</v>
       </c>
       <c r="M60">
-        <v>4.06951084</v>
+        <v>4.328762739999999</v>
       </c>
       <c r="N60">
-        <v>10.29048916</v>
+        <v>10.03123726</v>
       </c>
       <c r="O60">
-        <v>2.2639076152</v>
+        <v>2.2068721972</v>
       </c>
       <c r="P60">
-        <v>8.026581544799999</v>
+        <v>7.824365062800001</v>
       </c>
       <c r="Q60">
-        <v>11.3665815448</v>
+        <v>11.1643650628</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1379512441009094</v>
+        <v>0.1399607824196127</v>
       </c>
       <c r="T60">
-        <v>1.553802362009893</v>
+        <v>1.587686065009404</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.22</v>
       </c>
       <c r="W60">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.528679628729039</v>
+        <v>3.317345131278782</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08688274079204122</v>
+        <v>0.08682711906170051</v>
       </c>
       <c r="C61">
-        <v>55.05413638435229</v>
+        <v>54.06565629573038</v>
       </c>
       <c r="D61">
-        <v>115.1555363843523</v>
+        <v>115.3116562957304</v>
       </c>
       <c r="E61">
-        <v>64.37139999999999</v>
+        <v>65.51599999999999</v>
       </c>
       <c r="F61">
-        <v>67.53139999999999</v>
+        <v>68.67599999999999</v>
       </c>
       <c r="G61">
         <v>7.43</v>
@@ -6289,28 +6289,28 @@
         <v>14.36</v>
       </c>
       <c r="M61">
-        <v>4.328762739999999</v>
+        <v>4.4021316</v>
       </c>
       <c r="N61">
-        <v>10.03123726</v>
+        <v>9.957868399999999</v>
       </c>
       <c r="O61">
-        <v>2.2068721972</v>
+        <v>2.190731048</v>
       </c>
       <c r="P61">
-        <v>7.824365062800001</v>
+        <v>7.767137351999999</v>
       </c>
       <c r="Q61">
-        <v>11.1643650628</v>
+        <v>11.107137352</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1399607824196127</v>
+        <v>0.1420707976542513</v>
       </c>
       <c r="T61">
-        <v>1.587686065009404</v>
+        <v>1.623263953158891</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.317345131278782</v>
+        <v>3.262056045757469</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08682711906170051</v>
+        <v>0.08677149733135979</v>
       </c>
       <c r="C62">
-        <v>54.06565629573038</v>
+        <v>53.07760009494156</v>
       </c>
       <c r="D62">
-        <v>115.3116562957304</v>
+        <v>115.4682000949416</v>
       </c>
       <c r="E62">
-        <v>65.51599999999999</v>
+        <v>66.6606</v>
       </c>
       <c r="F62">
-        <v>68.67599999999999</v>
+        <v>69.8206</v>
       </c>
       <c r="G62">
         <v>7.43</v>
@@ -6371,28 +6371,28 @@
         <v>14.36</v>
       </c>
       <c r="M62">
-        <v>4.4021316</v>
+        <v>4.47550046</v>
       </c>
       <c r="N62">
-        <v>9.957868399999999</v>
+        <v>9.88449954</v>
       </c>
       <c r="O62">
-        <v>2.190731048</v>
+        <v>2.1745898988</v>
       </c>
       <c r="P62">
-        <v>7.767137351999999</v>
+        <v>7.7099096412</v>
       </c>
       <c r="Q62">
-        <v>11.107137352</v>
+        <v>11.0499096412</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1420707976542513</v>
+        <v>0.1442890187983584</v>
       </c>
       <c r="T62">
-        <v>1.623263953158891</v>
+        <v>1.660666348392967</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.262056045757469</v>
+        <v>3.208579717138494</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08677149733135979</v>
+        <v>0.08671587560101908</v>
       </c>
       <c r="C63">
-        <v>53.07760009494156</v>
+        <v>52.08996951070664</v>
       </c>
       <c r="D63">
-        <v>115.4682000949416</v>
+        <v>115.6251695107066</v>
       </c>
       <c r="E63">
-        <v>66.6606</v>
+        <v>67.8052</v>
       </c>
       <c r="F63">
-        <v>69.8206</v>
+        <v>70.9652</v>
       </c>
       <c r="G63">
         <v>7.43</v>
@@ -6453,28 +6453,28 @@
         <v>14.36</v>
       </c>
       <c r="M63">
-        <v>4.47550046</v>
+        <v>4.54886932</v>
       </c>
       <c r="N63">
-        <v>9.88449954</v>
+        <v>9.81113068</v>
       </c>
       <c r="O63">
-        <v>2.1745898988</v>
+        <v>2.1584487496</v>
       </c>
       <c r="P63">
-        <v>7.7099096412</v>
+        <v>7.6526819304</v>
       </c>
       <c r="Q63">
-        <v>11.0499096412</v>
+        <v>10.9926819304</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1442890187983584</v>
+        <v>0.1466239884237344</v>
       </c>
       <c r="T63">
-        <v>1.660666348392967</v>
+        <v>1.700037290744626</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.208579717138494</v>
+        <v>3.156828431378196</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08671587560101908</v>
+        <v>0.08666025387067838</v>
       </c>
       <c r="C64">
-        <v>52.08996951070664</v>
+        <v>51.10276628115933</v>
       </c>
       <c r="D64">
-        <v>115.6251695107066</v>
+        <v>115.7825662811593</v>
       </c>
       <c r="E64">
-        <v>67.8052</v>
+        <v>68.9498</v>
       </c>
       <c r="F64">
-        <v>70.9652</v>
+        <v>72.10979999999999</v>
       </c>
       <c r="G64">
         <v>7.43</v>
@@ -6535,28 +6535,28 @@
         <v>14.36</v>
       </c>
       <c r="M64">
-        <v>4.54886932</v>
+        <v>4.62223818</v>
       </c>
       <c r="N64">
-        <v>9.81113068</v>
+        <v>9.737761819999999</v>
       </c>
       <c r="O64">
-        <v>2.1584487496</v>
+        <v>2.1423076004</v>
       </c>
       <c r="P64">
-        <v>7.6526819304</v>
+        <v>7.5954542196</v>
       </c>
       <c r="Q64">
-        <v>10.9926819304</v>
+        <v>10.9354542196</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1466239884237344</v>
+        <v>0.1490851726234551</v>
       </c>
       <c r="T64">
-        <v>1.700037290744626</v>
+        <v>1.741536392142321</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.156828431378196</v>
+        <v>3.106720043578542</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08666025387067838</v>
+        <v>0.08660463214033765</v>
       </c>
       <c r="C65">
-        <v>51.10276628115933</v>
+        <v>50.11599215391075</v>
       </c>
       <c r="D65">
-        <v>115.7825662811593</v>
+        <v>115.9403921539108</v>
       </c>
       <c r="E65">
-        <v>68.9498</v>
+        <v>70.09440000000001</v>
       </c>
       <c r="F65">
-        <v>72.10979999999999</v>
+        <v>73.2544</v>
       </c>
       <c r="G65">
         <v>7.43</v>
@@ -6617,28 +6617,28 @@
         <v>14.36</v>
       </c>
       <c r="M65">
-        <v>4.62223818</v>
+        <v>4.695607040000001</v>
       </c>
       <c r="N65">
-        <v>9.737761819999999</v>
+        <v>9.664392959999999</v>
       </c>
       <c r="O65">
-        <v>2.1423076004</v>
+        <v>2.1261664512</v>
       </c>
       <c r="P65">
-        <v>7.5954542196</v>
+        <v>7.538226508799999</v>
       </c>
       <c r="Q65">
-        <v>10.9354542196</v>
+        <v>10.8782265088</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1490851726234551</v>
+        <v>0.1516830892787157</v>
       </c>
       <c r="T65">
-        <v>1.741536392142321</v>
+        <v>1.78534099917322</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.106720043578542</v>
+        <v>3.058177542897627</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08660463214033765</v>
+        <v>0.08654901040999693</v>
       </c>
       <c r="C66">
-        <v>50.11599215391075</v>
+        <v>49.12964888611347</v>
       </c>
       <c r="D66">
-        <v>115.9403921539108</v>
+        <v>116.0986488861135</v>
       </c>
       <c r="E66">
-        <v>70.09440000000001</v>
+        <v>71.239</v>
       </c>
       <c r="F66">
-        <v>73.2544</v>
+        <v>74.399</v>
       </c>
       <c r="G66">
         <v>7.43</v>
@@ -6699,28 +6699,28 @@
         <v>14.36</v>
       </c>
       <c r="M66">
-        <v>4.695607040000001</v>
+        <v>4.7689759</v>
       </c>
       <c r="N66">
-        <v>9.664392959999999</v>
+        <v>9.591024099999998</v>
       </c>
       <c r="O66">
-        <v>2.1261664512</v>
+        <v>2.110025301999999</v>
       </c>
       <c r="P66">
-        <v>7.538226508799999</v>
+        <v>7.480998797999999</v>
       </c>
       <c r="Q66">
-        <v>10.8782265088</v>
+        <v>10.820998798</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1516830892787157</v>
+        <v>0.154429458314277</v>
       </c>
       <c r="T66">
-        <v>1.78534099917322</v>
+        <v>1.831648726605886</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.058177542897627</v>
+        <v>3.011128657622279</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08654901040999693</v>
+        <v>0.09050882867965622</v>
       </c>
       <c r="C67">
-        <v>49.12964888611347</v>
+        <v>37.70230240138662</v>
       </c>
       <c r="D67">
-        <v>116.0986488861135</v>
+        <v>105.8159024013866</v>
       </c>
       <c r="E67">
-        <v>71.239</v>
+        <v>72.3836</v>
       </c>
       <c r="F67">
-        <v>74.399</v>
+        <v>75.5436</v>
       </c>
       <c r="G67">
         <v>7.43</v>
@@ -6781,45 +6781,45 @@
         <v>14.36</v>
       </c>
       <c r="M67">
-        <v>4.7689759</v>
+        <v>5.43158484</v>
       </c>
       <c r="N67">
-        <v>9.591024099999998</v>
+        <v>8.92841516</v>
       </c>
       <c r="O67">
-        <v>2.110025301999999</v>
+        <v>1.9642513352</v>
       </c>
       <c r="P67">
-        <v>7.480998797999999</v>
+        <v>6.9641638248</v>
       </c>
       <c r="Q67">
-        <v>10.820998798</v>
+        <v>10.3041638248</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.154429458314277</v>
+        <v>0.1573373784695771</v>
       </c>
       <c r="T67">
-        <v>1.831648726605886</v>
+        <v>1.880680438005178</v>
       </c>
       <c r="U67">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.011128657622279</v>
+        <v>2.643795581401616</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09050882867965622</v>
+        <v>0.0905140469493155</v>
       </c>
       <c r="C68">
-        <v>37.70230240138662</v>
+        <v>36.54535335336607</v>
       </c>
       <c r="D68">
-        <v>105.8159024013866</v>
+        <v>105.8035533533661</v>
       </c>
       <c r="E68">
-        <v>72.3836</v>
+        <v>73.5282</v>
       </c>
       <c r="F68">
-        <v>75.5436</v>
+        <v>76.68819999999999</v>
       </c>
       <c r="G68">
         <v>7.43</v>
@@ -6863,28 +6863,28 @@
         <v>14.36</v>
       </c>
       <c r="M68">
-        <v>5.43158484</v>
+        <v>5.51388158</v>
       </c>
       <c r="N68">
-        <v>8.92841516</v>
+        <v>8.84611842</v>
       </c>
       <c r="O68">
-        <v>1.9642513352</v>
+        <v>1.9461460524</v>
       </c>
       <c r="P68">
-        <v>6.9641638248</v>
+        <v>6.8999723676</v>
       </c>
       <c r="Q68">
-        <v>10.3041638248</v>
+        <v>10.2399723676</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1573373784695771</v>
+        <v>0.160421536210047</v>
       </c>
       <c r="T68">
-        <v>1.880680438005178</v>
+        <v>1.932683768277156</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.643795581401616</v>
+        <v>2.604335945858308</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0905140469493155</v>
+        <v>0.0905192652189748</v>
       </c>
       <c r="C69">
-        <v>36.54535335336607</v>
+        <v>35.38840718735445</v>
       </c>
       <c r="D69">
-        <v>105.8035533533661</v>
+        <v>105.7912071873545</v>
       </c>
       <c r="E69">
-        <v>73.5282</v>
+        <v>74.67280000000001</v>
       </c>
       <c r="F69">
-        <v>76.68819999999999</v>
+        <v>77.83280000000001</v>
       </c>
       <c r="G69">
         <v>7.43</v>
@@ -6945,28 +6945,28 @@
         <v>14.36</v>
       </c>
       <c r="M69">
-        <v>5.51388158</v>
+        <v>5.596178320000001</v>
       </c>
       <c r="N69">
-        <v>8.84611842</v>
+        <v>8.76382168</v>
       </c>
       <c r="O69">
-        <v>1.9461460524</v>
+        <v>1.9280407696</v>
       </c>
       <c r="P69">
-        <v>6.8999723676</v>
+        <v>6.8357809104</v>
       </c>
       <c r="Q69">
-        <v>10.2399723676</v>
+        <v>10.1757809104</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.160421536210047</v>
+        <v>0.1636984538092962</v>
       </c>
       <c r="T69">
-        <v>1.932683768277156</v>
+        <v>1.987937306691131</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.604335945858308</v>
+        <v>2.566036887830979</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0905192652189748</v>
+        <v>0.09052448348863408</v>
       </c>
       <c r="C70">
-        <v>35.38840718735445</v>
+        <v>34.23146390234312</v>
       </c>
       <c r="D70">
-        <v>105.7912071873545</v>
+        <v>105.7788639023431</v>
       </c>
       <c r="E70">
-        <v>74.67280000000001</v>
+        <v>75.81740000000001</v>
       </c>
       <c r="F70">
-        <v>77.83280000000001</v>
+        <v>78.9774</v>
       </c>
       <c r="G70">
         <v>7.43</v>
@@ -7027,28 +7027,28 @@
         <v>14.36</v>
       </c>
       <c r="M70">
-        <v>5.596178320000001</v>
+        <v>5.67847506</v>
       </c>
       <c r="N70">
-        <v>8.76382168</v>
+        <v>8.681524939999999</v>
       </c>
       <c r="O70">
-        <v>1.9280407696</v>
+        <v>1.9099354868</v>
       </c>
       <c r="P70">
-        <v>6.8357809104</v>
+        <v>6.771589453199999</v>
       </c>
       <c r="Q70">
-        <v>10.1757809104</v>
+        <v>10.1115894532</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1636984538092962</v>
+        <v>0.1671867854472067</v>
       </c>
       <c r="T70">
-        <v>1.987937306691131</v>
+        <v>2.046755589518912</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.566036887830979</v>
+        <v>2.528847947427632</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09052448348863408</v>
+        <v>0.09265910175829335</v>
       </c>
       <c r="C71">
-        <v>34.23146390234312</v>
+        <v>28.26821636201164</v>
       </c>
       <c r="D71">
-        <v>105.7788639023431</v>
+        <v>100.9602163620116</v>
       </c>
       <c r="E71">
-        <v>75.81740000000001</v>
+        <v>76.962</v>
       </c>
       <c r="F71">
-        <v>78.9774</v>
+        <v>80.122</v>
       </c>
       <c r="G71">
         <v>7.43</v>
@@ -7109,45 +7109,45 @@
         <v>14.36</v>
       </c>
       <c r="M71">
-        <v>5.67847506</v>
+        <v>6.0732476</v>
       </c>
       <c r="N71">
-        <v>8.681524939999999</v>
+        <v>8.286752399999999</v>
       </c>
       <c r="O71">
-        <v>1.9099354868</v>
+        <v>1.823085528</v>
       </c>
       <c r="P71">
-        <v>6.771589453199999</v>
+        <v>6.463666871999999</v>
       </c>
       <c r="Q71">
-        <v>10.1115894532</v>
+        <v>9.803666871999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1671867854472067</v>
+        <v>0.1709076725276445</v>
       </c>
       <c r="T71">
-        <v>2.046755589518912</v>
+        <v>2.109495091201878</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.528847947427632</v>
+        <v>2.364468064829104</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09265910175829335</v>
+        <v>0.09269474002795265</v>
       </c>
       <c r="C72">
-        <v>28.26821636201164</v>
+        <v>27.04689032805931</v>
       </c>
       <c r="D72">
-        <v>100.9602163620116</v>
+        <v>100.8834903280593</v>
       </c>
       <c r="E72">
-        <v>76.962</v>
+        <v>78.10660000000001</v>
       </c>
       <c r="F72">
-        <v>80.122</v>
+        <v>81.26660000000001</v>
       </c>
       <c r="G72">
         <v>7.43</v>
@@ -7191,28 +7191,28 @@
         <v>14.36</v>
       </c>
       <c r="M72">
-        <v>6.0732476</v>
+        <v>6.160008280000001</v>
       </c>
       <c r="N72">
-        <v>8.286752399999999</v>
+        <v>8.199991719999998</v>
       </c>
       <c r="O72">
-        <v>1.823085528</v>
+        <v>1.8039981784</v>
       </c>
       <c r="P72">
-        <v>6.463666871999999</v>
+        <v>6.395993541599998</v>
       </c>
       <c r="Q72">
-        <v>9.803666871999999</v>
+        <v>9.735993541599999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1709076725276445</v>
+        <v>0.1748851725101816</v>
       </c>
       <c r="T72">
-        <v>2.109495091201878</v>
+        <v>2.176561455069876</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.364468064829104</v>
+        <v>2.331165697718834</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09269474002795265</v>
+        <v>0.09273037829761194</v>
       </c>
       <c r="C73">
-        <v>27.04689032805932</v>
+        <v>25.82568082345055</v>
       </c>
       <c r="D73">
-        <v>100.8834903280593</v>
+        <v>100.8068808234506</v>
       </c>
       <c r="E73">
-        <v>78.1066</v>
+        <v>79.2512</v>
       </c>
       <c r="F73">
-        <v>81.2666</v>
+        <v>82.41119999999999</v>
       </c>
       <c r="G73">
         <v>7.43</v>
@@ -7273,28 +7273,28 @@
         <v>14.36</v>
       </c>
       <c r="M73">
-        <v>6.16000828</v>
+        <v>6.24676896</v>
       </c>
       <c r="N73">
-        <v>8.19999172</v>
+        <v>8.113231039999999</v>
       </c>
       <c r="O73">
-        <v>1.8039981784</v>
+        <v>1.7849108288</v>
       </c>
       <c r="P73">
-        <v>6.3959935416</v>
+        <v>6.328320211199999</v>
       </c>
       <c r="Q73">
-        <v>9.735993541599999</v>
+        <v>9.668320211199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1748851725101815</v>
+        <v>0.1791467796343283</v>
       </c>
       <c r="T73">
-        <v>2.176561455069876</v>
+        <v>2.248418273499873</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.331165697718835</v>
+        <v>2.298788396361629</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09273037829761194</v>
+        <v>0.09276601656727121</v>
       </c>
       <c r="C74">
-        <v>25.82568082345055</v>
+        <v>24.60458758291462</v>
       </c>
       <c r="D74">
-        <v>100.8068808234506</v>
+        <v>100.7303875829146</v>
       </c>
       <c r="E74">
-        <v>79.2512</v>
+        <v>80.39579999999999</v>
       </c>
       <c r="F74">
-        <v>82.41119999999999</v>
+        <v>83.55579999999999</v>
       </c>
       <c r="G74">
         <v>7.43</v>
@@ -7355,28 +7355,28 @@
         <v>14.36</v>
       </c>
       <c r="M74">
-        <v>6.24676896</v>
+        <v>6.33352964</v>
       </c>
       <c r="N74">
-        <v>8.113231039999999</v>
+        <v>8.026470359999999</v>
       </c>
       <c r="O74">
-        <v>1.7849108288</v>
+        <v>1.7658234792</v>
       </c>
       <c r="P74">
-        <v>6.328320211199999</v>
+        <v>6.2606468808</v>
       </c>
       <c r="Q74">
-        <v>9.668320211199999</v>
+        <v>9.600646880799999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1791467796343283</v>
+        <v>0.1837240613602637</v>
       </c>
       <c r="T74">
-        <v>2.248418273499873</v>
+        <v>2.325597819220982</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.298788396361629</v>
+        <v>2.267298144356675</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09276601656727121</v>
+        <v>0.09280165483693051</v>
       </c>
       <c r="C75">
-        <v>24.60458758291462</v>
+        <v>23.38361034198512</v>
       </c>
       <c r="D75">
-        <v>100.7303875829146</v>
+        <v>100.6540103419851</v>
       </c>
       <c r="E75">
-        <v>80.39579999999999</v>
+        <v>81.54039999999999</v>
       </c>
       <c r="F75">
-        <v>83.55579999999999</v>
+        <v>84.70039999999999</v>
       </c>
       <c r="G75">
         <v>7.43</v>
@@ -7437,28 +7437,28 @@
         <v>14.36</v>
       </c>
       <c r="M75">
-        <v>6.33352964</v>
+        <v>6.420290319999999</v>
       </c>
       <c r="N75">
-        <v>8.026470359999999</v>
+        <v>7.93970968</v>
       </c>
       <c r="O75">
-        <v>1.7658234792</v>
+        <v>1.7467361296</v>
       </c>
       <c r="P75">
-        <v>6.2606468808</v>
+        <v>6.1929735504</v>
       </c>
       <c r="Q75">
-        <v>9.600646880799999</v>
+        <v>9.532973550399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1837240613602637</v>
+        <v>0.1886534416805019</v>
       </c>
       <c r="T75">
-        <v>2.325597819220982</v>
+        <v>2.408714253074484</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.267298144356675</v>
+        <v>2.236658980243747</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09280165483693051</v>
+        <v>0.09283729310658978</v>
       </c>
       <c r="C76">
-        <v>23.38361034198512</v>
+        <v>22.16274883699742</v>
       </c>
       <c r="D76">
-        <v>100.6540103419851</v>
+        <v>100.5777488369974</v>
       </c>
       <c r="E76">
-        <v>81.54039999999999</v>
+        <v>82.685</v>
       </c>
       <c r="F76">
-        <v>84.70039999999999</v>
+        <v>85.845</v>
       </c>
       <c r="G76">
         <v>7.43</v>
@@ -7519,28 +7519,28 @@
         <v>14.36</v>
       </c>
       <c r="M76">
-        <v>6.420290319999999</v>
+        <v>6.507051000000001</v>
       </c>
       <c r="N76">
-        <v>7.93970968</v>
+        <v>7.852948999999999</v>
       </c>
       <c r="O76">
-        <v>1.7467361296</v>
+        <v>1.72764878</v>
       </c>
       <c r="P76">
-        <v>6.1929735504</v>
+        <v>6.125300219999999</v>
       </c>
       <c r="Q76">
-        <v>9.532973550399999</v>
+        <v>9.46530022</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1886534416805019</v>
+        <v>0.1939771724263591</v>
       </c>
       <c r="T76">
-        <v>2.408714253074484</v>
+        <v>2.498480001636266</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.236658980243747</v>
+        <v>2.206836860507163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09283729310658978</v>
+        <v>0.09287293137624908</v>
       </c>
       <c r="C77">
-        <v>22.16274883699742</v>
+        <v>20.9420028050852</v>
       </c>
       <c r="D77">
-        <v>100.5777488369974</v>
+        <v>100.5016028050852</v>
       </c>
       <c r="E77">
-        <v>82.685</v>
+        <v>83.8296</v>
       </c>
       <c r="F77">
-        <v>85.845</v>
+        <v>86.9896</v>
       </c>
       <c r="G77">
         <v>7.43</v>
@@ -7601,28 +7601,28 @@
         <v>14.36</v>
       </c>
       <c r="M77">
-        <v>6.507051000000001</v>
+        <v>6.59381168</v>
       </c>
       <c r="N77">
-        <v>7.852948999999999</v>
+        <v>7.766188319999999</v>
       </c>
       <c r="O77">
-        <v>1.72764878</v>
+        <v>1.7085614304</v>
       </c>
       <c r="P77">
-        <v>6.125300219999999</v>
+        <v>6.0576268896</v>
       </c>
       <c r="Q77">
-        <v>9.46530022</v>
+        <v>9.3976268896</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1939771724263591</v>
+        <v>0.1997445474010378</v>
       </c>
       <c r="T77">
-        <v>2.498480001636266</v>
+        <v>2.595726229244864</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.206836860507163</v>
+        <v>2.177799533395227</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09287293137624908</v>
+        <v>0.09290856964590835</v>
       </c>
       <c r="C78">
-        <v>20.9420028050852</v>
+        <v>19.72137198417769</v>
       </c>
       <c r="D78">
-        <v>100.5016028050852</v>
+        <v>100.4255719841777</v>
       </c>
       <c r="E78">
-        <v>83.8296</v>
+        <v>84.9742</v>
       </c>
       <c r="F78">
-        <v>86.9896</v>
+        <v>88.13419999999999</v>
       </c>
       <c r="G78">
         <v>7.43</v>
@@ -7683,28 +7683,28 @@
         <v>14.36</v>
       </c>
       <c r="M78">
-        <v>6.59381168</v>
+        <v>6.68057236</v>
       </c>
       <c r="N78">
-        <v>7.766188319999999</v>
+        <v>7.679427639999999</v>
       </c>
       <c r="O78">
-        <v>1.7085614304</v>
+        <v>1.6894740808</v>
       </c>
       <c r="P78">
-        <v>6.0576268896</v>
+        <v>5.989953559199999</v>
       </c>
       <c r="Q78">
-        <v>9.3976268896</v>
+        <v>9.3299535592</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1997445474010378</v>
+        <v>0.2060134332430798</v>
       </c>
       <c r="T78">
-        <v>2.595726229244864</v>
+        <v>2.701428650558556</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.177799533395227</v>
+        <v>2.149516422571913</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09290856964590835</v>
+        <v>0.09294420791556764</v>
       </c>
       <c r="C79">
-        <v>19.72137198417769</v>
+        <v>18.50085611299643</v>
       </c>
       <c r="D79">
-        <v>100.4255719841777</v>
+        <v>100.3496561129964</v>
       </c>
       <c r="E79">
-        <v>84.9742</v>
+        <v>86.11880000000001</v>
       </c>
       <c r="F79">
-        <v>88.13419999999999</v>
+        <v>89.2788</v>
       </c>
       <c r="G79">
         <v>7.43</v>
@@ -7765,28 +7765,28 @@
         <v>14.36</v>
       </c>
       <c r="M79">
-        <v>6.68057236</v>
+        <v>6.76733304</v>
       </c>
       <c r="N79">
-        <v>7.679427639999999</v>
+        <v>7.592666959999999</v>
       </c>
       <c r="O79">
-        <v>1.6894740808</v>
+        <v>1.6703867312</v>
       </c>
       <c r="P79">
-        <v>5.989953559199999</v>
+        <v>5.922280228799999</v>
       </c>
       <c r="Q79">
-        <v>9.3299535592</v>
+        <v>9.262280228799998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2060134332430798</v>
+        <v>0.2128522177980347</v>
       </c>
       <c r="T79">
-        <v>2.701428650558556</v>
+        <v>2.816740382900766</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.149516422571913</v>
+        <v>2.121958519718426</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09294420791556764</v>
+        <v>0.09297984618522692</v>
       </c>
       <c r="C80">
-        <v>18.50085611299643</v>
+        <v>17.28045493105255</v>
       </c>
       <c r="D80">
-        <v>100.3496561129964</v>
+        <v>100.2738549310525</v>
       </c>
       <c r="E80">
-        <v>86.11880000000001</v>
+        <v>87.2634</v>
       </c>
       <c r="F80">
-        <v>89.2788</v>
+        <v>90.4234</v>
       </c>
       <c r="G80">
         <v>7.43</v>
@@ -7847,28 +7847,28 @@
         <v>14.36</v>
       </c>
       <c r="M80">
-        <v>6.76733304</v>
+        <v>6.854093720000001</v>
       </c>
       <c r="N80">
-        <v>7.592666959999999</v>
+        <v>7.505906279999999</v>
       </c>
       <c r="O80">
-        <v>1.6703867312</v>
+        <v>1.6512993816</v>
       </c>
       <c r="P80">
-        <v>5.922280228799999</v>
+        <v>5.854606898399999</v>
       </c>
       <c r="Q80">
-        <v>9.262280228799998</v>
+        <v>9.1946068984</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2128522177980347</v>
+        <v>0.2203423151677473</v>
       </c>
       <c r="T80">
-        <v>2.816740382900766</v>
+        <v>2.943034184989854</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.121958519718426</v>
+        <v>2.095098285291611</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09297984618522692</v>
+        <v>0.09301548445488622</v>
       </c>
       <c r="C81">
-        <v>17.28045493105255</v>
+        <v>16.06016817864351</v>
       </c>
       <c r="D81">
-        <v>100.2738549310525</v>
+        <v>100.1981681786435</v>
       </c>
       <c r="E81">
-        <v>87.2634</v>
+        <v>88.408</v>
       </c>
       <c r="F81">
-        <v>90.4234</v>
+        <v>91.568</v>
       </c>
       <c r="G81">
         <v>7.43</v>
@@ -7929,28 +7929,28 @@
         <v>14.36</v>
       </c>
       <c r="M81">
-        <v>6.854093720000001</v>
+        <v>6.9408544</v>
       </c>
       <c r="N81">
-        <v>7.505906279999999</v>
+        <v>7.419145599999999</v>
       </c>
       <c r="O81">
-        <v>1.6512993816</v>
+        <v>1.632212032</v>
       </c>
       <c r="P81">
-        <v>5.854606898399999</v>
+        <v>5.786933567999999</v>
       </c>
       <c r="Q81">
-        <v>9.1946068984</v>
+        <v>9.126933567999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2203423151677473</v>
+        <v>0.228581422274431</v>
       </c>
       <c r="T81">
-        <v>2.943034184989854</v>
+        <v>3.08195736728785</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.095098285291611</v>
+        <v>2.068909556725466</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09301548445488622</v>
+        <v>0.09305112272454549</v>
       </c>
       <c r="C82">
-        <v>16.06016817864351</v>
+        <v>14.83999559685041</v>
       </c>
       <c r="D82">
-        <v>100.1981681786435</v>
+        <v>100.1225955968504</v>
       </c>
       <c r="E82">
-        <v>88.408</v>
+        <v>89.5526</v>
       </c>
       <c r="F82">
-        <v>91.568</v>
+        <v>92.71259999999999</v>
       </c>
       <c r="G82">
         <v>7.43</v>
@@ -8011,28 +8011,28 @@
         <v>14.36</v>
       </c>
       <c r="M82">
-        <v>6.9408544</v>
+        <v>7.02761508</v>
       </c>
       <c r="N82">
-        <v>7.419145599999999</v>
+        <v>7.332384919999999</v>
       </c>
       <c r="O82">
-        <v>1.632212032</v>
+        <v>1.6131246824</v>
       </c>
       <c r="P82">
-        <v>5.786933567999999</v>
+        <v>5.719260237599999</v>
       </c>
       <c r="Q82">
-        <v>9.126933567999998</v>
+        <v>9.0592602376</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.228581422274431</v>
+        <v>0.2376878038133973</v>
       </c>
       <c r="T82">
-        <v>3.08195736728785</v>
+        <v>3.235504042459319</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.068909556725466</v>
+        <v>2.043367463432559</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09305112272454549</v>
+        <v>0.09308676099420478</v>
       </c>
       <c r="C83">
-        <v>14.83999559685041</v>
+        <v>13.61993692753481</v>
       </c>
       <c r="D83">
-        <v>100.1225955968504</v>
+        <v>100.0471369275348</v>
       </c>
       <c r="E83">
-        <v>89.5526</v>
+        <v>90.69720000000001</v>
       </c>
       <c r="F83">
-        <v>92.71259999999999</v>
+        <v>93.85720000000001</v>
       </c>
       <c r="G83">
         <v>7.43</v>
@@ -8093,28 +8093,28 @@
         <v>14.36</v>
       </c>
       <c r="M83">
-        <v>7.02761508</v>
+        <v>7.114375760000001</v>
       </c>
       <c r="N83">
-        <v>7.332384919999999</v>
+        <v>7.245624239999999</v>
       </c>
       <c r="O83">
-        <v>1.6131246824</v>
+        <v>1.5940373328</v>
       </c>
       <c r="P83">
-        <v>5.719260237599999</v>
+        <v>5.651586907199999</v>
       </c>
       <c r="Q83">
-        <v>9.0592602376</v>
+        <v>8.991586907199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2376878038133973</v>
+        <v>0.2478060055233599</v>
       </c>
       <c r="T83">
-        <v>3.235504042459319</v>
+        <v>3.406111459316508</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.043367463432559</v>
+        <v>2.018448348024845</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09308676099420478</v>
+        <v>0.1023154792638641</v>
       </c>
       <c r="C84">
-        <v>13.61993692753481</v>
+        <v>-3.861901160448753</v>
       </c>
       <c r="D84">
-        <v>100.0471369275348</v>
+        <v>83.70989883955126</v>
       </c>
       <c r="E84">
-        <v>90.69720000000001</v>
+        <v>91.84180000000001</v>
       </c>
       <c r="F84">
-        <v>93.85720000000001</v>
+        <v>95.0018</v>
       </c>
       <c r="G84">
         <v>7.43</v>
@@ -8175,45 +8175,45 @@
         <v>14.36</v>
       </c>
       <c r="M84">
-        <v>7.114375760000001</v>
+        <v>8.550162</v>
       </c>
       <c r="N84">
-        <v>7.245624239999999</v>
+        <v>5.809837999999999</v>
       </c>
       <c r="O84">
-        <v>1.5940373328</v>
+        <v>1.27816436</v>
       </c>
       <c r="P84">
-        <v>5.651586907199999</v>
+        <v>4.531673639999999</v>
       </c>
       <c r="Q84">
-        <v>8.991586907199999</v>
+        <v>7.871673639999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2478060055233599</v>
+        <v>0.2591145839050827</v>
       </c>
       <c r="T84">
-        <v>3.406111459316508</v>
+        <v>3.596790336980424</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.22</v>
       </c>
       <c r="W84">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.018448348024845</v>
+        <v>1.679500341630954</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1023154792638641</v>
+        <v>0.1024618775335233</v>
       </c>
       <c r="C85">
-        <v>-3.861901160448753</v>
+        <v>-5.222783868980827</v>
       </c>
       <c r="D85">
-        <v>83.70989883955126</v>
+        <v>83.49361613101917</v>
       </c>
       <c r="E85">
-        <v>91.84180000000001</v>
+        <v>92.9864</v>
       </c>
       <c r="F85">
-        <v>95.0018</v>
+        <v>96.1464</v>
       </c>
       <c r="G85">
         <v>7.43</v>
@@ -8257,28 +8257,28 @@
         <v>14.36</v>
       </c>
       <c r="M85">
-        <v>8.550162</v>
+        <v>8.653176</v>
       </c>
       <c r="N85">
-        <v>5.809837999999999</v>
+        <v>5.706823999999999</v>
       </c>
       <c r="O85">
-        <v>1.27816436</v>
+        <v>1.25550128</v>
       </c>
       <c r="P85">
-        <v>4.531673639999999</v>
+        <v>4.451322719999999</v>
       </c>
       <c r="Q85">
-        <v>7.871673639999999</v>
+        <v>7.791322719999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2591145839050827</v>
+        <v>0.271836734584521</v>
       </c>
       <c r="T85">
-        <v>3.596790336980424</v>
+        <v>3.811304074352331</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.679500341630954</v>
+        <v>1.659506289944871</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1024618775335233</v>
+        <v>0.1026082758031826</v>
       </c>
       <c r="C86">
-        <v>-5.222783868980812</v>
+        <v>-6.582551830978588</v>
       </c>
       <c r="D86">
-        <v>83.49361613101917</v>
+        <v>83.2784481690214</v>
       </c>
       <c r="E86">
-        <v>92.98639999999999</v>
+        <v>94.131</v>
       </c>
       <c r="F86">
-        <v>96.14639999999999</v>
+        <v>97.291</v>
       </c>
       <c r="G86">
         <v>7.43</v>
@@ -8339,28 +8339,28 @@
         <v>14.36</v>
       </c>
       <c r="M86">
-        <v>8.653175999999998</v>
+        <v>8.75619</v>
       </c>
       <c r="N86">
-        <v>5.706824000000001</v>
+        <v>5.603809999999999</v>
       </c>
       <c r="O86">
-        <v>1.25550128</v>
+        <v>1.2328382</v>
       </c>
       <c r="P86">
-        <v>4.45132272</v>
+        <v>4.3709718</v>
       </c>
       <c r="Q86">
-        <v>7.79132272</v>
+        <v>7.710971799999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2718367345845208</v>
+        <v>0.2862551720212175</v>
       </c>
       <c r="T86">
-        <v>3.811304074352328</v>
+        <v>4.054419643373821</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.659506289944871</v>
+        <v>1.639982686533755</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1026082758031826</v>
+        <v>0.1027546740728419</v>
       </c>
       <c r="C87">
-        <v>-6.582551830978588</v>
+        <v>-7.941213642591492</v>
       </c>
       <c r="D87">
-        <v>83.2784481690214</v>
+        <v>83.06438635740851</v>
       </c>
       <c r="E87">
-        <v>94.131</v>
+        <v>95.2756</v>
       </c>
       <c r="F87">
-        <v>97.291</v>
+        <v>98.43559999999999</v>
       </c>
       <c r="G87">
         <v>7.43</v>
@@ -8421,28 +8421,28 @@
         <v>14.36</v>
       </c>
       <c r="M87">
-        <v>8.75619</v>
+        <v>8.859203999999998</v>
       </c>
       <c r="N87">
-        <v>5.603809999999999</v>
+        <v>5.500796000000001</v>
       </c>
       <c r="O87">
-        <v>1.2328382</v>
+        <v>1.21017512</v>
       </c>
       <c r="P87">
-        <v>4.3709718</v>
+        <v>4.290620880000001</v>
       </c>
       <c r="Q87">
-        <v>7.710971799999999</v>
+        <v>7.63062088</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2862551720212175</v>
+        <v>0.302733386234585</v>
       </c>
       <c r="T87">
-        <v>4.054419643373821</v>
+        <v>4.332266007969813</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.639982686533755</v>
+        <v>1.62091312041127</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1027546740728419</v>
+        <v>0.1029010723425012</v>
       </c>
       <c r="C88">
-        <v>-7.941213642591492</v>
+        <v>-9.298777811812243</v>
       </c>
       <c r="D88">
-        <v>83.06438635740851</v>
+        <v>82.85142218818775</v>
       </c>
       <c r="E88">
-        <v>95.2756</v>
+        <v>96.42019999999999</v>
       </c>
       <c r="F88">
-        <v>98.43559999999999</v>
+        <v>99.58019999999999</v>
       </c>
       <c r="G88">
         <v>7.43</v>
@@ -8503,28 +8503,28 @@
         <v>14.36</v>
       </c>
       <c r="M88">
-        <v>8.859203999999998</v>
+        <v>8.962217999999998</v>
       </c>
       <c r="N88">
-        <v>5.500796000000001</v>
+        <v>5.397782000000001</v>
       </c>
       <c r="O88">
-        <v>1.21017512</v>
+        <v>1.18751204</v>
       </c>
       <c r="P88">
-        <v>4.290620880000001</v>
+        <v>4.210269960000001</v>
       </c>
       <c r="Q88">
-        <v>7.63062088</v>
+        <v>7.550269960000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.302733386234585</v>
+        <v>0.3217467103269323</v>
       </c>
       <c r="T88">
-        <v>4.332266007969813</v>
+        <v>4.652857967119035</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.62091312041127</v>
+        <v>1.602281935119186</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1029010723425012</v>
+        <v>0.1030474706121605</v>
       </c>
       <c r="C89">
-        <v>-9.298777811812243</v>
+        <v>-10.65525275960398</v>
       </c>
       <c r="D89">
-        <v>82.85142218818775</v>
+        <v>82.63954724039601</v>
       </c>
       <c r="E89">
-        <v>96.42019999999999</v>
+        <v>97.56480000000001</v>
       </c>
       <c r="F89">
-        <v>99.58019999999999</v>
+        <v>100.7248</v>
       </c>
       <c r="G89">
         <v>7.43</v>
@@ -8585,28 +8585,28 @@
         <v>14.36</v>
       </c>
       <c r="M89">
-        <v>8.962217999999998</v>
+        <v>9.065232</v>
       </c>
       <c r="N89">
-        <v>5.397782000000001</v>
+        <v>5.294767999999999</v>
       </c>
       <c r="O89">
-        <v>1.18751204</v>
+        <v>1.16484896</v>
       </c>
       <c r="P89">
-        <v>4.210269960000001</v>
+        <v>4.12991904</v>
       </c>
       <c r="Q89">
-        <v>7.550269960000001</v>
+        <v>7.46991904</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3217467103269323</v>
+        <v>0.3439289217680039</v>
       </c>
       <c r="T89">
-        <v>4.652857967119035</v>
+        <v>5.026881919459793</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.602281935119186</v>
+        <v>1.584074185856468</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1030474706121605</v>
+        <v>0.1031938688818198</v>
       </c>
       <c r="C90">
-        <v>-10.65525275960398</v>
+        <v>-12.01064682101033</v>
       </c>
       <c r="D90">
-        <v>82.63954724039601</v>
+        <v>82.42875317898968</v>
       </c>
       <c r="E90">
-        <v>97.56480000000001</v>
+        <v>98.7094</v>
       </c>
       <c r="F90">
-        <v>100.7248</v>
+        <v>101.8694</v>
       </c>
       <c r="G90">
         <v>7.43</v>
@@ -8667,28 +8667,28 @@
         <v>14.36</v>
       </c>
       <c r="M90">
-        <v>9.065232</v>
+        <v>9.168246</v>
       </c>
       <c r="N90">
-        <v>5.294767999999999</v>
+        <v>5.191754</v>
       </c>
       <c r="O90">
-        <v>1.16484896</v>
+        <v>1.14218588</v>
       </c>
       <c r="P90">
-        <v>4.12991904</v>
+        <v>4.04956812</v>
       </c>
       <c r="Q90">
-        <v>7.46991904</v>
+        <v>7.38956812</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3439289217680039</v>
+        <v>0.3701442625619978</v>
       </c>
       <c r="T90">
-        <v>5.026881919459793</v>
+        <v>5.468910226771599</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.584074185856468</v>
+        <v>1.56627559949853</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1031938688818198</v>
+        <v>0.103340267151479</v>
       </c>
       <c r="C91">
-        <v>-12.01064682101033</v>
+        <v>-13.36496824624818</v>
       </c>
       <c r="D91">
-        <v>82.42875317898968</v>
+        <v>82.21903175375181</v>
       </c>
       <c r="E91">
-        <v>98.7094</v>
+        <v>99.854</v>
       </c>
       <c r="F91">
-        <v>101.8694</v>
+        <v>103.014</v>
       </c>
       <c r="G91">
         <v>7.43</v>
@@ -8749,28 +8749,28 @@
         <v>14.36</v>
       </c>
       <c r="M91">
-        <v>9.168246</v>
+        <v>9.27126</v>
       </c>
       <c r="N91">
-        <v>5.191754</v>
+        <v>5.08874</v>
       </c>
       <c r="O91">
-        <v>1.14218588</v>
+        <v>1.1195228</v>
       </c>
       <c r="P91">
-        <v>4.04956812</v>
+        <v>3.9692172</v>
       </c>
       <c r="Q91">
-        <v>7.38956812</v>
+        <v>7.309217199999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3701442625619978</v>
+        <v>0.4016026715147905</v>
       </c>
       <c r="T91">
-        <v>5.468910226771599</v>
+        <v>5.999344195545766</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.56627559949853</v>
+        <v>1.54887253728188</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.103340267151479</v>
+        <v>0.1034866654211383</v>
       </c>
       <c r="C92">
-        <v>-13.36496824624818</v>
+        <v>-14.71822520178439</v>
       </c>
       <c r="D92">
-        <v>82.21903175375181</v>
+        <v>82.01037479821559</v>
       </c>
       <c r="E92">
-        <v>99.854</v>
+        <v>100.9986</v>
       </c>
       <c r="F92">
-        <v>103.014</v>
+        <v>104.1586</v>
       </c>
       <c r="G92">
         <v>7.43</v>
@@ -8831,28 +8831,28 @@
         <v>14.36</v>
       </c>
       <c r="M92">
-        <v>9.27126</v>
+        <v>9.374274</v>
       </c>
       <c r="N92">
-        <v>5.08874</v>
+        <v>4.985726</v>
       </c>
       <c r="O92">
-        <v>1.1195228</v>
+        <v>1.09685972</v>
       </c>
       <c r="P92">
-        <v>3.9692172</v>
+        <v>3.88886628</v>
       </c>
       <c r="Q92">
-        <v>7.309217199999999</v>
+        <v>7.22886628</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4016026715147905</v>
+        <v>0.4400518380126482</v>
       </c>
       <c r="T92">
-        <v>5.999344195545766</v>
+        <v>6.647652379603082</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.54887253728188</v>
+        <v>1.531851959949112</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1034866654211383</v>
+        <v>0.1036330636907976</v>
       </c>
       <c r="C93">
-        <v>-14.71822520178439</v>
+        <v>-16.07042577139558</v>
       </c>
       <c r="D93">
-        <v>82.01037479821559</v>
+        <v>81.80277422860443</v>
       </c>
       <c r="E93">
-        <v>100.9986</v>
+        <v>102.1432</v>
       </c>
       <c r="F93">
-        <v>104.1586</v>
+        <v>105.3032</v>
       </c>
       <c r="G93">
         <v>7.43</v>
@@ -8913,28 +8913,28 @@
         <v>14.36</v>
       </c>
       <c r="M93">
-        <v>9.374274</v>
+        <v>9.477288</v>
       </c>
       <c r="N93">
-        <v>4.985726</v>
+        <v>4.882712</v>
       </c>
       <c r="O93">
-        <v>1.09685972</v>
+        <v>1.07419664</v>
       </c>
       <c r="P93">
-        <v>3.88886628</v>
+        <v>3.808515359999999</v>
       </c>
       <c r="Q93">
-        <v>7.22886628</v>
+        <v>7.148515359999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4400518380126482</v>
+        <v>0.4881132961349705</v>
       </c>
       <c r="T93">
-        <v>6.647652379603082</v>
+        <v>7.458037609674728</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.531851959949112</v>
+        <v>1.515201395167056</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1036330636907976</v>
+        <v>0.1481522446376782</v>
       </c>
       <c r="C94">
-        <v>-16.07042577139558</v>
+        <v>-52.7959993077535</v>
       </c>
       <c r="D94">
-        <v>81.80277422860443</v>
+        <v>46.2218006922465</v>
       </c>
       <c r="E94">
-        <v>102.1432</v>
+        <v>103.2878</v>
       </c>
       <c r="F94">
-        <v>105.3032</v>
+        <v>106.4478</v>
       </c>
       <c r="G94">
         <v>7.43</v>
@@ -8995,45 +8995,45 @@
         <v>14.36</v>
       </c>
       <c r="M94">
-        <v>9.477288</v>
+        <v>15.62653704</v>
       </c>
       <c r="N94">
-        <v>4.882712</v>
+        <v>-1.266537040000003</v>
       </c>
       <c r="O94">
-        <v>1.07419664</v>
+        <v>-0.2786381488000007</v>
       </c>
       <c r="P94">
-        <v>3.808515359999999</v>
+        <v>-0.9878988912000022</v>
       </c>
       <c r="Q94">
-        <v>7.148515359999999</v>
+        <v>2.352101108799998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4881132961349705</v>
+        <v>0.5604164750291613</v>
       </c>
       <c r="T94">
-        <v>7.458037609674728</v>
+        <v>8.677173078139976</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.22</v>
+        <v>0.2021689125308597</v>
       </c>
       <c r="W94">
-        <v>0.0702</v>
+        <v>0.1171216036404698</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.515201395167056</v>
+        <v>0.9189496024129987</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1481522446376782</v>
+        <v>0.1491622446376782</v>
       </c>
       <c r="C95">
-        <v>-52.7959993077535</v>
+        <v>-54.39225376691132</v>
       </c>
       <c r="D95">
-        <v>46.2218006922465</v>
+        <v>45.77014623308868</v>
       </c>
       <c r="E95">
-        <v>103.2878</v>
+        <v>104.4324</v>
       </c>
       <c r="F95">
-        <v>106.4478</v>
+        <v>107.5924</v>
       </c>
       <c r="G95">
         <v>7.43</v>
@@ -9077,37 +9077,37 @@
         <v>14.36</v>
       </c>
       <c r="M95">
-        <v>15.62653704</v>
+        <v>15.79456432</v>
       </c>
       <c r="N95">
-        <v>-1.266537040000003</v>
+        <v>-1.434564320000002</v>
       </c>
       <c r="O95">
-        <v>-0.2786381488000007</v>
+        <v>-0.3156041504000003</v>
       </c>
       <c r="P95">
-        <v>-0.9878988912000022</v>
+        <v>-1.118960169600001</v>
       </c>
       <c r="Q95">
-        <v>2.352101108799998</v>
+        <v>2.221039830399999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5604164750291613</v>
+        <v>0.6461858875340216</v>
       </c>
       <c r="T95">
-        <v>8.677173078139976</v>
+        <v>10.12336859116331</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2021689125308597</v>
+        <v>0.2000181794188293</v>
       </c>
       <c r="W95">
-        <v>0.1171216036404698</v>
+        <v>0.1174373312613159</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9189496024129987</v>
+        <v>0.9091735428128604</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1491622446376782</v>
+        <v>0.1501722446376782</v>
       </c>
       <c r="C96">
-        <v>-54.39225376691132</v>
+        <v>-55.9797669940427</v>
       </c>
       <c r="D96">
-        <v>45.77014623308868</v>
+        <v>45.3272330059573</v>
       </c>
       <c r="E96">
-        <v>104.4324</v>
+        <v>105.577</v>
       </c>
       <c r="F96">
-        <v>107.5924</v>
+        <v>108.737</v>
       </c>
       <c r="G96">
         <v>7.43</v>
@@ -9159,37 +9159,37 @@
         <v>14.36</v>
       </c>
       <c r="M96">
-        <v>15.79456432</v>
+        <v>15.9625916</v>
       </c>
       <c r="N96">
-        <v>-1.434564320000002</v>
+        <v>-1.602591600000002</v>
       </c>
       <c r="O96">
-        <v>-0.3156041504000003</v>
+        <v>-0.3525701520000005</v>
       </c>
       <c r="P96">
-        <v>-1.118960169600001</v>
+        <v>-1.250021448000002</v>
       </c>
       <c r="Q96">
-        <v>2.221039830399999</v>
+        <v>2.089978551999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6461858875340216</v>
+        <v>0.7662630650408263</v>
       </c>
       <c r="T96">
-        <v>10.12336859116331</v>
+        <v>12.14804230939598</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2000181794188293</v>
+        <v>0.1979127248986311</v>
       </c>
       <c r="W96">
-        <v>0.1174373312613159</v>
+        <v>0.117746411984881</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9091735428128604</v>
+        <v>0.8996032949937777</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1501722446376782</v>
+        <v>0.1511822446376782</v>
       </c>
       <c r="C97">
-        <v>-55.9797669940427</v>
+        <v>-57.55879032117355</v>
       </c>
       <c r="D97">
-        <v>45.3272330059573</v>
+        <v>44.89280967882645</v>
       </c>
       <c r="E97">
-        <v>105.577</v>
+        <v>106.7216</v>
       </c>
       <c r="F97">
-        <v>108.737</v>
+        <v>109.8816</v>
       </c>
       <c r="G97">
         <v>7.43</v>
@@ -9241,37 +9241,37 @@
         <v>14.36</v>
       </c>
       <c r="M97">
-        <v>15.9625916</v>
+        <v>16.13061888</v>
       </c>
       <c r="N97">
-        <v>-1.602591600000002</v>
+        <v>-1.770618880000004</v>
       </c>
       <c r="O97">
-        <v>-0.3525701520000005</v>
+        <v>-0.3895361536000009</v>
       </c>
       <c r="P97">
-        <v>-1.250021448000002</v>
+        <v>-1.381082726400003</v>
       </c>
       <c r="Q97">
-        <v>2.089978551999998</v>
+        <v>1.958917273599996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7662630650408263</v>
+        <v>0.9463788313010332</v>
       </c>
       <c r="T97">
-        <v>12.14804230939598</v>
+        <v>15.18505288674497</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1979127248986311</v>
+        <v>0.1958511340142703</v>
       </c>
       <c r="W97">
-        <v>0.117746411984881</v>
+        <v>0.1180490535267051</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8996032949937777</v>
+        <v>0.8902324273375924</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1511822446376782</v>
+        <v>0.1521922446376782</v>
       </c>
       <c r="C98">
-        <v>-57.55879032117354</v>
+        <v>-59.12956553657599</v>
       </c>
       <c r="D98">
-        <v>44.89280967882645</v>
+        <v>44.466634463424</v>
       </c>
       <c r="E98">
-        <v>106.7216</v>
+        <v>107.8662</v>
       </c>
       <c r="F98">
-        <v>109.8816</v>
+        <v>111.0262</v>
       </c>
       <c r="G98">
         <v>7.43</v>
@@ -9323,37 +9323,37 @@
         <v>14.36</v>
       </c>
       <c r="M98">
-        <v>16.13061888</v>
+        <v>16.29864616</v>
       </c>
       <c r="N98">
-        <v>-1.770618880000001</v>
+        <v>-1.938646160000001</v>
       </c>
       <c r="O98">
-        <v>-0.3895361536000002</v>
+        <v>-0.4265021552000002</v>
       </c>
       <c r="P98">
-        <v>-1.381082726400001</v>
+        <v>-1.512144004800001</v>
       </c>
       <c r="Q98">
-        <v>1.958917273599999</v>
+        <v>1.827855995199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9463788313010308</v>
+        <v>1.246571775068041</v>
       </c>
       <c r="T98">
-        <v>15.18505288674494</v>
+        <v>20.24673718232658</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1958511340142704</v>
+        <v>0.1938320501584531</v>
       </c>
       <c r="W98">
-        <v>0.1180490535267051</v>
+        <v>0.1183454550367391</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8902324273375926</v>
+        <v>0.8810547734475143</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1521922446376782</v>
+        <v>0.1532022446376782</v>
       </c>
       <c r="C99">
-        <v>-59.12956553657599</v>
+        <v>-60.69232533351104</v>
       </c>
       <c r="D99">
-        <v>44.466634463424</v>
+        <v>44.04847466648895</v>
       </c>
       <c r="E99">
-        <v>107.8662</v>
+        <v>109.0108</v>
       </c>
       <c r="F99">
-        <v>111.0262</v>
+        <v>112.1708</v>
       </c>
       <c r="G99">
         <v>7.43</v>
@@ -9405,37 +9405,37 @@
         <v>14.36</v>
       </c>
       <c r="M99">
-        <v>16.29864616</v>
+        <v>16.46667344</v>
       </c>
       <c r="N99">
-        <v>-1.938646160000001</v>
+        <v>-2.106673440000002</v>
       </c>
       <c r="O99">
-        <v>-0.4265021552000002</v>
+        <v>-0.4634681568000004</v>
       </c>
       <c r="P99">
-        <v>-1.512144004800001</v>
+        <v>-1.643205283200001</v>
       </c>
       <c r="Q99">
-        <v>1.827855995199999</v>
+        <v>1.696794716799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.246571775068041</v>
+        <v>1.846957662602062</v>
       </c>
       <c r="T99">
-        <v>20.24673718232658</v>
+        <v>30.37010577348987</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1938320501584531</v>
+        <v>0.1918541720956118</v>
       </c>
       <c r="W99">
-        <v>0.1183454550367391</v>
+        <v>0.1186358075363642</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8810547734475143</v>
+        <v>0.8720644186164173</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1532022446376782</v>
+        <v>0.1542122446376782</v>
       </c>
       <c r="C100">
-        <v>-60.69232533351104</v>
+        <v>-62.24729373388722</v>
       </c>
       <c r="D100">
-        <v>44.04847466648895</v>
+        <v>43.63810626611278</v>
       </c>
       <c r="E100">
-        <v>109.0108</v>
+        <v>110.1554</v>
       </c>
       <c r="F100">
-        <v>112.1708</v>
+        <v>113.3154</v>
       </c>
       <c r="G100">
         <v>7.43</v>
@@ -9487,37 +9487,37 @@
         <v>14.36</v>
       </c>
       <c r="M100">
-        <v>16.46667344</v>
+        <v>16.63470072</v>
       </c>
       <c r="N100">
-        <v>-2.106673440000002</v>
+        <v>-2.274700720000002</v>
       </c>
       <c r="O100">
-        <v>-0.4634681568000004</v>
+        <v>-0.5004341584000005</v>
       </c>
       <c r="P100">
-        <v>-1.643205283200001</v>
+        <v>-1.774266561600002</v>
       </c>
       <c r="Q100">
-        <v>1.696794716799999</v>
+        <v>1.565733438399998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.846957662602062</v>
+        <v>3.648115325204123</v>
       </c>
       <c r="T100">
-        <v>30.37010577348987</v>
+        <v>60.74021154697974</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1918541720956118</v>
+        <v>0.1899162511653531</v>
       </c>
       <c r="W100">
-        <v>0.1186358075363642</v>
+        <v>0.1189202943289262</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8720644186164173</v>
+        <v>0.8632556871152413</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1542122446376782</v>
-      </c>
-      <c r="C101">
-        <v>-62.24729373388722</v>
-      </c>
-      <c r="D101">
-        <v>43.63810626611278</v>
-      </c>
-      <c r="E101">
-        <v>110.1554</v>
-      </c>
-      <c r="F101">
-        <v>113.3154</v>
-      </c>
-      <c r="G101">
-        <v>7.43</v>
-      </c>
-      <c r="H101">
-        <v>111.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.7</v>
-      </c>
-      <c r="K101">
-        <v>3.34</v>
-      </c>
-      <c r="L101">
-        <v>14.36</v>
-      </c>
-      <c r="M101">
-        <v>16.63470072</v>
-      </c>
-      <c r="N101">
-        <v>-2.274700720000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.5004341584000005</v>
-      </c>
-      <c r="P101">
-        <v>-1.774266561600002</v>
-      </c>
-      <c r="Q101">
-        <v>1.565733438399998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.648115325204123</v>
-      </c>
-      <c r="T101">
-        <v>60.74021154697974</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1899162511653531</v>
-      </c>
-      <c r="W101">
-        <v>0.1189202943289262</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8632556871152413</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
